--- a/research/traditional_assets/database/data/mongolia/mongolia_steel.xlsx
+++ b/research/traditional_assets/database/data/mongolia/mongolia_steel.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sehk_975" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.102</v>
+        <v>0.137</v>
+      </c>
+      <c r="E2">
+        <v>0.512</v>
       </c>
       <c r="G2">
-        <v>0.1943734015345268</v>
+        <v>0.1381845086627882</v>
       </c>
       <c r="H2">
-        <v>0.1943734015345268</v>
+        <v>0.1381845086627882</v>
       </c>
       <c r="I2">
-        <v>-0.2685421994884911</v>
+        <v>0.3258303558645598</v>
       </c>
       <c r="J2">
-        <v>-0.2685421994884911</v>
+        <v>0.2865134929235695</v>
       </c>
       <c r="K2">
-        <v>-74</v>
+        <v>227.829</v>
       </c>
       <c r="L2">
-        <v>-0.3785166240409207</v>
+        <v>0.2380884702725128</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>9.99</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.009617791470106864</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.04384867598066972</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>9.99</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>50.8</v>
+        <v>216.8</v>
       </c>
       <c r="V2">
-        <v>0.1853338197738051</v>
+        <v>0.2087224415134302</v>
       </c>
       <c r="W2">
-        <v>-0.08463913988333524</v>
+        <v>0.1295788537994401</v>
       </c>
       <c r="X2">
-        <v>0.4383101057611904</v>
+        <v>0.1949548772425486</v>
       </c>
       <c r="Y2">
-        <v>-0.5229492456445257</v>
+        <v>-0.06537602344310853</v>
       </c>
       <c r="Z2">
-        <v>0.1518210763376563</v>
+        <v>0.7462442486157684</v>
       </c>
       <c r="AA2">
-        <v>-0.04077036576842433</v>
+        <v>0.07190225542379128</v>
       </c>
       <c r="AB2">
-        <v>0.2748585179970939</v>
+        <v>0.1797785117861763</v>
       </c>
       <c r="AC2">
-        <v>-0.3156288837655182</v>
+        <v>-0.107876256362385</v>
       </c>
       <c r="AD2">
-        <v>451</v>
+        <v>341.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>451</v>
+        <v>341.6</v>
       </c>
       <c r="AG2">
-        <v>400.2</v>
+        <v>124.8</v>
       </c>
       <c r="AH2">
-        <v>0.6219831747345194</v>
+        <v>0.2474824313555024</v>
       </c>
       <c r="AI2">
-        <v>0.3451706719730599</v>
+        <v>0.2353427488804685</v>
       </c>
       <c r="AJ2">
-        <v>0.5935043749073113</v>
+        <v>0.1072625698324023</v>
       </c>
       <c r="AK2">
-        <v>0.3186813186813187</v>
+        <v>0.1010771847412327</v>
       </c>
       <c r="AL2">
-        <v>46.5</v>
+        <v>40.6</v>
       </c>
       <c r="AM2">
-        <v>46.464</v>
+        <v>39.849</v>
       </c>
       <c r="AN2">
-        <v>-59.81432360742706</v>
+        <v>0.8593062158830781</v>
       </c>
       <c r="AO2">
-        <v>-1.129032258064516</v>
+        <v>7.679556650246306</v>
       </c>
       <c r="AP2">
-        <v>-53.07692307692307</v>
+        <v>0.3139385706739115</v>
       </c>
       <c r="AQ2">
-        <v>-1.129907024793388</v>
+        <v>7.8242866822254</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +724,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.102</v>
+        <v>0.137</v>
+      </c>
+      <c r="E3">
+        <v>0.512</v>
       </c>
       <c r="G3">
-        <v>0.1943734015345268</v>
+        <v>0.1394813885403597</v>
       </c>
       <c r="H3">
-        <v>0.1943734015345268</v>
+        <v>0.1394813885403597</v>
       </c>
       <c r="I3">
-        <v>-0.2685421994884911</v>
+        <v>0.3272689251359264</v>
       </c>
       <c r="J3">
-        <v>-0.2685421994884911</v>
+        <v>0.2482880245364562</v>
       </c>
       <c r="K3">
-        <v>-74</v>
+        <v>228.2</v>
       </c>
       <c r="L3">
-        <v>-0.3785166240409207</v>
+        <v>0.2386030949393559</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>9.99</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.009968070245459988</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.04377738825591587</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +763,8973 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>9.99</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>50.8</v>
+        <v>208.2</v>
       </c>
       <c r="V3">
-        <v>0.1853338197738051</v>
+        <v>0.2077429654759529</v>
       </c>
       <c r="W3">
-        <v>-0.08463913988333524</v>
+        <v>0.2667757774140753</v>
       </c>
       <c r="X3">
-        <v>0.4383101057611904</v>
+        <v>0.2126523378943848</v>
       </c>
       <c r="Y3">
-        <v>-0.5229492456445257</v>
+        <v>0.05412343951969045</v>
       </c>
       <c r="Z3">
-        <v>0.1518210763376563</v>
+        <v>0.761707550175215</v>
       </c>
       <c r="AA3">
-        <v>-0.04077036576842433</v>
+        <v>0.1891228629075077</v>
       </c>
       <c r="AB3">
-        <v>0.2748585179970939</v>
+        <v>0.1822996069816401</v>
       </c>
       <c r="AC3">
-        <v>-0.3156288837655182</v>
+        <v>0.00682325592586755</v>
       </c>
       <c r="AD3">
-        <v>451</v>
+        <v>341.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>451</v>
+        <v>341.6</v>
       </c>
       <c r="AG3">
-        <v>400.2</v>
+        <v>133.4</v>
       </c>
       <c r="AH3">
-        <v>0.6219831747345194</v>
+        <v>0.2542044947164757</v>
       </c>
       <c r="AI3">
-        <v>0.3451706719730599</v>
+        <v>0.2429760295895868</v>
       </c>
       <c r="AJ3">
-        <v>0.5935043749073113</v>
+        <v>0.1174709404719972</v>
       </c>
       <c r="AK3">
-        <v>0.3186813186813187</v>
+        <v>0.1113801452784504</v>
       </c>
       <c r="AL3">
-        <v>46.5</v>
+        <v>40.6</v>
       </c>
       <c r="AM3">
-        <v>46.464</v>
+        <v>39.849</v>
       </c>
       <c r="AN3">
-        <v>-59.81432360742706</v>
+        <v>0.8567845497868072</v>
       </c>
       <c r="AO3">
-        <v>-1.129032258064516</v>
+        <v>7.70935960591133</v>
       </c>
       <c r="AP3">
-        <v>-53.07692307692307</v>
+        <v>0.3345874090795085</v>
       </c>
       <c r="AQ3">
-        <v>-1.129907024793388</v>
+        <v>7.854651308690305</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aspire Mining Limited (ASX:AKM)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-2.298624754420432</v>
+      </c>
+      <c r="H4">
+        <v>-2.298624754420432</v>
+      </c>
+      <c r="I4">
+        <v>-2.377210216110019</v>
+      </c>
+      <c r="J4">
+        <v>-2.377210216110019</v>
+      </c>
+      <c r="K4">
+        <v>-0.371</v>
+      </c>
+      <c r="L4">
+        <v>-0.7288801571709234</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>8.6</v>
+      </c>
+      <c r="V4">
+        <v>0.2356164383561644</v>
+      </c>
+      <c r="W4">
+        <v>-0.007618069815195071</v>
+      </c>
+      <c r="X4">
+        <v>0.1772574165907124</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1848754864059075</v>
+      </c>
+      <c r="Z4">
+        <v>0.01906367041198502</v>
+      </c>
+      <c r="AA4">
+        <v>-0.04531835205992508</v>
+      </c>
+      <c r="AB4">
+        <v>0.1772574165907124</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2225757686506375</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-8.6</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.3082437275985663</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2324324324324324</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
+        <v>7.350427350427351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mongolian Mining Corporation (SEHK:975)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEHK:975</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>7.70935960591133</v>
+      </c>
+      <c r="F2">
+        <v>4.62228504513074</v>
+      </c>
+      <c r="G2">
+        <v>0.856784549786807</v>
+      </c>
+      <c r="H2">
+        <v>3.33674943566591</v>
+      </c>
+      <c r="I2">
+        <v>0.254204494716476</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>1002.2</v>
+      </c>
+      <c r="L2">
+        <v>451.241845134377</v>
+      </c>
+      <c r="M2">
+        <v>1135.6</v>
+      </c>
+      <c r="N2">
+        <v>1573.40384513438</v>
+      </c>
+      <c r="O2">
+        <v>341.6</v>
+      </c>
+      <c r="P2">
+        <v>1330.362</v>
+      </c>
+      <c r="Q2">
+        <v>0.18229960698164</v>
+      </c>
+      <c r="R2">
+        <v>0.142370455984511</v>
+      </c>
+      <c r="S2">
+        <v>0.093249528173816</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.212652337894385</v>
+      </c>
+      <c r="X2">
+        <v>10.4577205984511</v>
+      </c>
+      <c r="Y2">
+        <v>1.23250223638179</v>
+      </c>
+      <c r="Z2">
+        <v>73.86350447628919</v>
+      </c>
+      <c r="AA2">
+        <v>341.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.1243327042317547</v>
+      </c>
+      <c r="AC2">
+        <v>7.70935960591133</v>
+      </c>
+      <c r="AD2">
+        <v>341.6</v>
+      </c>
+      <c r="AE2">
+        <v>40.6</v>
+      </c>
+      <c r="AF2">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>398.7</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1002.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.1410564076579343</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>184.3</v>
+      </c>
+      <c r="AR2">
+        <v>40.6</v>
+      </c>
+      <c r="AS2">
+        <v>341.6</v>
+      </c>
+      <c r="AT2">
+        <v>208.2</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1772574165907124</v>
+      </c>
+      <c r="C2">
+        <v>1385.155035713714</v>
+      </c>
+      <c r="D2">
+        <v>1176.955035713714</v>
+      </c>
+      <c r="E2">
+        <v>-341.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>208.2</v>
+      </c>
+      <c r="H2">
+        <v>1002.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>398.7</v>
+      </c>
+      <c r="K2">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L2">
+        <v>313</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>313</v>
+      </c>
+      <c r="O2">
+        <v>78.25</v>
+      </c>
+      <c r="P2">
+        <v>234.75</v>
+      </c>
+      <c r="Q2">
+        <v>320.45</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1772574165907124</v>
+      </c>
+      <c r="T2">
+        <v>0.9815748103161356</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1768585230492356</v>
+      </c>
+      <c r="C3">
+        <v>1375.117620856779</v>
+      </c>
+      <c r="D3">
+        <v>1180.35562085678</v>
+      </c>
+      <c r="E3">
+        <v>-328.162</v>
+      </c>
+      <c r="F3">
+        <v>13.438</v>
+      </c>
+      <c r="G3">
+        <v>208.2</v>
+      </c>
+      <c r="H3">
+        <v>1002.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>398.7</v>
+      </c>
+      <c r="K3">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L3">
+        <v>313</v>
+      </c>
+      <c r="M3">
+        <v>0.6006786000000002</v>
+      </c>
+      <c r="N3">
+        <v>312.3993214</v>
+      </c>
+      <c r="O3">
+        <v>78.09983035</v>
+      </c>
+      <c r="P3">
+        <v>234.29949105</v>
+      </c>
+      <c r="Q3">
+        <v>319.99949105</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1783063364133693</v>
+      </c>
+      <c r="T3">
+        <v>0.9890109831215609</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>521.0773282084627</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1764596295077588</v>
+      </c>
+      <c r="C4">
+        <v>1365.09991361428</v>
+      </c>
+      <c r="D4">
+        <v>1183.77591361428</v>
+      </c>
+      <c r="E4">
+        <v>-314.724</v>
+      </c>
+      <c r="F4">
+        <v>26.876</v>
+      </c>
+      <c r="G4">
+        <v>208.2</v>
+      </c>
+      <c r="H4">
+        <v>1002.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>398.7</v>
+      </c>
+      <c r="K4">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L4">
+        <v>313</v>
+      </c>
+      <c r="M4">
+        <v>1.2013572</v>
+      </c>
+      <c r="N4">
+        <v>311.7986428</v>
+      </c>
+      <c r="O4">
+        <v>77.9496607</v>
+      </c>
+      <c r="P4">
+        <v>233.8489821</v>
+      </c>
+      <c r="Q4">
+        <v>319.5489821</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1793766627630192</v>
+      </c>
+      <c r="T4">
+        <v>0.9965989145556683</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>260.5386641042314</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.176060735966282</v>
+      </c>
+      <c r="C5">
+        <v>1355.102085803161</v>
+      </c>
+      <c r="D5">
+        <v>1187.216085803161</v>
+      </c>
+      <c r="E5">
+        <v>-301.286</v>
+      </c>
+      <c r="F5">
+        <v>40.31400000000001</v>
+      </c>
+      <c r="G5">
+        <v>208.2</v>
+      </c>
+      <c r="H5">
+        <v>1002.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>398.7</v>
+      </c>
+      <c r="K5">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L5">
+        <v>313</v>
+      </c>
+      <c r="M5">
+        <v>1.802035800000001</v>
+      </c>
+      <c r="N5">
+        <v>311.1979642</v>
+      </c>
+      <c r="O5">
+        <v>77.79949105</v>
+      </c>
+      <c r="P5">
+        <v>233.39847315</v>
+      </c>
+      <c r="Q5">
+        <v>319.09847315</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.180469057697198</v>
+      </c>
+      <c r="T5">
+        <v>1.004343298184293</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>173.6924427361542</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1756618424248053</v>
+      </c>
+      <c r="C6">
+        <v>1345.124311243458</v>
+      </c>
+      <c r="D6">
+        <v>1190.676311243458</v>
+      </c>
+      <c r="E6">
+        <v>-287.848</v>
+      </c>
+      <c r="F6">
+        <v>53.75200000000001</v>
+      </c>
+      <c r="G6">
+        <v>208.2</v>
+      </c>
+      <c r="H6">
+        <v>1002.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>398.7</v>
+      </c>
+      <c r="K6">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L6">
+        <v>313</v>
+      </c>
+      <c r="M6">
+        <v>2.402714400000001</v>
+      </c>
+      <c r="N6">
+        <v>310.5972856</v>
+      </c>
+      <c r="O6">
+        <v>77.64932140000001</v>
+      </c>
+      <c r="P6">
+        <v>232.9479642</v>
+      </c>
+      <c r="Q6">
+        <v>318.6479642</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1815842108591721</v>
+      </c>
+      <c r="T6">
+        <v>1.012249023138515</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>130.2693320521157</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1752629488833284</v>
+      </c>
+      <c r="C7">
+        <v>1335.166765787574</v>
+      </c>
+      <c r="D7">
+        <v>1194.156765787574</v>
+      </c>
+      <c r="E7">
+        <v>-274.41</v>
+      </c>
+      <c r="F7">
+        <v>67.19000000000001</v>
+      </c>
+      <c r="G7">
+        <v>208.2</v>
+      </c>
+      <c r="H7">
+        <v>1002.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>398.7</v>
+      </c>
+      <c r="K7">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L7">
+        <v>313</v>
+      </c>
+      <c r="M7">
+        <v>3.003393000000001</v>
+      </c>
+      <c r="N7">
+        <v>309.996607</v>
+      </c>
+      <c r="O7">
+        <v>77.49915175</v>
+      </c>
+      <c r="P7">
+        <v>232.49745525</v>
+      </c>
+      <c r="Q7">
+        <v>318.19745525</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1827228409298194</v>
+      </c>
+      <c r="T7">
+        <v>1.020321184407562</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>104.2154656416925</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1748640553418517</v>
+      </c>
+      <c r="C8">
+        <v>1325.229627350069</v>
+      </c>
+      <c r="D8">
+        <v>1197.657627350069</v>
+      </c>
+      <c r="E8">
+        <v>-260.972</v>
+      </c>
+      <c r="F8">
+        <v>80.62800000000001</v>
+      </c>
+      <c r="G8">
+        <v>208.2</v>
+      </c>
+      <c r="H8">
+        <v>1002.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>398.7</v>
+      </c>
+      <c r="K8">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L8">
+        <v>313</v>
+      </c>
+      <c r="M8">
+        <v>3.604071600000001</v>
+      </c>
+      <c r="N8">
+        <v>309.3959284</v>
+      </c>
+      <c r="O8">
+        <v>77.3489821</v>
+      </c>
+      <c r="P8">
+        <v>232.0469463</v>
+      </c>
+      <c r="Q8">
+        <v>317.7469463</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1838856971721826</v>
+      </c>
+      <c r="T8">
+        <v>1.028565093788717</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>86.84622136807712</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1744651618003749</v>
+      </c>
+      <c r="C9">
+        <v>1315.313075937977</v>
+      </c>
+      <c r="D9">
+        <v>1201.179075937977</v>
+      </c>
+      <c r="E9">
+        <v>-247.534</v>
+      </c>
+      <c r="F9">
+        <v>94.06600000000002</v>
+      </c>
+      <c r="G9">
+        <v>208.2</v>
+      </c>
+      <c r="H9">
+        <v>1002.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>398.7</v>
+      </c>
+      <c r="K9">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L9">
+        <v>313</v>
+      </c>
+      <c r="M9">
+        <v>4.204750200000001</v>
+      </c>
+      <c r="N9">
+        <v>308.7952498</v>
+      </c>
+      <c r="O9">
+        <v>77.19881245000001</v>
+      </c>
+      <c r="P9">
+        <v>231.59643735</v>
+      </c>
+      <c r="Q9">
+        <v>317.29643735</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1850735610756719</v>
+      </c>
+      <c r="T9">
+        <v>1.036986291543659</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>74.43961831549468</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1740662682588981</v>
+      </c>
+      <c r="C10">
+        <v>1305.417293681663</v>
+      </c>
+      <c r="D10">
+        <v>1204.721293681662</v>
+      </c>
+      <c r="E10">
+        <v>-234.096</v>
+      </c>
+      <c r="F10">
+        <v>107.504</v>
+      </c>
+      <c r="G10">
+        <v>208.2</v>
+      </c>
+      <c r="H10">
+        <v>1002.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>398.7</v>
+      </c>
+      <c r="K10">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L10">
+        <v>313</v>
+      </c>
+      <c r="M10">
+        <v>4.805428800000001</v>
+      </c>
+      <c r="N10">
+        <v>308.1945712</v>
+      </c>
+      <c r="O10">
+        <v>77.0486428</v>
+      </c>
+      <c r="P10">
+        <v>231.1459284</v>
+      </c>
+      <c r="Q10">
+        <v>316.8459284</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.186287248107498</v>
+      </c>
+      <c r="T10">
+        <v>1.045590558815014</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>65.13466602605784</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1736673747174214</v>
+      </c>
+      <c r="C11">
+        <v>1295.542464866213</v>
+      </c>
+      <c r="D11">
+        <v>1208.284464866213</v>
+      </c>
+      <c r="E11">
+        <v>-220.658</v>
+      </c>
+      <c r="F11">
+        <v>120.942</v>
+      </c>
+      <c r="G11">
+        <v>208.2</v>
+      </c>
+      <c r="H11">
+        <v>1002.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>398.7</v>
+      </c>
+      <c r="K11">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L11">
+        <v>313</v>
+      </c>
+      <c r="M11">
+        <v>5.406107400000001</v>
+      </c>
+      <c r="N11">
+        <v>307.5938926</v>
+      </c>
+      <c r="O11">
+        <v>76.89847315</v>
+      </c>
+      <c r="P11">
+        <v>230.69541945</v>
+      </c>
+      <c r="Q11">
+        <v>316.39541945</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1875276095795839</v>
+      </c>
+      <c r="T11">
+        <v>1.054383930861563</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>57.89748091205143</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1732684811759446</v>
+      </c>
+      <c r="C12">
+        <v>1285.688775963408</v>
+      </c>
+      <c r="D12">
+        <v>1211.868775963408</v>
+      </c>
+      <c r="E12">
+        <v>-207.22</v>
+      </c>
+      <c r="F12">
+        <v>134.38</v>
+      </c>
+      <c r="G12">
+        <v>208.2</v>
+      </c>
+      <c r="H12">
+        <v>1002.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>398.7</v>
+      </c>
+      <c r="K12">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L12">
+        <v>313</v>
+      </c>
+      <c r="M12">
+        <v>6.006786000000002</v>
+      </c>
+      <c r="N12">
+        <v>306.993214</v>
+      </c>
+      <c r="O12">
+        <v>76.74830350000001</v>
+      </c>
+      <c r="P12">
+        <v>230.2449105</v>
+      </c>
+      <c r="Q12">
+        <v>315.9449105</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1887955346399384</v>
+      </c>
+      <c r="T12">
+        <v>1.063372711175814</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>52.10773282084628</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1728695876344678</v>
+      </c>
+      <c r="C13">
+        <v>1275.856415664241</v>
+      </c>
+      <c r="D13">
+        <v>1215.474415664241</v>
+      </c>
+      <c r="E13">
+        <v>-193.782</v>
+      </c>
+      <c r="F13">
+        <v>147.818</v>
+      </c>
+      <c r="G13">
+        <v>208.2</v>
+      </c>
+      <c r="H13">
+        <v>1002.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>398.7</v>
+      </c>
+      <c r="K13">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L13">
+        <v>313</v>
+      </c>
+      <c r="M13">
+        <v>6.607464600000001</v>
+      </c>
+      <c r="N13">
+        <v>306.3925354</v>
+      </c>
+      <c r="O13">
+        <v>76.59813385</v>
+      </c>
+      <c r="P13">
+        <v>229.79440155</v>
+      </c>
+      <c r="Q13">
+        <v>315.49440155</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1900919523982784</v>
+      </c>
+      <c r="T13">
+        <v>1.072563486553306</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>47.37066620076934</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.172470694092991</v>
+      </c>
+      <c r="C14">
+        <v>1266.045574912037</v>
+      </c>
+      <c r="D14">
+        <v>1219.101574912037</v>
+      </c>
+      <c r="E14">
+        <v>-180.344</v>
+      </c>
+      <c r="F14">
+        <v>161.256</v>
+      </c>
+      <c r="G14">
+        <v>208.2</v>
+      </c>
+      <c r="H14">
+        <v>1002.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>398.7</v>
+      </c>
+      <c r="K14">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L14">
+        <v>313</v>
+      </c>
+      <c r="M14">
+        <v>7.208143200000002</v>
+      </c>
+      <c r="N14">
+        <v>305.7918568</v>
+      </c>
+      <c r="O14">
+        <v>76.4479642</v>
+      </c>
+      <c r="P14">
+        <v>229.3438926</v>
+      </c>
+      <c r="Q14">
+        <v>315.0438926</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1914178341965807</v>
+      </c>
+      <c r="T14">
+        <v>1.081963143189377</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>43.42311068403856</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1720718005515142</v>
+      </c>
+      <c r="C15">
+        <v>1256.256446936158</v>
+      </c>
+      <c r="D15">
+        <v>1222.750446936158</v>
+      </c>
+      <c r="E15">
+        <v>-166.906</v>
+      </c>
+      <c r="F15">
+        <v>174.694</v>
+      </c>
+      <c r="G15">
+        <v>208.2</v>
+      </c>
+      <c r="H15">
+        <v>1002.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>398.7</v>
+      </c>
+      <c r="K15">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L15">
+        <v>313</v>
+      </c>
+      <c r="M15">
+        <v>7.808821800000001</v>
+      </c>
+      <c r="N15">
+        <v>305.1911782</v>
+      </c>
+      <c r="O15">
+        <v>76.29779455000001</v>
+      </c>
+      <c r="P15">
+        <v>228.89338365</v>
+      </c>
+      <c r="Q15">
+        <v>314.59338365</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1927741960362232</v>
+      </c>
+      <c r="T15">
+        <v>1.091578883886047</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.033525</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>40.08287140065099</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1716729070100374</v>
+      </c>
+      <c r="C16">
+        <v>1246.489227286315</v>
+      </c>
+      <c r="D16">
+        <v>1226.421227286315</v>
+      </c>
+      <c r="E16">
+        <v>-153.468</v>
+      </c>
+      <c r="F16">
+        <v>188.132</v>
+      </c>
+      <c r="G16">
+        <v>208.2</v>
+      </c>
+      <c r="H16">
+        <v>1002.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>398.7</v>
+      </c>
+      <c r="K16">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L16">
+        <v>313</v>
+      </c>
+      <c r="M16">
+        <v>8.409500400000002</v>
+      </c>
+      <c r="N16">
+        <v>304.5904996</v>
+      </c>
+      <c r="O16">
+        <v>76.1476249</v>
+      </c>
+      <c r="P16">
+        <v>228.4428747</v>
+      </c>
+      <c r="Q16">
+        <v>314.1428747</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1941621011744621</v>
+      </c>
+      <c r="T16">
+        <v>1.101418246459385</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.033525</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>37.21980915774733</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1712740134685606</v>
+      </c>
+      <c r="C17">
+        <v>1236.744113867506</v>
+      </c>
+      <c r="D17">
+        <v>1230.114113867506</v>
+      </c>
+      <c r="E17">
+        <v>-140.03</v>
+      </c>
+      <c r="F17">
+        <v>201.57</v>
+      </c>
+      <c r="G17">
+        <v>208.2</v>
+      </c>
+      <c r="H17">
+        <v>1002.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>398.7</v>
+      </c>
+      <c r="K17">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L17">
+        <v>313</v>
+      </c>
+      <c r="M17">
+        <v>9.010179000000001</v>
+      </c>
+      <c r="N17">
+        <v>303.989821</v>
+      </c>
+      <c r="O17">
+        <v>75.99745525</v>
+      </c>
+      <c r="P17">
+        <v>227.99236575</v>
+      </c>
+      <c r="Q17">
+        <v>313.69236575</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.195582662904189</v>
+      </c>
+      <c r="T17">
+        <v>1.111489123446212</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.033525</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>34.73848854723086</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1708751199270838</v>
+      </c>
+      <c r="C18">
+        <v>1227.02130697558</v>
+      </c>
+      <c r="D18">
+        <v>1233.82930697558</v>
+      </c>
+      <c r="E18">
+        <v>-126.592</v>
+      </c>
+      <c r="F18">
+        <v>215.008</v>
+      </c>
+      <c r="G18">
+        <v>208.2</v>
+      </c>
+      <c r="H18">
+        <v>1002.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>398.7</v>
+      </c>
+      <c r="K18">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L18">
+        <v>313</v>
+      </c>
+      <c r="M18">
+        <v>9.610857600000003</v>
+      </c>
+      <c r="N18">
+        <v>303.3891424</v>
+      </c>
+      <c r="O18">
+        <v>75.84728559999999</v>
+      </c>
+      <c r="P18">
+        <v>227.5418568</v>
+      </c>
+      <c r="Q18">
+        <v>313.2418567999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1970370475322427</v>
+      </c>
+      <c r="T18">
+        <v>1.121799783218441</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.033525</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>32.56733301302891</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1704762263856071</v>
+      </c>
+      <c r="C19">
+        <v>1217.321009333454</v>
+      </c>
+      <c r="D19">
+        <v>1237.567009333454</v>
+      </c>
+      <c r="E19">
+        <v>-113.154</v>
+      </c>
+      <c r="F19">
+        <v>228.4460000000001</v>
+      </c>
+      <c r="G19">
+        <v>208.2</v>
+      </c>
+      <c r="H19">
+        <v>1002.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>398.7</v>
+      </c>
+      <c r="K19">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L19">
+        <v>313</v>
+      </c>
+      <c r="M19">
+        <v>10.2115362</v>
+      </c>
+      <c r="N19">
+        <v>302.7884638</v>
+      </c>
+      <c r="O19">
+        <v>75.69711595</v>
+      </c>
+      <c r="P19">
+        <v>227.09134785</v>
+      </c>
+      <c r="Q19">
+        <v>312.79134785</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1985264775730206</v>
+      </c>
+      <c r="T19">
+        <v>1.132358892623735</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.033525</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>30.65160754167428</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1700773328441303</v>
+      </c>
+      <c r="C20">
+        <v>1207.643426127981</v>
+      </c>
+      <c r="D20">
+        <v>1241.327426127981</v>
+      </c>
+      <c r="E20">
+        <v>-99.71600000000001</v>
+      </c>
+      <c r="F20">
+        <v>241.884</v>
+      </c>
+      <c r="G20">
+        <v>208.2</v>
+      </c>
+      <c r="H20">
+        <v>1002.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>398.7</v>
+      </c>
+      <c r="K20">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L20">
+        <v>313</v>
+      </c>
+      <c r="M20">
+        <v>10.8122148</v>
+      </c>
+      <c r="N20">
+        <v>302.1877852</v>
+      </c>
+      <c r="O20">
+        <v>75.5469463</v>
+      </c>
+      <c r="P20">
+        <v>226.6408389</v>
+      </c>
+      <c r="Q20">
+        <v>312.3408389</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2000522351757687</v>
+      </c>
+      <c r="T20">
+        <v>1.143175541282816</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.033525</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>28.94874045602571</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1696784393026536</v>
+      </c>
+      <c r="C21">
+        <v>1197.988765047505</v>
+      </c>
+      <c r="D21">
+        <v>1245.110765047506</v>
+      </c>
+      <c r="E21">
+        <v>-86.27799999999999</v>
+      </c>
+      <c r="F21">
+        <v>255.322</v>
+      </c>
+      <c r="G21">
+        <v>208.2</v>
+      </c>
+      <c r="H21">
+        <v>1002.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>398.7</v>
+      </c>
+      <c r="K21">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L21">
+        <v>313</v>
+      </c>
+      <c r="M21">
+        <v>11.4128934</v>
+      </c>
+      <c r="N21">
+        <v>301.5871066</v>
+      </c>
+      <c r="O21">
+        <v>75.39677664999999</v>
+      </c>
+      <c r="P21">
+        <v>226.19032995</v>
+      </c>
+      <c r="Q21">
+        <v>311.89032995</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2016156658057451</v>
+      </c>
+      <c r="T21">
+        <v>1.154259267686567</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.033525</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>27.42512253728751</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1692795457611768</v>
+      </c>
+      <c r="C22">
+        <v>1188.357236320097</v>
+      </c>
+      <c r="D22">
+        <v>1248.917236320097</v>
+      </c>
+      <c r="E22">
+        <v>-72.83999999999997</v>
+      </c>
+      <c r="F22">
+        <v>268.76</v>
+      </c>
+      <c r="G22">
+        <v>208.2</v>
+      </c>
+      <c r="H22">
+        <v>1002.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>398.7</v>
+      </c>
+      <c r="K22">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L22">
+        <v>313</v>
+      </c>
+      <c r="M22">
+        <v>12.013572</v>
+      </c>
+      <c r="N22">
+        <v>300.986428</v>
+      </c>
+      <c r="O22">
+        <v>75.246607</v>
+      </c>
+      <c r="P22">
+        <v>225.739821</v>
+      </c>
+      <c r="Q22">
+        <v>311.439821</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2032181822014709</v>
+      </c>
+      <c r="T22">
+        <v>1.165620087250411</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.033525</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>26.05386641042314</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1688806522197</v>
+      </c>
+      <c r="C23">
+        <v>1178.749052752488</v>
+      </c>
+      <c r="D23">
+        <v>1252.747052752488</v>
+      </c>
+      <c r="E23">
+        <v>-59.40199999999999</v>
+      </c>
+      <c r="F23">
+        <v>282.198</v>
+      </c>
+      <c r="G23">
+        <v>208.2</v>
+      </c>
+      <c r="H23">
+        <v>1002.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>398.7</v>
+      </c>
+      <c r="K23">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L23">
+        <v>313</v>
+      </c>
+      <c r="M23">
+        <v>12.6142506</v>
+      </c>
+      <c r="N23">
+        <v>300.3857494</v>
+      </c>
+      <c r="O23">
+        <v>75.09643735</v>
+      </c>
+      <c r="P23">
+        <v>225.28931205</v>
+      </c>
+      <c r="Q23">
+        <v>310.98931205</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2048612686325316</v>
+      </c>
+      <c r="T23">
+        <v>1.177268522499416</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.033525</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>24.8132061051649</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1684817586782232</v>
+      </c>
+      <c r="C24">
+        <v>1169.164429769737</v>
+      </c>
+      <c r="D24">
+        <v>1256.600429769737</v>
+      </c>
+      <c r="E24">
+        <v>-45.964</v>
+      </c>
+      <c r="F24">
+        <v>295.636</v>
+      </c>
+      <c r="G24">
+        <v>208.2</v>
+      </c>
+      <c r="H24">
+        <v>1002.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>398.7</v>
+      </c>
+      <c r="K24">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L24">
+        <v>313</v>
+      </c>
+      <c r="M24">
+        <v>13.2149292</v>
+      </c>
+      <c r="N24">
+        <v>299.7850708</v>
+      </c>
+      <c r="O24">
+        <v>74.94626769999999</v>
+      </c>
+      <c r="P24">
+        <v>224.8388031</v>
+      </c>
+      <c r="Q24">
+        <v>310.5388031</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2065464854849015</v>
+      </c>
+      <c r="T24">
+        <v>1.189215635575318</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.033525</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>23.68533310038467</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1680828651367464</v>
+      </c>
+      <c r="C25">
+        <v>1159.603585455619</v>
+      </c>
+      <c r="D25">
+        <v>1260.477585455619</v>
+      </c>
+      <c r="E25">
+        <v>-32.52599999999995</v>
+      </c>
+      <c r="F25">
+        <v>309.0740000000001</v>
+      </c>
+      <c r="G25">
+        <v>208.2</v>
+      </c>
+      <c r="H25">
+        <v>1002.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>398.7</v>
+      </c>
+      <c r="K25">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L25">
+        <v>313</v>
+      </c>
+      <c r="M25">
+        <v>13.8156078</v>
+      </c>
+      <c r="N25">
+        <v>299.1843922</v>
+      </c>
+      <c r="O25">
+        <v>74.79609805</v>
+      </c>
+      <c r="P25">
+        <v>224.38829415</v>
+      </c>
+      <c r="Q25">
+        <v>310.08829415</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2082754742035667</v>
+      </c>
+      <c r="T25">
+        <v>1.201473063276568</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.033525</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>22.6555360090636</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1676839715952697</v>
+      </c>
+      <c r="C26">
+        <v>1150.066740593772</v>
+      </c>
+      <c r="D26">
+        <v>1264.378740593772</v>
+      </c>
+      <c r="E26">
+        <v>-19.08799999999997</v>
+      </c>
+      <c r="F26">
+        <v>322.5120000000001</v>
+      </c>
+      <c r="G26">
+        <v>208.2</v>
+      </c>
+      <c r="H26">
+        <v>1002.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>398.7</v>
+      </c>
+      <c r="K26">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L26">
+        <v>313</v>
+      </c>
+      <c r="M26">
+        <v>14.4162864</v>
+      </c>
+      <c r="N26">
+        <v>298.5837136</v>
+      </c>
+      <c r="O26">
+        <v>74.6459284</v>
+      </c>
+      <c r="P26">
+        <v>223.9377852</v>
+      </c>
+      <c r="Q26">
+        <v>309.6377852</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2100499626253548</v>
+      </c>
+      <c r="T26">
+        <v>1.214053054864694</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.033525</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>21.71155534201928</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1672850780537929</v>
+      </c>
+      <c r="C27">
+        <v>1140.554118709605</v>
+      </c>
+      <c r="D27">
+        <v>1268.304118709605</v>
+      </c>
+      <c r="E27">
+        <v>-5.649999999999977</v>
+      </c>
+      <c r="F27">
+        <v>335.95</v>
+      </c>
+      <c r="G27">
+        <v>208.2</v>
+      </c>
+      <c r="H27">
+        <v>1002.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>398.7</v>
+      </c>
+      <c r="K27">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L27">
+        <v>313</v>
+      </c>
+      <c r="M27">
+        <v>15.016965</v>
+      </c>
+      <c r="N27">
+        <v>297.983035</v>
+      </c>
+      <c r="O27">
+        <v>74.49575874999999</v>
+      </c>
+      <c r="P27">
+        <v>223.48727625</v>
+      </c>
+      <c r="Q27">
+        <v>309.18727625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2118717707383905</v>
+      </c>
+      <c r="T27">
+        <v>1.22696851289517</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.033525</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>20.84309312833851</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1668861845123161</v>
+      </c>
+      <c r="C28">
+        <v>1131.065946112989</v>
+      </c>
+      <c r="D28">
+        <v>1272.253946112989</v>
+      </c>
+      <c r="E28">
+        <v>7.788000000000011</v>
+      </c>
+      <c r="F28">
+        <v>349.388</v>
+      </c>
+      <c r="G28">
+        <v>208.2</v>
+      </c>
+      <c r="H28">
+        <v>1002.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>398.7</v>
+      </c>
+      <c r="K28">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L28">
+        <v>313</v>
+      </c>
+      <c r="M28">
+        <v>15.6176436</v>
+      </c>
+      <c r="N28">
+        <v>297.3823564</v>
+      </c>
+      <c r="O28">
+        <v>74.3455891</v>
+      </c>
+      <c r="P28">
+        <v>223.0367673</v>
+      </c>
+      <c r="Q28">
+        <v>308.7367673</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2137428169085352</v>
+      </c>
+      <c r="T28">
+        <v>1.240233037358901</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.033525</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>20.04143570032549</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1664872909708393</v>
+      </c>
+      <c r="C29">
+        <v>1121.602451941754</v>
+      </c>
+      <c r="D29">
+        <v>1276.228451941754</v>
+      </c>
+      <c r="E29">
+        <v>21.22600000000006</v>
+      </c>
+      <c r="F29">
+        <v>362.8260000000001</v>
+      </c>
+      <c r="G29">
+        <v>208.2</v>
+      </c>
+      <c r="H29">
+        <v>1002.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>398.7</v>
+      </c>
+      <c r="K29">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L29">
+        <v>313</v>
+      </c>
+      <c r="M29">
+        <v>16.21832220000001</v>
+      </c>
+      <c r="N29">
+        <v>296.7816778</v>
+      </c>
+      <c r="O29">
+        <v>74.19541945</v>
+      </c>
+      <c r="P29">
+        <v>222.58625835</v>
+      </c>
+      <c r="Q29">
+        <v>308.28625835</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2156651246175881</v>
+      </c>
+      <c r="T29">
+        <v>1.253860973451776</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.033525</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>19.29916030401714</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1660883974293625</v>
+      </c>
+      <c r="C30">
+        <v>1112.163868205997</v>
+      </c>
+      <c r="D30">
+        <v>1280.227868205998</v>
+      </c>
+      <c r="E30">
+        <v>34.66400000000004</v>
+      </c>
+      <c r="F30">
+        <v>376.2640000000001</v>
+      </c>
+      <c r="G30">
+        <v>208.2</v>
+      </c>
+      <c r="H30">
+        <v>1002.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>398.7</v>
+      </c>
+      <c r="K30">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L30">
+        <v>313</v>
+      </c>
+      <c r="M30">
+        <v>16.8190008</v>
+      </c>
+      <c r="N30">
+        <v>296.1809992</v>
+      </c>
+      <c r="O30">
+        <v>74.04524979999999</v>
+      </c>
+      <c r="P30">
+        <v>222.1357494</v>
+      </c>
+      <c r="Q30">
+        <v>307.8357493999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2176408297630035</v>
+      </c>
+      <c r="T30">
+        <v>1.267867463325008</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.033525</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>18.60990457887367</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1656895038878857</v>
+      </c>
+      <c r="C31">
+        <v>1102.750429833232</v>
+      </c>
+      <c r="D31">
+        <v>1284.252429833232</v>
+      </c>
+      <c r="E31">
+        <v>48.10199999999998</v>
+      </c>
+      <c r="F31">
+        <v>389.702</v>
+      </c>
+      <c r="G31">
+        <v>208.2</v>
+      </c>
+      <c r="H31">
+        <v>1002.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>398.7</v>
+      </c>
+      <c r="K31">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L31">
+        <v>313</v>
+      </c>
+      <c r="M31">
+        <v>17.4196794</v>
+      </c>
+      <c r="N31">
+        <v>295.5803206</v>
+      </c>
+      <c r="O31">
+        <v>73.89508015</v>
+      </c>
+      <c r="P31">
+        <v>221.68524045</v>
+      </c>
+      <c r="Q31">
+        <v>307.38524045</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2196721885744869</v>
+      </c>
+      <c r="T31">
+        <v>1.282268502208755</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.033525</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>17.96818373132631</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1652906103464089</v>
+      </c>
+      <c r="C32">
+        <v>1093.362374714384</v>
+      </c>
+      <c r="D32">
+        <v>1288.302374714384</v>
+      </c>
+      <c r="E32">
+        <v>61.54000000000002</v>
+      </c>
+      <c r="F32">
+        <v>403.14</v>
+      </c>
+      <c r="G32">
+        <v>208.2</v>
+      </c>
+      <c r="H32">
+        <v>1002.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>398.7</v>
+      </c>
+      <c r="K32">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L32">
+        <v>313</v>
+      </c>
+      <c r="M32">
+        <v>18.020358</v>
+      </c>
+      <c r="N32">
+        <v>294.979642</v>
+      </c>
+      <c r="O32">
+        <v>73.7449105</v>
+      </c>
+      <c r="P32">
+        <v>221.2347315</v>
+      </c>
+      <c r="Q32">
+        <v>306.9347315</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2217615862091556</v>
+      </c>
+      <c r="T32">
+        <v>1.297080999346322</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.033525</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>17.36924427361543</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1648917168049321</v>
+      </c>
+      <c r="C33">
+        <v>1083.999943750674</v>
+      </c>
+      <c r="D33">
+        <v>1292.377943750674</v>
+      </c>
+      <c r="E33">
+        <v>74.97800000000001</v>
+      </c>
+      <c r="F33">
+        <v>416.578</v>
+      </c>
+      <c r="G33">
+        <v>208.2</v>
+      </c>
+      <c r="H33">
+        <v>1002.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>398.7</v>
+      </c>
+      <c r="K33">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L33">
+        <v>313</v>
+      </c>
+      <c r="M33">
+        <v>18.6210366</v>
+      </c>
+      <c r="N33">
+        <v>294.3789634</v>
+      </c>
+      <c r="O33">
+        <v>73.59474084999999</v>
+      </c>
+      <c r="P33">
+        <v>220.78422255</v>
+      </c>
+      <c r="Q33">
+        <v>306.48422255</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2239115460941046</v>
+      </c>
+      <c r="T33">
+        <v>1.312322844227007</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.033525</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>16.80894607124073</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1644928232634554</v>
+      </c>
+      <c r="C34">
+        <v>1074.663380901375</v>
+      </c>
+      <c r="D34">
+        <v>1296.479380901375</v>
+      </c>
+      <c r="E34">
+        <v>88.41600000000005</v>
+      </c>
+      <c r="F34">
+        <v>430.0160000000001</v>
+      </c>
+      <c r="G34">
+        <v>208.2</v>
+      </c>
+      <c r="H34">
+        <v>1002.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>398.7</v>
+      </c>
+      <c r="K34">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L34">
+        <v>313</v>
+      </c>
+      <c r="M34">
+        <v>19.22171520000001</v>
+      </c>
+      <c r="N34">
+        <v>293.7782848</v>
+      </c>
+      <c r="O34">
+        <v>73.4445712</v>
+      </c>
+      <c r="P34">
+        <v>220.3337136</v>
+      </c>
+      <c r="Q34">
+        <v>306.0337136</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2261247400933167</v>
+      </c>
+      <c r="T34">
+        <v>1.328012978663007</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.033525</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>16.28366650651446</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1640939297219786</v>
+      </c>
+      <c r="C35">
+        <v>1065.352933232497</v>
+      </c>
+      <c r="D35">
+        <v>1300.606933232497</v>
+      </c>
+      <c r="E35">
+        <v>101.854</v>
+      </c>
+      <c r="F35">
+        <v>443.4540000000001</v>
+      </c>
+      <c r="G35">
+        <v>208.2</v>
+      </c>
+      <c r="H35">
+        <v>1002.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>398.7</v>
+      </c>
+      <c r="K35">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L35">
+        <v>313</v>
+      </c>
+      <c r="M35">
+        <v>19.8223938</v>
+      </c>
+      <c r="N35">
+        <v>293.1776062</v>
+      </c>
+      <c r="O35">
+        <v>73.29440155</v>
+      </c>
+      <c r="P35">
+        <v>219.88320465</v>
+      </c>
+      <c r="Q35">
+        <v>305.58320465</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2284039995850427</v>
+      </c>
+      <c r="T35">
+        <v>1.344171475320977</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.033525</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>15.79022206692312</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1636950361805018</v>
+      </c>
+      <c r="C36">
+        <v>1056.068850966397</v>
+      </c>
+      <c r="D36">
+        <v>1304.760850966397</v>
+      </c>
+      <c r="E36">
+        <v>115.2920000000001</v>
+      </c>
+      <c r="F36">
+        <v>456.8920000000001</v>
+      </c>
+      <c r="G36">
+        <v>208.2</v>
+      </c>
+      <c r="H36">
+        <v>1002.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>398.7</v>
+      </c>
+      <c r="K36">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L36">
+        <v>313</v>
+      </c>
+      <c r="M36">
+        <v>20.42307240000001</v>
+      </c>
+      <c r="N36">
+        <v>292.5769276</v>
+      </c>
+      <c r="O36">
+        <v>73.14423189999999</v>
+      </c>
+      <c r="P36">
+        <v>219.4326957</v>
+      </c>
+      <c r="Q36">
+        <v>305.1326957</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2307523275462149</v>
+      </c>
+      <c r="T36">
+        <v>1.360819623392824</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.033525</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>15.32580377083714</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.163296142639025</v>
+      </c>
+      <c r="C37">
+        <v>1046.811387532348</v>
+      </c>
+      <c r="D37">
+        <v>1308.941387532348</v>
+      </c>
+      <c r="E37">
+        <v>128.7300000000001</v>
+      </c>
+      <c r="F37">
+        <v>470.3300000000001</v>
+      </c>
+      <c r="G37">
+        <v>208.2</v>
+      </c>
+      <c r="H37">
+        <v>1002.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>398.7</v>
+      </c>
+      <c r="K37">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L37">
+        <v>313</v>
+      </c>
+      <c r="M37">
+        <v>21.023751</v>
+      </c>
+      <c r="N37">
+        <v>291.976249</v>
+      </c>
+      <c r="O37">
+        <v>72.99406225</v>
+      </c>
+      <c r="P37">
+        <v>218.98218675</v>
+      </c>
+      <c r="Q37">
+        <v>304.68218675</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2331729117523462</v>
+      </c>
+      <c r="T37">
+        <v>1.377980022174575</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.033525</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>14.88792366309894</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1628972490975482</v>
+      </c>
+      <c r="C38">
+        <v>1037.580799618073</v>
+      </c>
+      <c r="D38">
+        <v>1313.148799618073</v>
+      </c>
+      <c r="E38">
+        <v>142.168</v>
+      </c>
+      <c r="F38">
+        <v>483.768</v>
+      </c>
+      <c r="G38">
+        <v>208.2</v>
+      </c>
+      <c r="H38">
+        <v>1002.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>398.7</v>
+      </c>
+      <c r="K38">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L38">
+        <v>313</v>
+      </c>
+      <c r="M38">
+        <v>21.6244296</v>
+      </c>
+      <c r="N38">
+        <v>291.3755704</v>
+      </c>
+      <c r="O38">
+        <v>72.8438926</v>
+      </c>
+      <c r="P38">
+        <v>218.5316778</v>
+      </c>
+      <c r="Q38">
+        <v>304.2316778</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2356691392149191</v>
+      </c>
+      <c r="T38">
+        <v>1.395676683418255</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.033525</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>14.47437022801286</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1624983555560715</v>
+      </c>
+      <c r="C39">
+        <v>1028.377347222291</v>
+      </c>
+      <c r="D39">
+        <v>1317.383347222291</v>
+      </c>
+      <c r="E39">
+        <v>155.6060000000001</v>
+      </c>
+      <c r="F39">
+        <v>497.2060000000001</v>
+      </c>
+      <c r="G39">
+        <v>208.2</v>
+      </c>
+      <c r="H39">
+        <v>1002.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>398.7</v>
+      </c>
+      <c r="K39">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L39">
+        <v>313</v>
+      </c>
+      <c r="M39">
+        <v>22.2251082</v>
+      </c>
+      <c r="N39">
+        <v>290.7748918</v>
+      </c>
+      <c r="O39">
+        <v>72.69372294999999</v>
+      </c>
+      <c r="P39">
+        <v>218.08116885</v>
+      </c>
+      <c r="Q39">
+        <v>303.78116885</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2382446119937643</v>
+      </c>
+      <c r="T39">
+        <v>1.413935143431576</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.033525</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>14.08317103266116</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1620994620145947</v>
+      </c>
+      <c r="C40">
+        <v>1019.201293708269</v>
+      </c>
+      <c r="D40">
+        <v>1321.645293708269</v>
+      </c>
+      <c r="E40">
+        <v>169.044</v>
+      </c>
+      <c r="F40">
+        <v>510.6440000000001</v>
+      </c>
+      <c r="G40">
+        <v>208.2</v>
+      </c>
+      <c r="H40">
+        <v>1002.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>398.7</v>
+      </c>
+      <c r="K40">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L40">
+        <v>313</v>
+      </c>
+      <c r="M40">
+        <v>22.8257868</v>
+      </c>
+      <c r="N40">
+        <v>290.1742132</v>
+      </c>
+      <c r="O40">
+        <v>72.5435533</v>
+      </c>
+      <c r="P40">
+        <v>217.6306599</v>
+      </c>
+      <c r="Q40">
+        <v>303.3306599</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2409031645396689</v>
+      </c>
+      <c r="T40">
+        <v>1.432782586025972</v>
+      </c>
+      <c r="U40">
+        <v>0.0447</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.033525</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>13.71256126864376</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1617005684731179</v>
+      </c>
+      <c r="C41">
+        <v>1010.052905858425</v>
+      </c>
+      <c r="D41">
+        <v>1325.934905858425</v>
+      </c>
+      <c r="E41">
+        <v>182.4820000000001</v>
+      </c>
+      <c r="F41">
+        <v>524.0820000000001</v>
+      </c>
+      <c r="G41">
+        <v>208.2</v>
+      </c>
+      <c r="H41">
+        <v>1002.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>398.7</v>
+      </c>
+      <c r="K41">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L41">
+        <v>313</v>
+      </c>
+      <c r="M41">
+        <v>23.4264654</v>
+      </c>
+      <c r="N41">
+        <v>289.5735346</v>
+      </c>
+      <c r="O41">
+        <v>72.39338365</v>
+      </c>
+      <c r="P41">
+        <v>217.18015095</v>
+      </c>
+      <c r="Q41">
+        <v>302.88015095</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2436488827428163</v>
+      </c>
+      <c r="T41">
+        <v>1.452247977557889</v>
+      </c>
+      <c r="U41">
+        <v>0.0447</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.033525</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>13.36095713355033</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1613016749316411</v>
+      </c>
+      <c r="C42">
+        <v>1000.932453929998</v>
+      </c>
+      <c r="D42">
+        <v>1330.252453929998</v>
+      </c>
+      <c r="E42">
+        <v>195.9200000000001</v>
+      </c>
+      <c r="F42">
+        <v>537.5200000000001</v>
+      </c>
+      <c r="G42">
+        <v>208.2</v>
+      </c>
+      <c r="H42">
+        <v>1002.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>398.7</v>
+      </c>
+      <c r="K42">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L42">
+        <v>313</v>
+      </c>
+      <c r="M42">
+        <v>24.02714400000001</v>
+      </c>
+      <c r="N42">
+        <v>288.972856</v>
+      </c>
+      <c r="O42">
+        <v>72.24321399999999</v>
+      </c>
+      <c r="P42">
+        <v>216.729642</v>
+      </c>
+      <c r="Q42">
+        <v>302.4296419999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2464861248860686</v>
+      </c>
+      <c r="T42">
+        <v>1.472362215474203</v>
+      </c>
+      <c r="U42">
+        <v>0.0447</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.033525</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>13.02693320521157</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1612410313901644</v>
+      </c>
+      <c r="C43">
+        <v>988.1533116588864</v>
+      </c>
+      <c r="D43">
+        <v>1330.911311658886</v>
+      </c>
+      <c r="E43">
+        <v>209.3580000000001</v>
+      </c>
+      <c r="F43">
+        <v>550.9580000000001</v>
+      </c>
+      <c r="G43">
+        <v>208.2</v>
+      </c>
+      <c r="H43">
+        <v>1002.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>398.7</v>
+      </c>
+      <c r="K43">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L43">
+        <v>313</v>
+      </c>
+      <c r="M43">
+        <v>25.2338764</v>
+      </c>
+      <c r="N43">
+        <v>287.7661236</v>
+      </c>
+      <c r="O43">
+        <v>71.9415309</v>
+      </c>
+      <c r="P43">
+        <v>215.8245927</v>
+      </c>
+      <c r="Q43">
+        <v>301.5245927</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2494195447290921</v>
+      </c>
+      <c r="T43">
+        <v>1.493158291963952</v>
+      </c>
+      <c r="U43">
+        <v>0.0458</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.03435</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>12.40396025717238</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1608503878486876</v>
+      </c>
+      <c r="C44">
+        <v>978.9751253091509</v>
+      </c>
+      <c r="D44">
+        <v>1335.171125309151</v>
+      </c>
+      <c r="E44">
+        <v>222.796</v>
+      </c>
+      <c r="F44">
+        <v>564.3960000000001</v>
+      </c>
+      <c r="G44">
+        <v>208.2</v>
+      </c>
+      <c r="H44">
+        <v>1002.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>398.7</v>
+      </c>
+      <c r="K44">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L44">
+        <v>313</v>
+      </c>
+      <c r="M44">
+        <v>25.8493368</v>
+      </c>
+      <c r="N44">
+        <v>287.1506632</v>
+      </c>
+      <c r="O44">
+        <v>71.7876658</v>
+      </c>
+      <c r="P44">
+        <v>215.3629974</v>
+      </c>
+      <c r="Q44">
+        <v>301.0629974</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2524541169804958</v>
+      </c>
+      <c r="T44">
+        <v>1.514671474539554</v>
+      </c>
+      <c r="U44">
+        <v>0.0458</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.03435</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>12.10862787009684</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1604597443072108</v>
+      </c>
+      <c r="C45">
+        <v>969.8242950696861</v>
+      </c>
+      <c r="D45">
+        <v>1339.458295069686</v>
+      </c>
+      <c r="E45">
+        <v>236.234</v>
+      </c>
+      <c r="F45">
+        <v>577.8340000000001</v>
+      </c>
+      <c r="G45">
+        <v>208.2</v>
+      </c>
+      <c r="H45">
+        <v>1002.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>398.7</v>
+      </c>
+      <c r="K45">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L45">
+        <v>313</v>
+      </c>
+      <c r="M45">
+        <v>26.4647972</v>
+      </c>
+      <c r="N45">
+        <v>286.5352028</v>
+      </c>
+      <c r="O45">
+        <v>71.63380069999999</v>
+      </c>
+      <c r="P45">
+        <v>214.9014021</v>
+      </c>
+      <c r="Q45">
+        <v>300.6014021</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.255595165451247</v>
+      </c>
+      <c r="T45">
+        <v>1.536939505626581</v>
+      </c>
+      <c r="U45">
+        <v>0.0458</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.03435</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>11.82703187311785</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.160069100765734</v>
+      </c>
+      <c r="C46">
+        <v>960.701085306791</v>
+      </c>
+      <c r="D46">
+        <v>1343.773085306791</v>
+      </c>
+      <c r="E46">
+        <v>249.672</v>
+      </c>
+      <c r="F46">
+        <v>591.272</v>
+      </c>
+      <c r="G46">
+        <v>208.2</v>
+      </c>
+      <c r="H46">
+        <v>1002.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>398.7</v>
+      </c>
+      <c r="K46">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L46">
+        <v>313</v>
+      </c>
+      <c r="M46">
+        <v>27.0802576</v>
+      </c>
+      <c r="N46">
+        <v>285.9197424</v>
+      </c>
+      <c r="O46">
+        <v>71.4799356</v>
+      </c>
+      <c r="P46">
+        <v>214.4398068</v>
+      </c>
+      <c r="Q46">
+        <v>300.1398068</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.258848394224525</v>
+      </c>
+      <c r="T46">
+        <v>1.560002823538144</v>
+      </c>
+      <c r="U46">
+        <v>0.0458</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.03435</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>11.55823569418335</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1596784572242572</v>
+      </c>
+      <c r="C47">
+        <v>951.6057638041808</v>
+      </c>
+      <c r="D47">
+        <v>1348.115763804181</v>
+      </c>
+      <c r="E47">
+        <v>263.1100000000001</v>
+      </c>
+      <c r="F47">
+        <v>604.7100000000002</v>
+      </c>
+      <c r="G47">
+        <v>208.2</v>
+      </c>
+      <c r="H47">
+        <v>1002.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>398.7</v>
+      </c>
+      <c r="K47">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L47">
+        <v>313</v>
+      </c>
+      <c r="M47">
+        <v>27.69571800000001</v>
+      </c>
+      <c r="N47">
+        <v>285.304282</v>
+      </c>
+      <c r="O47">
+        <v>71.3260705</v>
+      </c>
+      <c r="P47">
+        <v>213.9782115</v>
+      </c>
+      <c r="Q47">
+        <v>299.6782115</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2622199222259222</v>
+      </c>
+      <c r="T47">
+        <v>1.583904807555582</v>
+      </c>
+      <c r="U47">
+        <v>0.0458</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.03435</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>11.30138601209039</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1592878136827805</v>
+      </c>
+      <c r="C48">
+        <v>942.5386018183854</v>
+      </c>
+      <c r="D48">
+        <v>1352.486601818385</v>
+      </c>
+      <c r="E48">
+        <v>276.5480000000001</v>
+      </c>
+      <c r="F48">
+        <v>618.1480000000001</v>
+      </c>
+      <c r="G48">
+        <v>208.2</v>
+      </c>
+      <c r="H48">
+        <v>1002.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>398.7</v>
+      </c>
+      <c r="K48">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L48">
+        <v>313</v>
+      </c>
+      <c r="M48">
+        <v>28.31117840000001</v>
+      </c>
+      <c r="N48">
+        <v>284.6888216</v>
+      </c>
+      <c r="O48">
+        <v>71.1722054</v>
+      </c>
+      <c r="P48">
+        <v>213.5166162</v>
+      </c>
+      <c r="Q48">
+        <v>299.2166162</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2657163216347786</v>
+      </c>
+      <c r="T48">
+        <v>1.608692050240333</v>
+      </c>
+      <c r="U48">
+        <v>0.0458</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.03435</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>11.05570370747973</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1588971701413037</v>
+      </c>
+      <c r="C49">
+        <v>933.4998741352321</v>
+      </c>
+      <c r="D49">
+        <v>1356.885874135232</v>
+      </c>
+      <c r="E49">
+        <v>289.9860000000001</v>
+      </c>
+      <c r="F49">
+        <v>631.5860000000001</v>
+      </c>
+      <c r="G49">
+        <v>208.2</v>
+      </c>
+      <c r="H49">
+        <v>1002.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>398.7</v>
+      </c>
+      <c r="K49">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L49">
+        <v>313</v>
+      </c>
+      <c r="M49">
+        <v>28.92663880000001</v>
+      </c>
+      <c r="N49">
+        <v>284.0733612</v>
+      </c>
+      <c r="O49">
+        <v>71.01834030000001</v>
+      </c>
+      <c r="P49">
+        <v>213.0550209</v>
+      </c>
+      <c r="Q49">
+        <v>298.7550209</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2693446606439692</v>
+      </c>
+      <c r="T49">
+        <v>1.634414660573565</v>
+      </c>
+      <c r="U49">
+        <v>0.0458</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.03435</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>10.82047596902271</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1585065265998269</v>
+      </c>
+      <c r="C50">
+        <v>924.4898591274284</v>
+      </c>
+      <c r="D50">
+        <v>1361.313859127428</v>
+      </c>
+      <c r="E50">
+        <v>303.4240000000001</v>
+      </c>
+      <c r="F50">
+        <v>645.0240000000001</v>
+      </c>
+      <c r="G50">
+        <v>208.2</v>
+      </c>
+      <c r="H50">
+        <v>1002.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>398.7</v>
+      </c>
+      <c r="K50">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L50">
+        <v>313</v>
+      </c>
+      <c r="M50">
+        <v>29.54209920000001</v>
+      </c>
+      <c r="N50">
+        <v>283.4579008</v>
+      </c>
+      <c r="O50">
+        <v>70.8644752</v>
+      </c>
+      <c r="P50">
+        <v>212.5934256</v>
+      </c>
+      <c r="Q50">
+        <v>298.2934256</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2731125511535132</v>
+      </c>
+      <c r="T50">
+        <v>1.66112660207346</v>
+      </c>
+      <c r="U50">
+        <v>0.0458</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.03435</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>10.59504938633474</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1581158830583501</v>
+      </c>
+      <c r="C51">
+        <v>915.5088388132839</v>
+      </c>
+      <c r="D51">
+        <v>1365.770838813284</v>
+      </c>
+      <c r="E51">
+        <v>316.8620000000001</v>
+      </c>
+      <c r="F51">
+        <v>658.4620000000001</v>
+      </c>
+      <c r="G51">
+        <v>208.2</v>
+      </c>
+      <c r="H51">
+        <v>1002.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>398.7</v>
+      </c>
+      <c r="K51">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L51">
+        <v>313</v>
+      </c>
+      <c r="M51">
+        <v>30.15755960000001</v>
+      </c>
+      <c r="N51">
+        <v>282.8424404</v>
+      </c>
+      <c r="O51">
+        <v>70.7106101</v>
+      </c>
+      <c r="P51">
+        <v>212.1318303</v>
+      </c>
+      <c r="Q51">
+        <v>297.8318303</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2770282020751963</v>
+      </c>
+      <c r="T51">
+        <v>1.688886070690998</v>
+      </c>
+      <c r="U51">
+        <v>0.0458</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.03435</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>10.37882388865444</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1577252395168733</v>
+      </c>
+      <c r="C52">
+        <v>906.5570989165819</v>
+      </c>
+      <c r="D52">
+        <v>1370.257098916582</v>
+      </c>
+      <c r="E52">
+        <v>330.3000000000001</v>
+      </c>
+      <c r="F52">
+        <v>671.9000000000001</v>
+      </c>
+      <c r="G52">
+        <v>208.2</v>
+      </c>
+      <c r="H52">
+        <v>1002.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>398.7</v>
+      </c>
+      <c r="K52">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L52">
+        <v>313</v>
+      </c>
+      <c r="M52">
+        <v>30.77302000000001</v>
+      </c>
+      <c r="N52">
+        <v>282.22698</v>
+      </c>
+      <c r="O52">
+        <v>70.55674499999999</v>
+      </c>
+      <c r="P52">
+        <v>211.670235</v>
+      </c>
+      <c r="Q52">
+        <v>297.370235</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2811004790337467</v>
+      </c>
+      <c r="T52">
+        <v>1.717755918053237</v>
+      </c>
+      <c r="U52">
+        <v>0.0458</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.03435</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>10.17124741088135</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1573345959753965</v>
+      </c>
+      <c r="C53">
+        <v>897.6349289276415</v>
+      </c>
+      <c r="D53">
+        <v>1374.772928927641</v>
+      </c>
+      <c r="E53">
+        <v>343.7380000000001</v>
+      </c>
+      <c r="F53">
+        <v>685.3380000000001</v>
+      </c>
+      <c r="G53">
+        <v>208.2</v>
+      </c>
+      <c r="H53">
+        <v>1002.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>398.7</v>
+      </c>
+      <c r="K53">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L53">
+        <v>313</v>
+      </c>
+      <c r="M53">
+        <v>31.3884804</v>
+      </c>
+      <c r="N53">
+        <v>281.6115196</v>
+      </c>
+      <c r="O53">
+        <v>70.4028799</v>
+      </c>
+      <c r="P53">
+        <v>211.2086397</v>
+      </c>
+      <c r="Q53">
+        <v>296.9086397</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2853389713783603</v>
+      </c>
+      <c r="T53">
+        <v>1.747804126532303</v>
+      </c>
+      <c r="U53">
+        <v>0.0458</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.03435</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>9.971811187138577</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1578019524339198</v>
+      </c>
+      <c r="C54">
+        <v>878.7977821557095</v>
+      </c>
+      <c r="D54">
+        <v>1369.373782155709</v>
+      </c>
+      <c r="E54">
+        <v>357.176</v>
+      </c>
+      <c r="F54">
+        <v>698.7760000000001</v>
+      </c>
+      <c r="G54">
+        <v>208.2</v>
+      </c>
+      <c r="H54">
+        <v>1002.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>398.7</v>
+      </c>
+      <c r="K54">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L54">
+        <v>313</v>
+      </c>
+      <c r="M54">
+        <v>33.541248</v>
+      </c>
+      <c r="N54">
+        <v>279.458752</v>
+      </c>
+      <c r="O54">
+        <v>69.864688</v>
+      </c>
+      <c r="P54">
+        <v>209.594064</v>
+      </c>
+      <c r="Q54">
+        <v>295.294064</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2897540675706661</v>
+      </c>
+      <c r="T54">
+        <v>1.779104343697996</v>
+      </c>
+      <c r="U54">
+        <v>0.048</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.036</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>9.331793497964059</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.157427808892443</v>
+      </c>
+      <c r="C55">
+        <v>869.6786881630323</v>
+      </c>
+      <c r="D55">
+        <v>1373.692688163032</v>
+      </c>
+      <c r="E55">
+        <v>370.6140000000001</v>
+      </c>
+      <c r="F55">
+        <v>712.2140000000002</v>
+      </c>
+      <c r="G55">
+        <v>208.2</v>
+      </c>
+      <c r="H55">
+        <v>1002.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>398.7</v>
+      </c>
+      <c r="K55">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L55">
+        <v>313</v>
+      </c>
+      <c r="M55">
+        <v>34.18627200000001</v>
+      </c>
+      <c r="N55">
+        <v>278.813728</v>
+      </c>
+      <c r="O55">
+        <v>69.70343199999999</v>
+      </c>
+      <c r="P55">
+        <v>209.110296</v>
+      </c>
+      <c r="Q55">
+        <v>294.810296</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2943570401966872</v>
+      </c>
+      <c r="T55">
+        <v>1.811736484998399</v>
+      </c>
+      <c r="U55">
+        <v>0.048</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.036</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>9.155721922530772</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1570536653509662</v>
+      </c>
+      <c r="C56">
+        <v>860.5869234000096</v>
+      </c>
+      <c r="D56">
+        <v>1378.03892340001</v>
+      </c>
+      <c r="E56">
+        <v>384.0520000000001</v>
+      </c>
+      <c r="F56">
+        <v>725.6520000000002</v>
+      </c>
+      <c r="G56">
+        <v>208.2</v>
+      </c>
+      <c r="H56">
+        <v>1002.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>398.7</v>
+      </c>
+      <c r="K56">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L56">
+        <v>313</v>
+      </c>
+      <c r="M56">
+        <v>34.83129600000001</v>
+      </c>
+      <c r="N56">
+        <v>278.168704</v>
+      </c>
+      <c r="O56">
+        <v>69.542176</v>
+      </c>
+      <c r="P56">
+        <v>208.626528</v>
+      </c>
+      <c r="Q56">
+        <v>294.326528</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2991601420673178</v>
+      </c>
+      <c r="T56">
+        <v>1.845787415050994</v>
+      </c>
+      <c r="U56">
+        <v>0.048</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.036</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>8.986171516557981</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1566795218094894</v>
+      </c>
+      <c r="C57">
+        <v>851.52274809135</v>
+      </c>
+      <c r="D57">
+        <v>1382.41274809135</v>
+      </c>
+      <c r="E57">
+        <v>397.4900000000001</v>
+      </c>
+      <c r="F57">
+        <v>739.0900000000001</v>
+      </c>
+      <c r="G57">
+        <v>208.2</v>
+      </c>
+      <c r="H57">
+        <v>1002.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>398.7</v>
+      </c>
+      <c r="K57">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L57">
+        <v>313</v>
+      </c>
+      <c r="M57">
+        <v>35.47632000000001</v>
+      </c>
+      <c r="N57">
+        <v>277.52368</v>
+      </c>
+      <c r="O57">
+        <v>69.38092</v>
+      </c>
+      <c r="P57">
+        <v>208.14276</v>
+      </c>
+      <c r="Q57">
+        <v>293.84276</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3041767151321987</v>
+      </c>
+      <c r="T57">
+        <v>1.881351719772594</v>
+      </c>
+      <c r="U57">
+        <v>0.048</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.036</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.82278657989329</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1563053782680126</v>
+      </c>
+      <c r="C58">
+        <v>842.4864257760415</v>
+      </c>
+      <c r="D58">
+        <v>1386.814425776042</v>
+      </c>
+      <c r="E58">
+        <v>410.9280000000001</v>
+      </c>
+      <c r="F58">
+        <v>752.5280000000001</v>
+      </c>
+      <c r="G58">
+        <v>208.2</v>
+      </c>
+      <c r="H58">
+        <v>1002.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>398.7</v>
+      </c>
+      <c r="K58">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L58">
+        <v>313</v>
+      </c>
+      <c r="M58">
+        <v>36.12134400000001</v>
+      </c>
+      <c r="N58">
+        <v>276.878656</v>
+      </c>
+      <c r="O58">
+        <v>69.21966399999999</v>
+      </c>
+      <c r="P58">
+        <v>207.658992</v>
+      </c>
+      <c r="Q58">
+        <v>293.3589919999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3094213142454832</v>
+      </c>
+      <c r="T58">
+        <v>1.91853258379972</v>
+      </c>
+      <c r="U58">
+        <v>0.048</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.036</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.665236819538052</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1559312347265359</v>
+      </c>
+      <c r="C59">
+        <v>833.478223360284</v>
+      </c>
+      <c r="D59">
+        <v>1391.244223360284</v>
+      </c>
+      <c r="E59">
+        <v>424.3660000000002</v>
+      </c>
+      <c r="F59">
+        <v>765.9660000000002</v>
+      </c>
+      <c r="G59">
+        <v>208.2</v>
+      </c>
+      <c r="H59">
+        <v>1002.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>398.7</v>
+      </c>
+      <c r="K59">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L59">
+        <v>313</v>
+      </c>
+      <c r="M59">
+        <v>36.76636800000001</v>
+      </c>
+      <c r="N59">
+        <v>276.233632</v>
+      </c>
+      <c r="O59">
+        <v>69.058408</v>
+      </c>
+      <c r="P59">
+        <v>207.175224</v>
+      </c>
+      <c r="Q59">
+        <v>292.875224</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3149098482012462</v>
+      </c>
+      <c r="T59">
+        <v>1.957442790339736</v>
+      </c>
+      <c r="U59">
+        <v>0.048</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.036</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.513215120949665</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1555570911850591</v>
+      </c>
+      <c r="C60">
+        <v>824.4984111714389</v>
+      </c>
+      <c r="D60">
+        <v>1395.702411171439</v>
+      </c>
+      <c r="E60">
+        <v>437.804</v>
+      </c>
+      <c r="F60">
+        <v>779.404</v>
+      </c>
+      <c r="G60">
+        <v>208.2</v>
+      </c>
+      <c r="H60">
+        <v>1002.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>398.7</v>
+      </c>
+      <c r="K60">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L60">
+        <v>313</v>
+      </c>
+      <c r="M60">
+        <v>37.411392</v>
+      </c>
+      <c r="N60">
+        <v>275.588608</v>
+      </c>
+      <c r="O60">
+        <v>68.89715200000001</v>
+      </c>
+      <c r="P60">
+        <v>206.691456</v>
+      </c>
+      <c r="Q60">
+        <v>292.391456</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3206597409168073</v>
+      </c>
+      <c r="T60">
+        <v>1.998205863857847</v>
+      </c>
+      <c r="U60">
+        <v>0.048</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.036</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>8.366435549898812</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1551829476435823</v>
+      </c>
+      <c r="C61">
+        <v>815.5472630130207</v>
+      </c>
+      <c r="D61">
+        <v>1400.189263013021</v>
+      </c>
+      <c r="E61">
+        <v>451.2420000000001</v>
+      </c>
+      <c r="F61">
+        <v>792.8420000000001</v>
+      </c>
+      <c r="G61">
+        <v>208.2</v>
+      </c>
+      <c r="H61">
+        <v>1002.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>398.7</v>
+      </c>
+      <c r="K61">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L61">
+        <v>313</v>
+      </c>
+      <c r="M61">
+        <v>38.05641600000001</v>
+      </c>
+      <c r="N61">
+        <v>274.943584</v>
+      </c>
+      <c r="O61">
+        <v>68.735896</v>
+      </c>
+      <c r="P61">
+        <v>206.207688</v>
+      </c>
+      <c r="Q61">
+        <v>291.907688</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3266901162038592</v>
+      </c>
+      <c r="T61">
+        <v>2.040957379986599</v>
+      </c>
+      <c r="U61">
+        <v>0.048</v>
+      </c>
+      <c r="V61">
+        <v>0.25</v>
+      </c>
+      <c r="W61">
+        <v>0.036</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>8.224631557527644</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1548088041021055</v>
+      </c>
+      <c r="C62">
+        <v>806.6250562207537</v>
+      </c>
+      <c r="D62">
+        <v>1404.705056220754</v>
+      </c>
+      <c r="E62">
+        <v>464.6800000000001</v>
+      </c>
+      <c r="F62">
+        <v>806.2800000000001</v>
+      </c>
+      <c r="G62">
+        <v>208.2</v>
+      </c>
+      <c r="H62">
+        <v>1002.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>398.7</v>
+      </c>
+      <c r="K62">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L62">
+        <v>313</v>
+      </c>
+      <c r="M62">
+        <v>38.70144000000001</v>
+      </c>
+      <c r="N62">
+        <v>274.29856</v>
+      </c>
+      <c r="O62">
+        <v>68.57464</v>
+      </c>
+      <c r="P62">
+        <v>205.72392</v>
+      </c>
+      <c r="Q62">
+        <v>291.42392</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3330220102552637</v>
+      </c>
+      <c r="T62">
+        <v>2.085846471921788</v>
+      </c>
+      <c r="U62">
+        <v>0.048</v>
+      </c>
+      <c r="V62">
+        <v>0.25</v>
+      </c>
+      <c r="W62">
+        <v>0.036</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>8.087554364902184</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1544346605606287</v>
+      </c>
+      <c r="C63">
+        <v>797.7320717197113</v>
+      </c>
+      <c r="D63">
+        <v>1409.250071719711</v>
+      </c>
+      <c r="E63">
+        <v>478.1180000000001</v>
+      </c>
+      <c r="F63">
+        <v>819.7180000000001</v>
+      </c>
+      <c r="G63">
+        <v>208.2</v>
+      </c>
+      <c r="H63">
+        <v>1002.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>398.7</v>
+      </c>
+      <c r="K63">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L63">
+        <v>313</v>
+      </c>
+      <c r="M63">
+        <v>39.346464</v>
+      </c>
+      <c r="N63">
+        <v>273.653536</v>
+      </c>
+      <c r="O63">
+        <v>68.41338399999999</v>
+      </c>
+      <c r="P63">
+        <v>205.240152</v>
+      </c>
+      <c r="Q63">
+        <v>290.940152</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.339678616822125</v>
+      </c>
+      <c r="T63">
+        <v>2.133037568571603</v>
+      </c>
+      <c r="U63">
+        <v>0.048</v>
+      </c>
+      <c r="V63">
+        <v>0.25</v>
+      </c>
+      <c r="W63">
+        <v>0.036</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>7.954971506461163</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.154060517019152</v>
+      </c>
+      <c r="C64">
+        <v>788.8685940825773</v>
+      </c>
+      <c r="D64">
+        <v>1413.824594082577</v>
+      </c>
+      <c r="E64">
+        <v>491.556</v>
+      </c>
+      <c r="F64">
+        <v>833.1560000000001</v>
+      </c>
+      <c r="G64">
+        <v>208.2</v>
+      </c>
+      <c r="H64">
+        <v>1002.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>398.7</v>
+      </c>
+      <c r="K64">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L64">
+        <v>313</v>
+      </c>
+      <c r="M64">
+        <v>39.991488</v>
+      </c>
+      <c r="N64">
+        <v>273.008512</v>
+      </c>
+      <c r="O64">
+        <v>68.252128</v>
+      </c>
+      <c r="P64">
+        <v>204.756384</v>
+      </c>
+      <c r="Q64">
+        <v>290.456384</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3466855711030315</v>
+      </c>
+      <c r="T64">
+        <v>2.182712407150354</v>
+      </c>
+      <c r="U64">
+        <v>0.048</v>
+      </c>
+      <c r="V64">
+        <v>0.25</v>
+      </c>
+      <c r="W64">
+        <v>0.036</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>7.826665514421468</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1543951234776752</v>
+      </c>
+      <c r="C65">
+        <v>771.338078532037</v>
+      </c>
+      <c r="D65">
+        <v>1409.732078532037</v>
+      </c>
+      <c r="E65">
+        <v>504.9940000000001</v>
+      </c>
+      <c r="F65">
+        <v>846.5940000000002</v>
+      </c>
+      <c r="G65">
+        <v>208.2</v>
+      </c>
+      <c r="H65">
+        <v>1002.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>398.7</v>
+      </c>
+      <c r="K65">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L65">
+        <v>313</v>
+      </c>
+      <c r="M65">
+        <v>41.90640300000001</v>
+      </c>
+      <c r="N65">
+        <v>271.093597</v>
+      </c>
+      <c r="O65">
+        <v>67.77339925</v>
+      </c>
+      <c r="P65">
+        <v>203.32019775</v>
+      </c>
+      <c r="Q65">
+        <v>289.02019775</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3540712796693924</v>
+      </c>
+      <c r="T65">
+        <v>2.235072372138768</v>
+      </c>
+      <c r="U65">
+        <v>0.0495</v>
+      </c>
+      <c r="V65">
+        <v>0.25</v>
+      </c>
+      <c r="W65">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>7.46902567610014</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1540322299361984</v>
+      </c>
+      <c r="C66">
+        <v>762.3396582120899</v>
+      </c>
+      <c r="D66">
+        <v>1414.17165821209</v>
+      </c>
+      <c r="E66">
+        <v>518.4320000000001</v>
+      </c>
+      <c r="F66">
+        <v>860.0320000000002</v>
+      </c>
+      <c r="G66">
+        <v>208.2</v>
+      </c>
+      <c r="H66">
+        <v>1002.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>398.7</v>
+      </c>
+      <c r="K66">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L66">
+        <v>313</v>
+      </c>
+      <c r="M66">
+        <v>42.57158400000001</v>
+      </c>
+      <c r="N66">
+        <v>270.428416</v>
+      </c>
+      <c r="O66">
+        <v>67.60710399999999</v>
+      </c>
+      <c r="P66">
+        <v>202.821312</v>
+      </c>
+      <c r="Q66">
+        <v>288.521312</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3618673053783289</v>
+      </c>
+      <c r="T66">
+        <v>2.290341224070983</v>
+      </c>
+      <c r="U66">
+        <v>0.0495</v>
+      </c>
+      <c r="V66">
+        <v>0.25</v>
+      </c>
+      <c r="W66">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>7.352322149911075</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1536693363947216</v>
+      </c>
+      <c r="C67">
+        <v>753.3692888036097</v>
+      </c>
+      <c r="D67">
+        <v>1418.63928880361</v>
+      </c>
+      <c r="E67">
+        <v>531.8700000000001</v>
+      </c>
+      <c r="F67">
+        <v>873.4700000000001</v>
+      </c>
+      <c r="G67">
+        <v>208.2</v>
+      </c>
+      <c r="H67">
+        <v>1002.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>398.7</v>
+      </c>
+      <c r="K67">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L67">
+        <v>313</v>
+      </c>
+      <c r="M67">
+        <v>43.23676500000001</v>
+      </c>
+      <c r="N67">
+        <v>269.763235</v>
+      </c>
+      <c r="O67">
+        <v>67.44080875</v>
+      </c>
+      <c r="P67">
+        <v>202.32242625</v>
+      </c>
+      <c r="Q67">
+        <v>288.02242625</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3701088182706332</v>
+      </c>
+      <c r="T67">
+        <v>2.348768296113611</v>
+      </c>
+      <c r="U67">
+        <v>0.0495</v>
+      </c>
+      <c r="V67">
+        <v>0.25</v>
+      </c>
+      <c r="W67">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>7.239209501450905</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1533064428532448</v>
+      </c>
+      <c r="C68">
+        <v>744.4272370032397</v>
+      </c>
+      <c r="D68">
+        <v>1423.13523700324</v>
+      </c>
+      <c r="E68">
+        <v>545.3080000000001</v>
+      </c>
+      <c r="F68">
+        <v>886.9080000000001</v>
+      </c>
+      <c r="G68">
+        <v>208.2</v>
+      </c>
+      <c r="H68">
+        <v>1002.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>398.7</v>
+      </c>
+      <c r="K68">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L68">
+        <v>313</v>
+      </c>
+      <c r="M68">
+        <v>43.90194600000001</v>
+      </c>
+      <c r="N68">
+        <v>269.098054</v>
+      </c>
+      <c r="O68">
+        <v>67.2745135</v>
+      </c>
+      <c r="P68">
+        <v>201.8235405</v>
+      </c>
+      <c r="Q68">
+        <v>287.5235405</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3788351260389554</v>
+      </c>
+      <c r="T68">
+        <v>2.41063225474698</v>
+      </c>
+      <c r="U68">
+        <v>0.0495</v>
+      </c>
+      <c r="V68">
+        <v>0.25</v>
+      </c>
+      <c r="W68">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>7.129524509004679</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.152943549311768</v>
+      </c>
+      <c r="C69">
+        <v>735.5137728992272</v>
+      </c>
+      <c r="D69">
+        <v>1427.659772899227</v>
+      </c>
+      <c r="E69">
+        <v>558.7460000000002</v>
+      </c>
+      <c r="F69">
+        <v>900.3460000000002</v>
+      </c>
+      <c r="G69">
+        <v>208.2</v>
+      </c>
+      <c r="H69">
+        <v>1002.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>398.7</v>
+      </c>
+      <c r="K69">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L69">
+        <v>313</v>
+      </c>
+      <c r="M69">
+        <v>44.56712700000001</v>
+      </c>
+      <c r="N69">
+        <v>268.432873</v>
+      </c>
+      <c r="O69">
+        <v>67.10821824999999</v>
+      </c>
+      <c r="P69">
+        <v>201.32465475</v>
+      </c>
+      <c r="Q69">
+        <v>287.02465475</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3880903009447517</v>
+      </c>
+      <c r="T69">
+        <v>2.476245544206615</v>
+      </c>
+      <c r="U69">
+        <v>0.0495</v>
+      </c>
+      <c r="V69">
+        <v>0.25</v>
+      </c>
+      <c r="W69">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>7.023113695437444</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1525806557702913</v>
+      </c>
+      <c r="C70">
+        <v>726.629170025513</v>
+      </c>
+      <c r="D70">
+        <v>1432.213170025513</v>
+      </c>
+      <c r="E70">
+        <v>572.1840000000002</v>
+      </c>
+      <c r="F70">
+        <v>913.7840000000002</v>
+      </c>
+      <c r="G70">
+        <v>208.2</v>
+      </c>
+      <c r="H70">
+        <v>1002.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>398.7</v>
+      </c>
+      <c r="K70">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L70">
+        <v>313</v>
+      </c>
+      <c r="M70">
+        <v>45.23230800000001</v>
+      </c>
+      <c r="N70">
+        <v>267.767692</v>
+      </c>
+      <c r="O70">
+        <v>66.941923</v>
+      </c>
+      <c r="P70">
+        <v>200.825769</v>
+      </c>
+      <c r="Q70">
+        <v>286.525769</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3979239242821602</v>
+      </c>
+      <c r="T70">
+        <v>2.545959664257477</v>
+      </c>
+      <c r="U70">
+        <v>0.0495</v>
+      </c>
+      <c r="V70">
+        <v>0.25</v>
+      </c>
+      <c r="W70">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>6.919832611681012</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1522177622288145</v>
+      </c>
+      <c r="C71">
+        <v>717.773705416854</v>
+      </c>
+      <c r="D71">
+        <v>1436.795705416854</v>
+      </c>
+      <c r="E71">
+        <v>585.6220000000002</v>
+      </c>
+      <c r="F71">
+        <v>927.2220000000002</v>
+      </c>
+      <c r="G71">
+        <v>208.2</v>
+      </c>
+      <c r="H71">
+        <v>1002.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>398.7</v>
+      </c>
+      <c r="K71">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L71">
+        <v>313</v>
+      </c>
+      <c r="M71">
+        <v>45.89748900000001</v>
+      </c>
+      <c r="N71">
+        <v>267.102511</v>
+      </c>
+      <c r="O71">
+        <v>66.77562775</v>
+      </c>
+      <c r="P71">
+        <v>200.32688325</v>
+      </c>
+      <c r="Q71">
+        <v>286.02688325</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4083919749316597</v>
+      </c>
+      <c r="T71">
+        <v>2.620171469472911</v>
+      </c>
+      <c r="U71">
+        <v>0.0495</v>
+      </c>
+      <c r="V71">
+        <v>0.25</v>
+      </c>
+      <c r="W71">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.819545182526214</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1518548686873377</v>
+      </c>
+      <c r="C72">
+        <v>708.9476596650105</v>
+      </c>
+      <c r="D72">
+        <v>1441.407659665011</v>
+      </c>
+      <c r="E72">
+        <v>599.0600000000002</v>
+      </c>
+      <c r="F72">
+        <v>940.6600000000002</v>
+      </c>
+      <c r="G72">
+        <v>208.2</v>
+      </c>
+      <c r="H72">
+        <v>1002.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>398.7</v>
+      </c>
+      <c r="K72">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L72">
+        <v>313</v>
+      </c>
+      <c r="M72">
+        <v>46.56267000000001</v>
+      </c>
+      <c r="N72">
+        <v>266.43733</v>
+      </c>
+      <c r="O72">
+        <v>66.60933249999999</v>
+      </c>
+      <c r="P72">
+        <v>199.8279975</v>
+      </c>
+      <c r="Q72">
+        <v>285.5279975</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4195578956244591</v>
+      </c>
+      <c r="T72">
+        <v>2.699330728369373</v>
+      </c>
+      <c r="U72">
+        <v>0.0495</v>
+      </c>
+      <c r="V72">
+        <v>0.25</v>
+      </c>
+      <c r="W72">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>6.722123108490125</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.151491975145861</v>
+      </c>
+      <c r="C73">
+        <v>700.1513169760168</v>
+      </c>
+      <c r="D73">
+        <v>1446.049316976017</v>
+      </c>
+      <c r="E73">
+        <v>612.498</v>
+      </c>
+      <c r="F73">
+        <v>954.0980000000001</v>
+      </c>
+      <c r="G73">
+        <v>208.2</v>
+      </c>
+      <c r="H73">
+        <v>1002.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>398.7</v>
+      </c>
+      <c r="K73">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L73">
+        <v>313</v>
+      </c>
+      <c r="M73">
+        <v>47.22785100000001</v>
+      </c>
+      <c r="N73">
+        <v>265.772149</v>
+      </c>
+      <c r="O73">
+        <v>66.44303725</v>
+      </c>
+      <c r="P73">
+        <v>199.32911175</v>
+      </c>
+      <c r="Q73">
+        <v>285.02911175</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4314938798133136</v>
+      </c>
+      <c r="T73">
+        <v>2.783949246500074</v>
+      </c>
+      <c r="U73">
+        <v>0.0495</v>
+      </c>
+      <c r="V73">
+        <v>0.25</v>
+      </c>
+      <c r="W73">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.627445318229702</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1511290816043842</v>
+      </c>
+      <c r="C74">
+        <v>691.384965228566</v>
+      </c>
+      <c r="D74">
+        <v>1450.720965228566</v>
+      </c>
+      <c r="E74">
+        <v>625.936</v>
+      </c>
+      <c r="F74">
+        <v>967.5360000000001</v>
+      </c>
+      <c r="G74">
+        <v>208.2</v>
+      </c>
+      <c r="H74">
+        <v>1002.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>398.7</v>
+      </c>
+      <c r="K74">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L74">
+        <v>313</v>
+      </c>
+      <c r="M74">
+        <v>47.89303200000001</v>
+      </c>
+      <c r="N74">
+        <v>265.106968</v>
+      </c>
+      <c r="O74">
+        <v>66.276742</v>
+      </c>
+      <c r="P74">
+        <v>198.830226</v>
+      </c>
+      <c r="Q74">
+        <v>284.530226</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4442824343013719</v>
+      </c>
+      <c r="T74">
+        <v>2.874611944497254</v>
+      </c>
+      <c r="U74">
+        <v>0.0495</v>
+      </c>
+      <c r="V74">
+        <v>0.25</v>
+      </c>
+      <c r="W74">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.535397466587623</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1507661880629074</v>
+      </c>
+      <c r="C75">
+        <v>682.6488960335212</v>
+      </c>
+      <c r="D75">
+        <v>1455.422896033521</v>
+      </c>
+      <c r="E75">
+        <v>639.3740000000001</v>
+      </c>
+      <c r="F75">
+        <v>980.9740000000002</v>
+      </c>
+      <c r="G75">
+        <v>208.2</v>
+      </c>
+      <c r="H75">
+        <v>1002.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>398.7</v>
+      </c>
+      <c r="K75">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L75">
+        <v>313</v>
+      </c>
+      <c r="M75">
+        <v>48.55821300000001</v>
+      </c>
+      <c r="N75">
+        <v>264.441787</v>
+      </c>
+      <c r="O75">
+        <v>66.11044674999999</v>
+      </c>
+      <c r="P75">
+        <v>198.33134025</v>
+      </c>
+      <c r="Q75">
+        <v>284.03134025</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4580182891218791</v>
+      </c>
+      <c r="T75">
+        <v>2.971990397901632</v>
+      </c>
+      <c r="U75">
+        <v>0.0495</v>
+      </c>
+      <c r="V75">
+        <v>0.25</v>
+      </c>
+      <c r="W75">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>6.445871473894641</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1504032945214306</v>
+      </c>
+      <c r="C76">
+        <v>673.9434047946012</v>
+      </c>
+      <c r="D76">
+        <v>1460.155404794601</v>
+      </c>
+      <c r="E76">
+        <v>652.8120000000001</v>
+      </c>
+      <c r="F76">
+        <v>994.4120000000001</v>
+      </c>
+      <c r="G76">
+        <v>208.2</v>
+      </c>
+      <c r="H76">
+        <v>1002.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>398.7</v>
+      </c>
+      <c r="K76">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L76">
+        <v>313</v>
+      </c>
+      <c r="M76">
+        <v>49.22339400000001</v>
+      </c>
+      <c r="N76">
+        <v>263.776606</v>
+      </c>
+      <c r="O76">
+        <v>65.9441515</v>
+      </c>
+      <c r="P76">
+        <v>197.8324545</v>
+      </c>
+      <c r="Q76">
+        <v>283.5324545</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4728107481593483</v>
+      </c>
+      <c r="T76">
+        <v>3.076859501567886</v>
+      </c>
+      <c r="U76">
+        <v>0.0495</v>
+      </c>
+      <c r="V76">
+        <v>0.25</v>
+      </c>
+      <c r="W76">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>6.358765102625795</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1500404009799538</v>
+      </c>
+      <c r="C77">
+        <v>665.2687907702398</v>
+      </c>
+      <c r="D77">
+        <v>1464.91879077024</v>
+      </c>
+      <c r="E77">
+        <v>666.2500000000001</v>
+      </c>
+      <c r="F77">
+        <v>1007.85</v>
+      </c>
+      <c r="G77">
+        <v>208.2</v>
+      </c>
+      <c r="H77">
+        <v>1002.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>398.7</v>
+      </c>
+      <c r="K77">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L77">
+        <v>313</v>
+      </c>
+      <c r="M77">
+        <v>49.88857500000001</v>
+      </c>
+      <c r="N77">
+        <v>263.111425</v>
+      </c>
+      <c r="O77">
+        <v>65.77785625</v>
+      </c>
+      <c r="P77">
+        <v>197.33356875</v>
+      </c>
+      <c r="Q77">
+        <v>283.03356875</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4887866039198152</v>
+      </c>
+      <c r="T77">
+        <v>3.190118133527441</v>
+      </c>
+      <c r="U77">
+        <v>0.0495</v>
+      </c>
+      <c r="V77">
+        <v>0.25</v>
+      </c>
+      <c r="W77">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>6.273981567924118</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.149677507438477</v>
+      </c>
+      <c r="C78">
+        <v>656.6253571366732</v>
+      </c>
+      <c r="D78">
+        <v>1469.713357136673</v>
+      </c>
+      <c r="E78">
+        <v>679.6880000000001</v>
+      </c>
+      <c r="F78">
+        <v>1021.288</v>
+      </c>
+      <c r="G78">
+        <v>208.2</v>
+      </c>
+      <c r="H78">
+        <v>1002.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>398.7</v>
+      </c>
+      <c r="K78">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L78">
+        <v>313</v>
+      </c>
+      <c r="M78">
+        <v>50.55375600000001</v>
+      </c>
+      <c r="N78">
+        <v>262.446244</v>
+      </c>
+      <c r="O78">
+        <v>65.61156099999999</v>
+      </c>
+      <c r="P78">
+        <v>196.834683</v>
+      </c>
+      <c r="Q78">
+        <v>282.534683</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5060937809936543</v>
+      </c>
+      <c r="T78">
+        <v>3.312814984816958</v>
+      </c>
+      <c r="U78">
+        <v>0.0495</v>
+      </c>
+      <c r="V78">
+        <v>0.25</v>
+      </c>
+      <c r="W78">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>6.191429178872484</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1501231138970003</v>
+      </c>
+      <c r="C79">
+        <v>637.3043581691461</v>
+      </c>
+      <c r="D79">
+        <v>1463.830358169146</v>
+      </c>
+      <c r="E79">
+        <v>693.1260000000001</v>
+      </c>
+      <c r="F79">
+        <v>1034.726</v>
+      </c>
+      <c r="G79">
+        <v>208.2</v>
+      </c>
+      <c r="H79">
+        <v>1002.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>398.7</v>
+      </c>
+      <c r="K79">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L79">
+        <v>313</v>
+      </c>
+      <c r="M79">
+        <v>52.66755340000001</v>
+      </c>
+      <c r="N79">
+        <v>260.3324466</v>
+      </c>
+      <c r="O79">
+        <v>65.08311164999999</v>
+      </c>
+      <c r="P79">
+        <v>195.24933495</v>
+      </c>
+      <c r="Q79">
+        <v>280.94933495</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5249059299869576</v>
+      </c>
+      <c r="T79">
+        <v>3.446181127522955</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.25</v>
+      </c>
+      <c r="W79">
+        <v>0.038175</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.942937915168088</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1497707203555234</v>
+      </c>
+      <c r="C80">
+        <v>628.5148308688265</v>
+      </c>
+      <c r="D80">
+        <v>1468.478830868827</v>
+      </c>
+      <c r="E80">
+        <v>706.5640000000002</v>
+      </c>
+      <c r="F80">
+        <v>1048.164</v>
+      </c>
+      <c r="G80">
+        <v>208.2</v>
+      </c>
+      <c r="H80">
+        <v>1002.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>398.7</v>
+      </c>
+      <c r="K80">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L80">
+        <v>313</v>
+      </c>
+      <c r="M80">
+        <v>53.35154760000001</v>
+      </c>
+      <c r="N80">
+        <v>259.6484524</v>
+      </c>
+      <c r="O80">
+        <v>64.9121131</v>
+      </c>
+      <c r="P80">
+        <v>194.7363393</v>
+      </c>
+      <c r="Q80">
+        <v>280.4363393</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5454282743432883</v>
+      </c>
+      <c r="T80">
+        <v>3.591671465020405</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.25</v>
+      </c>
+      <c r="W80">
+        <v>0.038175</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.866746403435164</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1494183268140467</v>
+      </c>
+      <c r="C81">
+        <v>619.7549205732876</v>
+      </c>
+      <c r="D81">
+        <v>1473.156920573288</v>
+      </c>
+      <c r="E81">
+        <v>720.0020000000001</v>
+      </c>
+      <c r="F81">
+        <v>1061.602</v>
+      </c>
+      <c r="G81">
+        <v>208.2</v>
+      </c>
+      <c r="H81">
+        <v>1002.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>398.7</v>
+      </c>
+      <c r="K81">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L81">
+        <v>313</v>
+      </c>
+      <c r="M81">
+        <v>54.0355418</v>
+      </c>
+      <c r="N81">
+        <v>258.9644582</v>
+      </c>
+      <c r="O81">
+        <v>64.74111454999999</v>
+      </c>
+      <c r="P81">
+        <v>194.22334365</v>
+      </c>
+      <c r="Q81">
+        <v>279.92334365</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5679051276859366</v>
+      </c>
+      <c r="T81">
+        <v>3.751018025136661</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.25</v>
+      </c>
+      <c r="W81">
+        <v>0.038175</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.792483790733453</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1490659332725699</v>
+      </c>
+      <c r="C82">
+        <v>611.0249112371725</v>
+      </c>
+      <c r="D82">
+        <v>1477.864911237173</v>
+      </c>
+      <c r="E82">
+        <v>733.4400000000002</v>
+      </c>
+      <c r="F82">
+        <v>1075.04</v>
+      </c>
+      <c r="G82">
+        <v>208.2</v>
+      </c>
+      <c r="H82">
+        <v>1002.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>398.7</v>
+      </c>
+      <c r="K82">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L82">
+        <v>313</v>
+      </c>
+      <c r="M82">
+        <v>54.71953600000001</v>
+      </c>
+      <c r="N82">
+        <v>258.280464</v>
+      </c>
+      <c r="O82">
+        <v>64.570116</v>
+      </c>
+      <c r="P82">
+        <v>193.710348</v>
+      </c>
+      <c r="Q82">
+        <v>279.410348</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5926296663628496</v>
+      </c>
+      <c r="T82">
+        <v>3.926299241264543</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.25</v>
+      </c>
+      <c r="W82">
+        <v>0.038175</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.720077743349284</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1487135397310931</v>
+      </c>
+      <c r="C83">
+        <v>602.3250904566689</v>
+      </c>
+      <c r="D83">
+        <v>1482.603090456669</v>
+      </c>
+      <c r="E83">
+        <v>746.8780000000003</v>
+      </c>
+      <c r="F83">
+        <v>1088.478</v>
+      </c>
+      <c r="G83">
+        <v>208.2</v>
+      </c>
+      <c r="H83">
+        <v>1002.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>398.7</v>
+      </c>
+      <c r="K83">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L83">
+        <v>313</v>
+      </c>
+      <c r="M83">
+        <v>55.40353020000001</v>
+      </c>
+      <c r="N83">
+        <v>257.5964698</v>
+      </c>
+      <c r="O83">
+        <v>64.39911744999999</v>
+      </c>
+      <c r="P83">
+        <v>193.19735235</v>
+      </c>
+      <c r="Q83">
+        <v>278.8973523499999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6199567880583849</v>
+      </c>
+      <c r="T83">
+        <v>4.120031111721675</v>
+      </c>
+      <c r="U83">
+        <v>0.0509</v>
+      </c>
+      <c r="V83">
+        <v>0.25</v>
+      </c>
+      <c r="W83">
+        <v>0.038175</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.649459499604231</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1483611461896163</v>
+      </c>
+      <c r="C84">
+        <v>593.6557495280717</v>
+      </c>
+      <c r="D84">
+        <v>1487.371749528072</v>
+      </c>
+      <c r="E84">
+        <v>760.3160000000001</v>
+      </c>
+      <c r="F84">
+        <v>1101.916</v>
+      </c>
+      <c r="G84">
+        <v>208.2</v>
+      </c>
+      <c r="H84">
+        <v>1002.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>398.7</v>
+      </c>
+      <c r="K84">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L84">
+        <v>313</v>
+      </c>
+      <c r="M84">
+        <v>56.08752440000001</v>
+      </c>
+      <c r="N84">
+        <v>256.9124756</v>
+      </c>
+      <c r="O84">
+        <v>64.2281189</v>
+      </c>
+      <c r="P84">
+        <v>192.6843567</v>
+      </c>
+      <c r="Q84">
+        <v>278.3843567</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6503202566089799</v>
+      </c>
+      <c r="T84">
+        <v>4.335288745562933</v>
+      </c>
+      <c r="U84">
+        <v>0.0509</v>
+      </c>
+      <c r="V84">
+        <v>0.25</v>
+      </c>
+      <c r="W84">
+        <v>0.038175</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.580563652048083</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1480087526481395</v>
+      </c>
+      <c r="C85">
+        <v>585.0171835074843</v>
+      </c>
+      <c r="D85">
+        <v>1492.171183507485</v>
+      </c>
+      <c r="E85">
+        <v>773.7540000000002</v>
+      </c>
+      <c r="F85">
+        <v>1115.354</v>
+      </c>
+      <c r="G85">
+        <v>208.2</v>
+      </c>
+      <c r="H85">
+        <v>1002.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>398.7</v>
+      </c>
+      <c r="K85">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L85">
+        <v>313</v>
+      </c>
+      <c r="M85">
+        <v>56.77151860000001</v>
+      </c>
+      <c r="N85">
+        <v>256.2284814</v>
+      </c>
+      <c r="O85">
+        <v>64.05712034999999</v>
+      </c>
+      <c r="P85">
+        <v>192.17136105</v>
+      </c>
+      <c r="Q85">
+        <v>277.87136105</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6842558979302329</v>
+      </c>
+      <c r="T85">
+        <v>4.575870806914928</v>
+      </c>
+      <c r="U85">
+        <v>0.0509</v>
+      </c>
+      <c r="V85">
+        <v>0.25</v>
+      </c>
+      <c r="W85">
+        <v>0.038175</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.5133279453969</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1476563591066627</v>
+      </c>
+      <c r="C86">
+        <v>576.4096912716711</v>
+      </c>
+      <c r="D86">
+        <v>1497.001691271671</v>
+      </c>
+      <c r="E86">
+        <v>787.1920000000001</v>
+      </c>
+      <c r="F86">
+        <v>1128.792</v>
+      </c>
+      <c r="G86">
+        <v>208.2</v>
+      </c>
+      <c r="H86">
+        <v>1002.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>398.7</v>
+      </c>
+      <c r="K86">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L86">
+        <v>313</v>
+      </c>
+      <c r="M86">
+        <v>57.45551280000001</v>
+      </c>
+      <c r="N86">
+        <v>255.5444872</v>
+      </c>
+      <c r="O86">
+        <v>63.8861218</v>
+      </c>
+      <c r="P86">
+        <v>191.6583654</v>
+      </c>
+      <c r="Q86">
+        <v>277.3583654</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7224334944166422</v>
+      </c>
+      <c r="T86">
+        <v>4.846525625935919</v>
+      </c>
+      <c r="U86">
+        <v>0.0509</v>
+      </c>
+      <c r="V86">
+        <v>0.25</v>
+      </c>
+      <c r="W86">
+        <v>0.038175</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.447693088904081</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.147303965565186</v>
+      </c>
+      <c r="C87">
+        <v>567.833575580102</v>
+      </c>
+      <c r="D87">
+        <v>1501.863575580102</v>
+      </c>
+      <c r="E87">
+        <v>800.63</v>
+      </c>
+      <c r="F87">
+        <v>1142.23</v>
+      </c>
+      <c r="G87">
+        <v>208.2</v>
+      </c>
+      <c r="H87">
+        <v>1002.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>398.7</v>
+      </c>
+      <c r="K87">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L87">
+        <v>313</v>
+      </c>
+      <c r="M87">
+        <v>58.139507</v>
+      </c>
+      <c r="N87">
+        <v>254.860493</v>
+      </c>
+      <c r="O87">
+        <v>63.71512325</v>
+      </c>
+      <c r="P87">
+        <v>191.14536975</v>
+      </c>
+      <c r="Q87">
+        <v>276.84536975</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7657014371012401</v>
+      </c>
+      <c r="T87">
+        <v>5.153267754159712</v>
+      </c>
+      <c r="U87">
+        <v>0.0509</v>
+      </c>
+      <c r="V87">
+        <v>0.25</v>
+      </c>
+      <c r="W87">
+        <v>0.038175</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.383602581975798</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1469515720237092</v>
+      </c>
+      <c r="C88">
+        <v>559.2891431382109</v>
+      </c>
+      <c r="D88">
+        <v>1506.757143138211</v>
+      </c>
+      <c r="E88">
+        <v>814.0680000000001</v>
+      </c>
+      <c r="F88">
+        <v>1155.668</v>
+      </c>
+      <c r="G88">
+        <v>208.2</v>
+      </c>
+      <c r="H88">
+        <v>1002.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>398.7</v>
+      </c>
+      <c r="K88">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L88">
+        <v>313</v>
+      </c>
+      <c r="M88">
+        <v>58.82350120000001</v>
+      </c>
+      <c r="N88">
+        <v>254.1764988</v>
+      </c>
+      <c r="O88">
+        <v>63.5441247</v>
+      </c>
+      <c r="P88">
+        <v>190.6323741</v>
+      </c>
+      <c r="Q88">
+        <v>276.3323741</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.8151505144550657</v>
+      </c>
+      <c r="T88">
+        <v>5.503830186415474</v>
+      </c>
+      <c r="U88">
+        <v>0.0509</v>
+      </c>
+      <c r="V88">
+        <v>0.25</v>
+      </c>
+      <c r="W88">
+        <v>0.038175</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.321002551952823</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1465991784822324</v>
+      </c>
+      <c r="C89">
+        <v>550.7767046618862</v>
+      </c>
+      <c r="D89">
+        <v>1511.682704661886</v>
+      </c>
+      <c r="E89">
+        <v>827.5060000000002</v>
+      </c>
+      <c r="F89">
+        <v>1169.106</v>
+      </c>
+      <c r="G89">
+        <v>208.2</v>
+      </c>
+      <c r="H89">
+        <v>1002.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>398.7</v>
+      </c>
+      <c r="K89">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L89">
+        <v>313</v>
+      </c>
+      <c r="M89">
+        <v>59.50749540000001</v>
+      </c>
+      <c r="N89">
+        <v>253.4925046</v>
+      </c>
+      <c r="O89">
+        <v>63.37312615</v>
+      </c>
+      <c r="P89">
+        <v>190.11937845</v>
+      </c>
+      <c r="Q89">
+        <v>275.81937845</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8722071421710185</v>
+      </c>
+      <c r="T89">
+        <v>5.908325300556738</v>
+      </c>
+      <c r="U89">
+        <v>0.0509</v>
+      </c>
+      <c r="V89">
+        <v>0.25</v>
+      </c>
+      <c r="W89">
+        <v>0.038175</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.259841603079802</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1462467849407557</v>
+      </c>
+      <c r="C90">
+        <v>542.2965749432419</v>
+      </c>
+      <c r="D90">
+        <v>1516.640574943242</v>
+      </c>
+      <c r="E90">
+        <v>840.9440000000001</v>
+      </c>
+      <c r="F90">
+        <v>1182.544</v>
+      </c>
+      <c r="G90">
+        <v>208.2</v>
+      </c>
+      <c r="H90">
+        <v>1002.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>398.7</v>
+      </c>
+      <c r="K90">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L90">
+        <v>313</v>
+      </c>
+      <c r="M90">
+        <v>60.1914896</v>
+      </c>
+      <c r="N90">
+        <v>252.8085104</v>
+      </c>
+      <c r="O90">
+        <v>63.2021276</v>
+      </c>
+      <c r="P90">
+        <v>189.6063828</v>
+      </c>
+      <c r="Q90">
+        <v>275.3063828</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.9387732078396305</v>
+      </c>
+      <c r="T90">
+        <v>6.380236267054881</v>
+      </c>
+      <c r="U90">
+        <v>0.0509</v>
+      </c>
+      <c r="V90">
+        <v>0.25</v>
+      </c>
+      <c r="W90">
+        <v>0.038175</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>5.200070675772078</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1458943913992788</v>
+      </c>
+      <c r="C91">
+        <v>533.849072917679</v>
+      </c>
+      <c r="D91">
+        <v>1521.631072917679</v>
+      </c>
+      <c r="E91">
+        <v>854.3820000000002</v>
+      </c>
+      <c r="F91">
+        <v>1195.982</v>
+      </c>
+      <c r="G91">
+        <v>208.2</v>
+      </c>
+      <c r="H91">
+        <v>1002.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>398.7</v>
+      </c>
+      <c r="K91">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L91">
+        <v>313</v>
+      </c>
+      <c r="M91">
+        <v>60.87548380000001</v>
+      </c>
+      <c r="N91">
+        <v>252.1245162</v>
+      </c>
+      <c r="O91">
+        <v>63.03112905</v>
+      </c>
+      <c r="P91">
+        <v>189.09338715</v>
+      </c>
+      <c r="Q91">
+        <v>274.7933871499999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.017442194538899</v>
+      </c>
+      <c r="T91">
+        <v>6.937949227461776</v>
+      </c>
+      <c r="U91">
+        <v>0.0509</v>
+      </c>
+      <c r="V91">
+        <v>0.25</v>
+      </c>
+      <c r="W91">
+        <v>0.038175</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>5.141642915370143</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1455419978578021</v>
+      </c>
+      <c r="C92">
+        <v>525.4345217322764</v>
+      </c>
+      <c r="D92">
+        <v>1526.654521732277</v>
+      </c>
+      <c r="E92">
+        <v>867.8200000000003</v>
+      </c>
+      <c r="F92">
+        <v>1209.42</v>
+      </c>
+      <c r="G92">
+        <v>208.2</v>
+      </c>
+      <c r="H92">
+        <v>1002.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>398.7</v>
+      </c>
+      <c r="K92">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L92">
+        <v>313</v>
+      </c>
+      <c r="M92">
+        <v>61.55947800000001</v>
+      </c>
+      <c r="N92">
+        <v>251.440522</v>
+      </c>
+      <c r="O92">
+        <v>62.8601305</v>
+      </c>
+      <c r="P92">
+        <v>188.5803915</v>
+      </c>
+      <c r="Q92">
+        <v>274.2803915</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.111844978578021</v>
+      </c>
+      <c r="T92">
+        <v>7.607204779950052</v>
+      </c>
+      <c r="U92">
+        <v>0.0509</v>
+      </c>
+      <c r="V92">
+        <v>0.25</v>
+      </c>
+      <c r="W92">
+        <v>0.038175</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>5.084513549643808</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1451896043163253</v>
+      </c>
+      <c r="C93">
+        <v>517.0532488155472</v>
+      </c>
+      <c r="D93">
+        <v>1531.711248815547</v>
+      </c>
+      <c r="E93">
+        <v>881.2580000000002</v>
+      </c>
+      <c r="F93">
+        <v>1222.858</v>
+      </c>
+      <c r="G93">
+        <v>208.2</v>
+      </c>
+      <c r="H93">
+        <v>1002.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>398.7</v>
+      </c>
+      <c r="K93">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L93">
+        <v>313</v>
+      </c>
+      <c r="M93">
+        <v>62.24347220000001</v>
+      </c>
+      <c r="N93">
+        <v>250.7565278</v>
+      </c>
+      <c r="O93">
+        <v>62.68913195</v>
+      </c>
+      <c r="P93">
+        <v>188.06739585</v>
+      </c>
+      <c r="Q93">
+        <v>273.76739585</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.227226159070281</v>
+      </c>
+      <c r="T93">
+        <v>8.425183788546832</v>
+      </c>
+      <c r="U93">
+        <v>0.0509</v>
+      </c>
+      <c r="V93">
+        <v>0.25</v>
+      </c>
+      <c r="W93">
+        <v>0.038175</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>5.028639774372998</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1448372107748485</v>
+      </c>
+      <c r="C94">
+        <v>508.7055859485747</v>
+      </c>
+      <c r="D94">
+        <v>1536.801585948575</v>
+      </c>
+      <c r="E94">
+        <v>894.6960000000003</v>
+      </c>
+      <c r="F94">
+        <v>1236.296</v>
+      </c>
+      <c r="G94">
+        <v>208.2</v>
+      </c>
+      <c r="H94">
+        <v>1002.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>398.7</v>
+      </c>
+      <c r="K94">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L94">
+        <v>313</v>
+      </c>
+      <c r="M94">
+        <v>62.92746640000001</v>
+      </c>
+      <c r="N94">
+        <v>250.0725336</v>
+      </c>
+      <c r="O94">
+        <v>62.5181334</v>
+      </c>
+      <c r="P94">
+        <v>187.5544002</v>
+      </c>
+      <c r="Q94">
+        <v>273.2544002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.371452634685607</v>
+      </c>
+      <c r="T94">
+        <v>9.44765754929281</v>
+      </c>
+      <c r="U94">
+        <v>0.0509</v>
+      </c>
+      <c r="V94">
+        <v>0.25</v>
+      </c>
+      <c r="W94">
+        <v>0.038175</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.973980646390682</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1444848172333718</v>
+      </c>
+      <c r="C95">
+        <v>500.3918693375849</v>
+      </c>
+      <c r="D95">
+        <v>1541.925869337585</v>
+      </c>
+      <c r="E95">
+        <v>908.1340000000001</v>
+      </c>
+      <c r="F95">
+        <v>1249.734</v>
+      </c>
+      <c r="G95">
+        <v>208.2</v>
+      </c>
+      <c r="H95">
+        <v>1002.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>398.7</v>
+      </c>
+      <c r="K95">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L95">
+        <v>313</v>
+      </c>
+      <c r="M95">
+        <v>63.61146060000001</v>
+      </c>
+      <c r="N95">
+        <v>249.3885394</v>
+      </c>
+      <c r="O95">
+        <v>62.34713485</v>
+      </c>
+      <c r="P95">
+        <v>187.04140455</v>
+      </c>
+      <c r="Q95">
+        <v>272.74140455</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.556886674762455</v>
+      </c>
+      <c r="T95">
+        <v>10.76226667025192</v>
+      </c>
+      <c r="U95">
+        <v>0.0509</v>
+      </c>
+      <c r="V95">
+        <v>0.25</v>
+      </c>
+      <c r="W95">
+        <v>0.038175</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.920496983526267</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1441324236918949</v>
+      </c>
+      <c r="C96">
+        <v>492.1124396879641</v>
+      </c>
+      <c r="D96">
+        <v>1547.084439687964</v>
+      </c>
+      <c r="E96">
+        <v>921.5720000000002</v>
+      </c>
+      <c r="F96">
+        <v>1263.172</v>
+      </c>
+      <c r="G96">
+        <v>208.2</v>
+      </c>
+      <c r="H96">
+        <v>1002.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>398.7</v>
+      </c>
+      <c r="K96">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L96">
+        <v>313</v>
+      </c>
+      <c r="M96">
+        <v>64.29545480000002</v>
+      </c>
+      <c r="N96">
+        <v>248.7045452</v>
+      </c>
+      <c r="O96">
+        <v>62.1761363</v>
+      </c>
+      <c r="P96">
+        <v>186.5284089</v>
+      </c>
+      <c r="Q96">
+        <v>272.2284089</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.804132061531584</v>
+      </c>
+      <c r="T96">
+        <v>12.51507883153074</v>
+      </c>
+      <c r="U96">
+        <v>0.0509</v>
+      </c>
+      <c r="V96">
+        <v>0.25</v>
+      </c>
+      <c r="W96">
+        <v>0.038175</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.868151270935561</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1437800301504182</v>
+      </c>
+      <c r="C97">
+        <v>483.8676422797714</v>
+      </c>
+      <c r="D97">
+        <v>1552.277642279772</v>
+      </c>
+      <c r="E97">
+        <v>935.0100000000003</v>
+      </c>
+      <c r="F97">
+        <v>1276.61</v>
+      </c>
+      <c r="G97">
+        <v>208.2</v>
+      </c>
+      <c r="H97">
+        <v>1002.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>398.7</v>
+      </c>
+      <c r="K97">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L97">
+        <v>313</v>
+      </c>
+      <c r="M97">
+        <v>64.97944900000002</v>
+      </c>
+      <c r="N97">
+        <v>248.020551</v>
+      </c>
+      <c r="O97">
+        <v>62.00513775</v>
+      </c>
+      <c r="P97">
+        <v>186.01541325</v>
+      </c>
+      <c r="Q97">
+        <v>271.71541325</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.150275603008367</v>
+      </c>
+      <c r="T97">
+        <v>14.96901585732109</v>
+      </c>
+      <c r="U97">
+        <v>0.0509</v>
+      </c>
+      <c r="V97">
+        <v>0.25</v>
+      </c>
+      <c r="W97">
+        <v>0.038175</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.816907573346766</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1434276366089414</v>
+      </c>
+      <c r="C98">
+        <v>475.6578270447847</v>
+      </c>
+      <c r="D98">
+        <v>1557.505827044785</v>
+      </c>
+      <c r="E98">
+        <v>948.4480000000002</v>
+      </c>
+      <c r="F98">
+        <v>1290.048</v>
+      </c>
+      <c r="G98">
+        <v>208.2</v>
+      </c>
+      <c r="H98">
+        <v>1002.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>398.7</v>
+      </c>
+      <c r="K98">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L98">
+        <v>313</v>
+      </c>
+      <c r="M98">
+        <v>65.66344320000002</v>
+      </c>
+      <c r="N98">
+        <v>247.3365568</v>
+      </c>
+      <c r="O98">
+        <v>61.8341392</v>
+      </c>
+      <c r="P98">
+        <v>185.5024176</v>
+      </c>
+      <c r="Q98">
+        <v>271.2024176</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.669490915223533</v>
+      </c>
+      <c r="T98">
+        <v>18.64992139600656</v>
+      </c>
+      <c r="U98">
+        <v>0.0509</v>
+      </c>
+      <c r="V98">
+        <v>0.25</v>
+      </c>
+      <c r="W98">
+        <v>0.038175</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.76673145279107</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1430752430674646</v>
+      </c>
+      <c r="C99">
+        <v>467.4833486450939</v>
+      </c>
+      <c r="D99">
+        <v>1562.769348645094</v>
+      </c>
+      <c r="E99">
+        <v>961.8860000000001</v>
+      </c>
+      <c r="F99">
+        <v>1303.486</v>
+      </c>
+      <c r="G99">
+        <v>208.2</v>
+      </c>
+      <c r="H99">
+        <v>1002.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>398.7</v>
+      </c>
+      <c r="K99">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L99">
+        <v>313</v>
+      </c>
+      <c r="M99">
+        <v>66.3474374</v>
+      </c>
+      <c r="N99">
+        <v>246.6525626</v>
+      </c>
+      <c r="O99">
+        <v>61.66314065</v>
+      </c>
+      <c r="P99">
+        <v>184.98942195</v>
+      </c>
+      <c r="Q99">
+        <v>270.68942195</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.534849768915484</v>
+      </c>
+      <c r="T99">
+        <v>24.7847639604824</v>
+      </c>
+      <c r="U99">
+        <v>0.0509</v>
+      </c>
+      <c r="V99">
+        <v>0.25</v>
+      </c>
+      <c r="W99">
+        <v>0.038175</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.717589891422091</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1427228495259878</v>
+      </c>
+      <c r="C100">
+        <v>459.3445665533045</v>
+      </c>
+      <c r="D100">
+        <v>1568.068566553305</v>
+      </c>
+      <c r="E100">
+        <v>975.3240000000002</v>
+      </c>
+      <c r="F100">
+        <v>1316.924</v>
+      </c>
+      <c r="G100">
+        <v>208.2</v>
+      </c>
+      <c r="H100">
+        <v>1002.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>398.7</v>
+      </c>
+      <c r="K100">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L100">
+        <v>313</v>
+      </c>
+      <c r="M100">
+        <v>67.0314316</v>
+      </c>
+      <c r="N100">
+        <v>245.9685684</v>
+      </c>
+      <c r="O100">
+        <v>61.4921421</v>
+      </c>
+      <c r="P100">
+        <v>184.4764263</v>
+      </c>
+      <c r="Q100">
+        <v>270.1764263</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.265567476299387</v>
+      </c>
+      <c r="T100">
+        <v>37.05444908943409</v>
+      </c>
+      <c r="U100">
+        <v>0.0509</v>
+      </c>
+      <c r="V100">
+        <v>0.25</v>
+      </c>
+      <c r="W100">
+        <v>0.038175</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.66945121906064</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1423704559845111</v>
+      </c>
+      <c r="C101">
+        <v>451.2418451343772</v>
+      </c>
+      <c r="D101">
+        <v>1573.403845134377</v>
+      </c>
+      <c r="E101">
+        <v>988.7620000000001</v>
+      </c>
+      <c r="F101">
+        <v>1330.362</v>
+      </c>
+      <c r="G101">
+        <v>208.2</v>
+      </c>
+      <c r="H101">
+        <v>1002.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>398.7</v>
+      </c>
+      <c r="K101">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="L101">
+        <v>313</v>
+      </c>
+      <c r="M101">
+        <v>67.71542580000001</v>
+      </c>
+      <c r="N101">
+        <v>245.2845742</v>
+      </c>
+      <c r="O101">
+        <v>61.32114355</v>
+      </c>
+      <c r="P101">
+        <v>183.96343065</v>
+      </c>
+      <c r="Q101">
+        <v>269.66343065</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.4577205984511</v>
+      </c>
+      <c r="T101">
+        <v>73.86350447628915</v>
+      </c>
+      <c r="U101">
+        <v>0.0509</v>
+      </c>
+      <c r="V101">
+        <v>0.25</v>
+      </c>
+      <c r="W101">
+        <v>0.038175</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.622285045130736</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mongolia/mongolia_steel.xlsx
+++ b/research/traditional_assets/database/data/mongolia/mongolia_steel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1603925278548756</v>
+        <v>0.1600252965352384</v>
       </c>
       <c r="C2">
-        <v>1193.738983145051</v>
+        <v>1184.884130870867</v>
       </c>
       <c r="D2">
-        <v>915.1389831450508</v>
+        <v>918.0811308708667</v>
       </c>
       <c r="E2">
-        <v>-215.8</v>
+        <v>-204.003</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.797</v>
       </c>
       <c r="G2">
         <v>278.6</v>
@@ -1451,28 +1451,28 @@
         <v>376.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5933891</v>
       </c>
       <c r="N2">
-        <v>376.9</v>
+        <v>376.3066109</v>
       </c>
       <c r="O2">
-        <v>94.22499999999999</v>
+        <v>94.07665272499999</v>
       </c>
       <c r="P2">
-        <v>282.675</v>
+        <v>282.229958175</v>
       </c>
       <c r="Q2">
-        <v>395.675</v>
+        <v>395.229958175</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1603925278548756</v>
+        <v>0.1612606530658974</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161357</v>
+        <v>0.989010983121561</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>635.1650207258609</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1600252965352384</v>
+        <v>0.1596580652156012</v>
       </c>
       <c r="C3">
-        <v>1184.884130870867</v>
+        <v>1176.048257468137</v>
       </c>
       <c r="D3">
-        <v>918.0811308708667</v>
+        <v>921.0422574681374</v>
       </c>
       <c r="E3">
-        <v>-204.003</v>
+        <v>-192.206</v>
       </c>
       <c r="F3">
-        <v>11.797</v>
+        <v>23.594</v>
       </c>
       <c r="G3">
         <v>278.6</v>
@@ -1533,28 +1533,28 @@
         <v>376.9</v>
       </c>
       <c r="M3">
-        <v>0.5933891</v>
+        <v>1.1867782</v>
       </c>
       <c r="N3">
-        <v>376.3066109</v>
+        <v>375.7132218</v>
       </c>
       <c r="O3">
-        <v>94.07665272499999</v>
+        <v>93.92830545</v>
       </c>
       <c r="P3">
-        <v>282.229958175</v>
+        <v>281.78491635</v>
       </c>
       <c r="Q3">
-        <v>395.229958175</v>
+        <v>394.78491635</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1612606530658974</v>
+        <v>0.1621464951179605</v>
       </c>
       <c r="T3">
-        <v>0.989010983121561</v>
+        <v>0.9965989145556684</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>635.1650207258609</v>
+        <v>317.5825103629305</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1596580652156012</v>
+        <v>0.159290833895964</v>
       </c>
       <c r="C4">
-        <v>1176.048257468137</v>
+        <v>1167.231547171196</v>
       </c>
       <c r="D4">
-        <v>921.0422574681374</v>
+        <v>924.022547171196</v>
       </c>
       <c r="E4">
-        <v>-192.206</v>
+        <v>-180.409</v>
       </c>
       <c r="F4">
-        <v>23.594</v>
+        <v>35.391</v>
       </c>
       <c r="G4">
         <v>278.6</v>
@@ -1615,28 +1615,28 @@
         <v>376.9</v>
       </c>
       <c r="M4">
-        <v>1.1867782</v>
+        <v>1.7801673</v>
       </c>
       <c r="N4">
-        <v>375.7132218</v>
+        <v>375.1198327</v>
       </c>
       <c r="O4">
-        <v>93.92830545</v>
+        <v>93.77995817499999</v>
       </c>
       <c r="P4">
-        <v>281.78491635</v>
+        <v>281.339874525</v>
       </c>
       <c r="Q4">
-        <v>394.78491635</v>
+        <v>394.339874525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1621464951179605</v>
+        <v>0.1630506019546021</v>
       </c>
       <c r="T4">
-        <v>0.9965989145556684</v>
+        <v>1.004343298184293</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>317.5825103629305</v>
+        <v>211.721673575287</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.159290833895964</v>
+        <v>0.1589236025763269</v>
       </c>
       <c r="C5">
-        <v>1167.231547171196</v>
+        <v>1158.434186606682</v>
       </c>
       <c r="D5">
-        <v>924.022547171196</v>
+        <v>927.0221866066815</v>
       </c>
       <c r="E5">
-        <v>-180.409</v>
+        <v>-168.612</v>
       </c>
       <c r="F5">
-        <v>35.391</v>
+        <v>47.188</v>
       </c>
       <c r="G5">
         <v>278.6</v>
@@ -1697,28 +1697,28 @@
         <v>376.9</v>
       </c>
       <c r="M5">
-        <v>1.7801673</v>
+        <v>2.3735564</v>
       </c>
       <c r="N5">
-        <v>375.1198327</v>
+        <v>374.5264436</v>
       </c>
       <c r="O5">
-        <v>93.77995817499999</v>
+        <v>93.6316109</v>
       </c>
       <c r="P5">
-        <v>281.339874525</v>
+        <v>280.8948327</v>
       </c>
       <c r="Q5">
-        <v>394.339874525</v>
+        <v>393.8948327</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1630506019546021</v>
+        <v>0.1639735443503405</v>
       </c>
       <c r="T5">
-        <v>1.004343298184293</v>
+        <v>1.012249023138515</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>211.721673575287</v>
+        <v>158.7912551814652</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1589236025763269</v>
+        <v>0.1585563712566897</v>
       </c>
       <c r="C6">
-        <v>1158.434186606682</v>
+        <v>1149.6563648325</v>
       </c>
       <c r="D6">
-        <v>927.0221866066815</v>
+        <v>930.0413648325001</v>
       </c>
       <c r="E6">
-        <v>-168.612</v>
+        <v>-156.815</v>
       </c>
       <c r="F6">
-        <v>47.188</v>
+        <v>58.98500000000001</v>
       </c>
       <c r="G6">
         <v>278.6</v>
@@ -1779,28 +1779,28 @@
         <v>376.9</v>
       </c>
       <c r="M6">
-        <v>2.3735564</v>
+        <v>2.9669455</v>
       </c>
       <c r="N6">
-        <v>374.5264436</v>
+        <v>373.9330545</v>
       </c>
       <c r="O6">
-        <v>93.6316109</v>
+        <v>93.48326362499999</v>
       </c>
       <c r="P6">
-        <v>280.8948327</v>
+        <v>280.449790875</v>
       </c>
       <c r="Q6">
-        <v>393.8948327</v>
+        <v>393.449790875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1639735443503405</v>
+        <v>0.164915917112305</v>
       </c>
       <c r="T6">
-        <v>1.012249023138515</v>
+        <v>1.020321184407562</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>158.7912551814652</v>
+        <v>127.0330041451722</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1585563712566897</v>
+        <v>0.1581891399370525</v>
       </c>
       <c r="C7">
-        <v>1149.6563648325</v>
+        <v>1140.898273377542</v>
       </c>
       <c r="D7">
-        <v>930.0413648325001</v>
+        <v>933.0802733775421</v>
       </c>
       <c r="E7">
-        <v>-156.815</v>
+        <v>-145.018</v>
       </c>
       <c r="F7">
-        <v>58.98500000000001</v>
+        <v>70.78200000000001</v>
       </c>
       <c r="G7">
         <v>278.6</v>
@@ -1861,28 +1861,28 @@
         <v>376.9</v>
       </c>
       <c r="M7">
-        <v>2.9669455</v>
+        <v>3.5603346</v>
       </c>
       <c r="N7">
-        <v>373.9330545</v>
+        <v>373.3396654</v>
       </c>
       <c r="O7">
-        <v>93.48326362499999</v>
+        <v>93.33491635</v>
       </c>
       <c r="P7">
-        <v>280.449790875</v>
+        <v>280.00474905</v>
       </c>
       <c r="Q7">
-        <v>393.449790875</v>
+        <v>393.00474905</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.164915917112305</v>
+        <v>0.1658783403585665</v>
       </c>
       <c r="T7">
-        <v>1.020321184407562</v>
+        <v>1.028565093788717</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>127.0330041451722</v>
+        <v>105.8608367876435</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1581891399370525</v>
+        <v>0.1578219086174153</v>
       </c>
       <c r="C8">
-        <v>1140.898273377542</v>
+        <v>1132.160106282185</v>
       </c>
       <c r="D8">
-        <v>933.0802733775421</v>
+        <v>936.1391062821851</v>
       </c>
       <c r="E8">
-        <v>-145.018</v>
+        <v>-133.221</v>
       </c>
       <c r="F8">
-        <v>70.782</v>
+        <v>82.57899999999999</v>
       </c>
       <c r="G8">
         <v>278.6</v>
@@ -1943,28 +1943,28 @@
         <v>376.9</v>
       </c>
       <c r="M8">
-        <v>3.5603346</v>
+        <v>4.1537237</v>
       </c>
       <c r="N8">
-        <v>373.3396654</v>
+        <v>372.7462763</v>
       </c>
       <c r="O8">
-        <v>93.33491635</v>
+        <v>93.18656907499999</v>
       </c>
       <c r="P8">
-        <v>280.00474905</v>
+        <v>279.559707225</v>
       </c>
       <c r="Q8">
-        <v>393.00474905</v>
+        <v>392.559707225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1658783403585665</v>
+        <v>0.1668614608789412</v>
       </c>
       <c r="T8">
-        <v>1.028565093788717</v>
+        <v>1.036986291543659</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>105.8608367876435</v>
+        <v>90.73786010369443</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1578219086174153</v>
+        <v>0.1574546772977782</v>
       </c>
       <c r="C9">
-        <v>1132.160106282185</v>
+        <v>1123.442060139596</v>
       </c>
       <c r="D9">
-        <v>936.1391062821851</v>
+        <v>939.2180601395961</v>
       </c>
       <c r="E9">
-        <v>-133.221</v>
+        <v>-121.424</v>
       </c>
       <c r="F9">
-        <v>82.57900000000001</v>
+        <v>94.376</v>
       </c>
       <c r="G9">
         <v>278.6</v>
@@ -2025,28 +2025,28 @@
         <v>376.9</v>
       </c>
       <c r="M9">
-        <v>4.1537237</v>
+        <v>4.7471128</v>
       </c>
       <c r="N9">
-        <v>372.7462763</v>
+        <v>372.1528872</v>
       </c>
       <c r="O9">
-        <v>93.18656907499999</v>
+        <v>93.03822179999999</v>
       </c>
       <c r="P9">
-        <v>279.559707225</v>
+        <v>279.1146654</v>
       </c>
       <c r="Q9">
-        <v>392.559707225</v>
+        <v>392.1146654</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1668614608789412</v>
+        <v>0.1678659535845415</v>
       </c>
       <c r="T9">
-        <v>1.036986291543659</v>
+        <v>1.045590558815014</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>90.73786010369442</v>
+        <v>79.39562759073262</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1574546772977782</v>
+        <v>0.1570874459781409</v>
       </c>
       <c r="C10">
-        <v>1123.442060139596</v>
+        <v>1114.744334137851</v>
       </c>
       <c r="D10">
-        <v>939.2180601395961</v>
+        <v>942.3173341378504</v>
       </c>
       <c r="E10">
-        <v>-121.424</v>
+        <v>-109.627</v>
       </c>
       <c r="F10">
-        <v>94.376</v>
+        <v>106.173</v>
       </c>
       <c r="G10">
         <v>278.6</v>
@@ -2107,28 +2107,28 @@
         <v>376.9</v>
       </c>
       <c r="M10">
-        <v>4.7471128</v>
+        <v>5.3405019</v>
       </c>
       <c r="N10">
-        <v>372.1528872</v>
+        <v>371.5594981</v>
       </c>
       <c r="O10">
-        <v>93.03822179999999</v>
+        <v>92.889874525</v>
       </c>
       <c r="P10">
-        <v>279.1146654</v>
+        <v>278.669623575</v>
       </c>
       <c r="Q10">
-        <v>392.1146654</v>
+        <v>391.669623575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1678659535845415</v>
+        <v>0.1688925230529021</v>
       </c>
       <c r="T10">
-        <v>1.045590558815014</v>
+        <v>1.054383930861563</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>79.39562759073262</v>
+        <v>70.57389119176233</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1570874459781409</v>
+        <v>0.1567202146585037</v>
       </c>
       <c r="C11">
-        <v>1114.744334137851</v>
+        <v>1106.067130102886</v>
       </c>
       <c r="D11">
-        <v>942.3173341378504</v>
+        <v>945.4371301028856</v>
       </c>
       <c r="E11">
-        <v>-109.627</v>
+        <v>-97.83000000000001</v>
       </c>
       <c r="F11">
-        <v>106.173</v>
+        <v>117.97</v>
       </c>
       <c r="G11">
         <v>278.6</v>
@@ -2189,28 +2189,28 @@
         <v>376.9</v>
       </c>
       <c r="M11">
-        <v>5.3405019</v>
+        <v>5.933891</v>
       </c>
       <c r="N11">
-        <v>371.5594981</v>
+        <v>370.966109</v>
       </c>
       <c r="O11">
-        <v>92.889874525</v>
+        <v>92.74152724999999</v>
       </c>
       <c r="P11">
-        <v>278.669623575</v>
+        <v>278.22458175</v>
       </c>
       <c r="Q11">
-        <v>391.669623575</v>
+        <v>391.22458175</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1688925230529021</v>
+        <v>0.1699419051761153</v>
       </c>
       <c r="T11">
-        <v>1.054383930861563</v>
+        <v>1.063372711175814</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>70.57389119176233</v>
+        <v>63.51650207258609</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1567202146585037</v>
+        <v>0.1563529833388666</v>
       </c>
       <c r="C12">
-        <v>1106.067130102886</v>
+        <v>1097.410652542316</v>
       </c>
       <c r="D12">
-        <v>945.4371301028856</v>
+        <v>948.5776525423156</v>
       </c>
       <c r="E12">
-        <v>-97.83</v>
+        <v>-86.03300000000002</v>
       </c>
       <c r="F12">
-        <v>117.97</v>
+        <v>129.767</v>
       </c>
       <c r="G12">
         <v>278.6</v>
@@ -2271,28 +2271,28 @@
         <v>376.9</v>
       </c>
       <c r="M12">
-        <v>5.933891</v>
+        <v>6.5272801</v>
       </c>
       <c r="N12">
-        <v>370.966109</v>
+        <v>370.3727199</v>
       </c>
       <c r="O12">
-        <v>92.74152724999999</v>
+        <v>92.593179975</v>
       </c>
       <c r="P12">
-        <v>278.22458175</v>
+        <v>277.779539925</v>
       </c>
       <c r="Q12">
-        <v>391.22458175</v>
+        <v>390.779539925</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1699419051761153</v>
+        <v>0.1710148689200748</v>
       </c>
       <c r="T12">
-        <v>1.063372711175814</v>
+        <v>1.072563486553306</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>63.51650207258609</v>
+        <v>57.74227461144191</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1563529833388666</v>
+        <v>0.1559857520192294</v>
       </c>
       <c r="C13">
-        <v>1097.410652542316</v>
+        <v>1088.775108690118</v>
       </c>
       <c r="D13">
-        <v>948.5776525423156</v>
+        <v>951.7391086901184</v>
       </c>
       <c r="E13">
-        <v>-86.03300000000002</v>
+        <v>-74.23600000000002</v>
       </c>
       <c r="F13">
-        <v>129.767</v>
+        <v>141.564</v>
       </c>
       <c r="G13">
         <v>278.6</v>
@@ -2353,28 +2353,28 @@
         <v>376.9</v>
       </c>
       <c r="M13">
-        <v>6.5272801</v>
+        <v>7.120669199999999</v>
       </c>
       <c r="N13">
-        <v>370.3727199</v>
+        <v>369.7793308</v>
       </c>
       <c r="O13">
-        <v>92.593179975</v>
+        <v>92.44483269999999</v>
       </c>
       <c r="P13">
-        <v>277.779539925</v>
+        <v>277.3344981</v>
       </c>
       <c r="Q13">
-        <v>390.779539925</v>
+        <v>390.3344981</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1710148689200748</v>
+        <v>0.1721122182036698</v>
       </c>
       <c r="T13">
-        <v>1.072563486553306</v>
+        <v>1.081963143189377</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>57.74227461144191</v>
+        <v>52.93041839382175</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1559857520192294</v>
+        <v>0.1556185206995922</v>
       </c>
       <c r="C14">
-        <v>1088.775108690118</v>
+        <v>1080.160708552219</v>
       </c>
       <c r="D14">
-        <v>951.7391086901184</v>
+        <v>954.9217085522189</v>
       </c>
       <c r="E14">
-        <v>-74.23600000000002</v>
+        <v>-62.43899999999999</v>
       </c>
       <c r="F14">
-        <v>141.564</v>
+        <v>153.361</v>
       </c>
       <c r="G14">
         <v>278.6</v>
@@ -2435,28 +2435,28 @@
         <v>376.9</v>
       </c>
       <c r="M14">
-        <v>7.120669199999999</v>
+        <v>7.7140583</v>
       </c>
       <c r="N14">
-        <v>369.7793308</v>
+        <v>369.1859417</v>
       </c>
       <c r="O14">
-        <v>92.44483269999999</v>
+        <v>92.296485425</v>
       </c>
       <c r="P14">
-        <v>277.3344981</v>
+        <v>276.889456275</v>
       </c>
       <c r="Q14">
-        <v>390.3344981</v>
+        <v>389.889456275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1721122182036698</v>
+        <v>0.1732347939075772</v>
       </c>
       <c r="T14">
-        <v>1.081963143189377</v>
+        <v>1.091578883886047</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>52.93041839382175</v>
+        <v>48.85884774814315</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1556185206995922</v>
+        <v>0.155251289379955</v>
       </c>
       <c r="C15">
-        <v>1080.160708552219</v>
+        <v>1071.567664952993</v>
       </c>
       <c r="D15">
-        <v>954.9217085522189</v>
+        <v>958.1256649529927</v>
       </c>
       <c r="E15">
-        <v>-62.43899999999999</v>
+        <v>-50.642</v>
       </c>
       <c r="F15">
-        <v>153.361</v>
+        <v>165.158</v>
       </c>
       <c r="G15">
         <v>278.6</v>
@@ -2517,28 +2517,28 @@
         <v>376.9</v>
       </c>
       <c r="M15">
-        <v>7.7140583</v>
+        <v>8.307447400000001</v>
       </c>
       <c r="N15">
-        <v>369.1859417</v>
+        <v>368.5925526</v>
       </c>
       <c r="O15">
-        <v>92.296485425</v>
+        <v>92.14813814999999</v>
       </c>
       <c r="P15">
-        <v>276.889456275</v>
+        <v>276.44441445</v>
       </c>
       <c r="Q15">
-        <v>389.889456275</v>
+        <v>389.44441445</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1732347939075772</v>
+        <v>0.1743834760232035</v>
       </c>
       <c r="T15">
-        <v>1.091578883886047</v>
+        <v>1.101418246459385</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>48.85884774814315</v>
+        <v>45.36893005184721</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.155251289379955</v>
+        <v>0.1548840580603178</v>
       </c>
       <c r="C16">
-        <v>1071.567664952993</v>
+        <v>1062.996193582706</v>
       </c>
       <c r="D16">
-        <v>958.1256649529927</v>
+        <v>961.3511935827065</v>
       </c>
       <c r="E16">
-        <v>-50.642</v>
+        <v>-38.84499999999997</v>
       </c>
       <c r="F16">
-        <v>165.158</v>
+        <v>176.955</v>
       </c>
       <c r="G16">
         <v>278.6</v>
@@ -2599,28 +2599,28 @@
         <v>376.9</v>
       </c>
       <c r="M16">
-        <v>8.307447400000001</v>
+        <v>8.900836500000002</v>
       </c>
       <c r="N16">
-        <v>368.5925526</v>
+        <v>367.9991635</v>
       </c>
       <c r="O16">
-        <v>92.14813814999999</v>
+        <v>91.99979087499999</v>
       </c>
       <c r="P16">
-        <v>276.44441445</v>
+        <v>275.999372625</v>
       </c>
       <c r="Q16">
-        <v>389.44441445</v>
+        <v>388.999372625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1743834760232035</v>
+        <v>0.1755591859533151</v>
       </c>
       <c r="T16">
-        <v>1.101418246459385</v>
+        <v>1.111489123446213</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>45.36893005184721</v>
+        <v>42.34433471505739</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1548840580603178</v>
+        <v>0.1545168267406806</v>
       </c>
       <c r="C17">
-        <v>1062.996193582707</v>
+        <v>1054.446513045923</v>
       </c>
       <c r="D17">
-        <v>961.3511935827065</v>
+        <v>964.5985130459233</v>
       </c>
       <c r="E17">
-        <v>-38.845</v>
+        <v>-27.048</v>
       </c>
       <c r="F17">
-        <v>176.955</v>
+        <v>188.752</v>
       </c>
       <c r="G17">
         <v>278.6</v>
@@ -2681,28 +2681,28 @@
         <v>376.9</v>
       </c>
       <c r="M17">
-        <v>8.9008365</v>
+        <v>9.4942256</v>
       </c>
       <c r="N17">
-        <v>367.9991635</v>
+        <v>367.4057744</v>
       </c>
       <c r="O17">
-        <v>91.99979087499999</v>
+        <v>91.8514436</v>
       </c>
       <c r="P17">
-        <v>275.999372625</v>
+        <v>275.5543308</v>
       </c>
       <c r="Q17">
-        <v>388.999372625</v>
+        <v>388.5543308</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1755591859533151</v>
+        <v>0.1767628889770007</v>
       </c>
       <c r="T17">
-        <v>1.111489123446213</v>
+        <v>1.121799783218441</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>42.34433471505739</v>
+        <v>39.69781379536631</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1545168267406806</v>
+        <v>0.1541495954210435</v>
       </c>
       <c r="C18">
-        <v>1054.446513045923</v>
+        <v>1045.918844910887</v>
       </c>
       <c r="D18">
-        <v>964.5985130459233</v>
+        <v>967.8678449108868</v>
       </c>
       <c r="E18">
-        <v>-27.048</v>
+        <v>-15.25099999999998</v>
       </c>
       <c r="F18">
-        <v>188.752</v>
+        <v>200.549</v>
       </c>
       <c r="G18">
         <v>278.6</v>
@@ -2763,28 +2763,28 @@
         <v>376.9</v>
       </c>
       <c r="M18">
-        <v>9.4942256</v>
+        <v>10.0876147</v>
       </c>
       <c r="N18">
-        <v>367.4057744</v>
+        <v>366.8123853</v>
       </c>
       <c r="O18">
-        <v>91.8514436</v>
+        <v>91.70309632499999</v>
       </c>
       <c r="P18">
-        <v>275.5543308</v>
+        <v>275.109288975</v>
       </c>
       <c r="Q18">
-        <v>388.5543308</v>
+        <v>388.109288975</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1767628889770007</v>
+        <v>0.1779955968928234</v>
       </c>
       <c r="T18">
-        <v>1.121799783218441</v>
+        <v>1.132358892623735</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>39.69781379536631</v>
+        <v>37.36264827799182</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1541495954210435</v>
+        <v>0.1537823641014062</v>
       </c>
       <c r="C19">
-        <v>1045.918844910887</v>
+        <v>1037.413413759919</v>
       </c>
       <c r="D19">
-        <v>967.8678449108868</v>
+        <v>971.1594137599188</v>
       </c>
       <c r="E19">
-        <v>-15.25099999999998</v>
+        <v>-3.453999999999979</v>
       </c>
       <c r="F19">
-        <v>200.549</v>
+        <v>212.346</v>
       </c>
       <c r="G19">
         <v>278.6</v>
@@ -2845,28 +2845,28 @@
         <v>376.9</v>
       </c>
       <c r="M19">
-        <v>10.0876147</v>
+        <v>10.6810038</v>
       </c>
       <c r="N19">
-        <v>366.8123853</v>
+        <v>366.2189962</v>
       </c>
       <c r="O19">
-        <v>91.70309632499999</v>
+        <v>91.55474905</v>
       </c>
       <c r="P19">
-        <v>275.109288975</v>
+        <v>274.66424715</v>
       </c>
       <c r="Q19">
-        <v>388.109288975</v>
+        <v>387.66424715</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1779955968928234</v>
+        <v>0.1792583708553735</v>
       </c>
       <c r="T19">
-        <v>1.132358892623735</v>
+        <v>1.143175541282816</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>37.36264827799182</v>
+        <v>35.28694559588116</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1537823641014062</v>
+        <v>0.1534151327817691</v>
       </c>
       <c r="C20">
-        <v>1037.413413759919</v>
+        <v>1028.930447240845</v>
       </c>
       <c r="D20">
-        <v>971.1594137599188</v>
+        <v>974.473447240845</v>
       </c>
       <c r="E20">
-        <v>-3.454000000000008</v>
+        <v>8.342999999999989</v>
       </c>
       <c r="F20">
-        <v>212.346</v>
+        <v>224.143</v>
       </c>
       <c r="G20">
         <v>278.6</v>
@@ -2927,28 +2927,28 @@
         <v>376.9</v>
       </c>
       <c r="M20">
-        <v>10.6810038</v>
+        <v>11.2743929</v>
       </c>
       <c r="N20">
-        <v>366.2189962</v>
+        <v>365.6256071</v>
       </c>
       <c r="O20">
-        <v>91.55474905</v>
+        <v>91.40640177499999</v>
       </c>
       <c r="P20">
-        <v>274.66424715</v>
+        <v>274.219205325</v>
       </c>
       <c r="Q20">
-        <v>387.66424715</v>
+        <v>387.219205325</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1792583708553735</v>
+        <v>0.1805523244219371</v>
       </c>
       <c r="T20">
-        <v>1.143175541282816</v>
+        <v>1.154259267686567</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>35.28694559588117</v>
+        <v>33.42973793294005</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1534151327817691</v>
+        <v>0.1530479014621319</v>
       </c>
       <c r="C21">
-        <v>1028.930447240845</v>
+        <v>1020.47017611948</v>
       </c>
       <c r="D21">
-        <v>974.473447240845</v>
+        <v>977.8101761194798</v>
       </c>
       <c r="E21">
-        <v>8.342999999999989</v>
+        <v>20.14000000000001</v>
       </c>
       <c r="F21">
-        <v>224.143</v>
+        <v>235.94</v>
       </c>
       <c r="G21">
         <v>278.6</v>
@@ -3009,28 +3009,28 @@
         <v>376.9</v>
       </c>
       <c r="M21">
-        <v>11.2743929</v>
+        <v>11.867782</v>
       </c>
       <c r="N21">
-        <v>365.6256071</v>
+        <v>365.032218</v>
       </c>
       <c r="O21">
-        <v>91.40640177499999</v>
+        <v>91.2580545</v>
       </c>
       <c r="P21">
-        <v>274.219205325</v>
+        <v>273.7741635</v>
       </c>
       <c r="Q21">
-        <v>387.219205325</v>
+        <v>386.7741635</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1805523244219371</v>
+        <v>0.1818786268276648</v>
       </c>
       <c r="T21">
-        <v>1.154259267686567</v>
+        <v>1.165620087250411</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>33.42973793294005</v>
+        <v>31.75825103629305</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1530479014621319</v>
+        <v>0.1526806701424947</v>
       </c>
       <c r="C22">
-        <v>1020.47017611948</v>
+        <v>1012.032834333189</v>
       </c>
       <c r="D22">
-        <v>977.8101761194798</v>
+        <v>981.1698343331896</v>
       </c>
       <c r="E22">
-        <v>20.14000000000001</v>
+        <v>31.93700000000001</v>
       </c>
       <c r="F22">
-        <v>235.94</v>
+        <v>247.737</v>
       </c>
       <c r="G22">
         <v>278.6</v>
@@ -3091,28 +3091,28 @@
         <v>376.9</v>
       </c>
       <c r="M22">
-        <v>11.867782</v>
+        <v>12.4611711</v>
       </c>
       <c r="N22">
-        <v>365.032218</v>
+        <v>364.4388289</v>
       </c>
       <c r="O22">
-        <v>91.2580545</v>
+        <v>91.10970722499999</v>
       </c>
       <c r="P22">
-        <v>273.7741635</v>
+        <v>273.329121675</v>
       </c>
       <c r="Q22">
-        <v>386.7741635</v>
+        <v>386.329121675</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1818786268276648</v>
+        <v>0.1832385065094869</v>
       </c>
       <c r="T22">
-        <v>1.165620087250411</v>
+        <v>1.177268522499416</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>31.75825103629305</v>
+        <v>30.24595336789814</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1526806701424947</v>
+        <v>0.1523134388228575</v>
       </c>
       <c r="C23">
-        <v>1012.032834333189</v>
+        <v>1003.618659045568</v>
       </c>
       <c r="D23">
-        <v>981.1698343331896</v>
+        <v>984.5526590455684</v>
       </c>
       <c r="E23">
-        <v>31.93699999999998</v>
+        <v>43.73399999999998</v>
       </c>
       <c r="F23">
-        <v>247.737</v>
+        <v>259.534</v>
       </c>
       <c r="G23">
         <v>278.6</v>
@@ -3173,28 +3173,28 @@
         <v>376.9</v>
       </c>
       <c r="M23">
-        <v>12.4611711</v>
+        <v>13.0545602</v>
       </c>
       <c r="N23">
-        <v>364.4388289</v>
+        <v>363.8454398</v>
       </c>
       <c r="O23">
-        <v>91.10970722499999</v>
+        <v>90.96135994999999</v>
       </c>
       <c r="P23">
-        <v>273.329121675</v>
+        <v>272.88407985</v>
       </c>
       <c r="Q23">
-        <v>386.329121675</v>
+        <v>385.88407985</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1832385065094869</v>
+        <v>0.1846332549010993</v>
       </c>
       <c r="T23">
-        <v>1.177268522499416</v>
+        <v>1.189215635575318</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>30.24595336789814</v>
+        <v>28.87113730572095</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1523134388228575</v>
+        <v>0.1519462075032203</v>
       </c>
       <c r="C24">
-        <v>1003.618659045568</v>
+        <v>995.2278907022447</v>
       </c>
       <c r="D24">
-        <v>984.5526590455684</v>
+        <v>987.9588907022447</v>
       </c>
       <c r="E24">
-        <v>43.73399999999998</v>
+        <v>55.53100000000001</v>
       </c>
       <c r="F24">
-        <v>259.534</v>
+        <v>271.331</v>
       </c>
       <c r="G24">
         <v>278.6</v>
@@ -3255,28 +3255,28 @@
         <v>376.9</v>
       </c>
       <c r="M24">
-        <v>13.0545602</v>
+        <v>13.6479493</v>
       </c>
       <c r="N24">
-        <v>363.8454398</v>
+        <v>363.2520507</v>
       </c>
       <c r="O24">
-        <v>90.96135994999999</v>
+        <v>90.813012675</v>
       </c>
       <c r="P24">
-        <v>272.88407985</v>
+        <v>272.439038025</v>
       </c>
       <c r="Q24">
-        <v>385.88407985</v>
+        <v>385.439038025</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1846332549010993</v>
+        <v>0.1860642305236627</v>
       </c>
       <c r="T24">
-        <v>1.189215635575318</v>
+        <v>1.201473063276569</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>28.87113730572095</v>
+        <v>27.61587046634178</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1519462075032203</v>
+        <v>0.1515789761835831</v>
       </c>
       <c r="C25">
-        <v>995.2278907022447</v>
+        <v>986.860773087854</v>
       </c>
       <c r="D25">
-        <v>987.9588907022447</v>
+        <v>991.3887730878539</v>
       </c>
       <c r="E25">
-        <v>55.53100000000001</v>
+        <v>67.32800000000003</v>
       </c>
       <c r="F25">
-        <v>271.331</v>
+        <v>283.128</v>
       </c>
       <c r="G25">
         <v>278.6</v>
@@ -3337,28 +3337,28 @@
         <v>376.9</v>
       </c>
       <c r="M25">
-        <v>13.6479493</v>
+        <v>14.2413384</v>
       </c>
       <c r="N25">
-        <v>363.2520507</v>
+        <v>362.6586616</v>
       </c>
       <c r="O25">
-        <v>90.813012675</v>
+        <v>90.66466539999999</v>
       </c>
       <c r="P25">
-        <v>272.439038025</v>
+        <v>271.9939962</v>
       </c>
       <c r="Q25">
-        <v>385.439038025</v>
+        <v>384.9939962</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1860642305236627</v>
+        <v>0.1875328633994515</v>
       </c>
       <c r="T25">
-        <v>1.201473063276569</v>
+        <v>1.214053054864694</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>27.61587046634178</v>
+        <v>26.46520919691087</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1515789761835831</v>
+        <v>0.151211744863946</v>
       </c>
       <c r="C26">
-        <v>986.8607730878541</v>
+        <v>978.5175533841998</v>
       </c>
       <c r="D26">
-        <v>991.3887730878539</v>
+        <v>994.8425533841997</v>
       </c>
       <c r="E26">
-        <v>67.32799999999997</v>
+        <v>79.125</v>
       </c>
       <c r="F26">
-        <v>283.128</v>
+        <v>294.925</v>
       </c>
       <c r="G26">
         <v>278.6</v>
@@ -3419,28 +3419,28 @@
         <v>376.9</v>
       </c>
       <c r="M26">
-        <v>14.2413384</v>
+        <v>14.8347275</v>
       </c>
       <c r="N26">
-        <v>362.6586616</v>
+        <v>362.0652725</v>
       </c>
       <c r="O26">
-        <v>90.66466539999999</v>
+        <v>90.516318125</v>
       </c>
       <c r="P26">
-        <v>271.9939962</v>
+        <v>271.548954375</v>
       </c>
       <c r="Q26">
-        <v>384.9939962</v>
+        <v>384.548954375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1875328633994515</v>
+        <v>0.1890406598185946</v>
       </c>
       <c r="T26">
-        <v>1.214053054864694</v>
+        <v>1.22696851289517</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>26.46520919691087</v>
+        <v>25.40660082903444</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.151211744863946</v>
+        <v>0.1508445135443088</v>
       </c>
       <c r="C27">
-        <v>978.5175533841998</v>
+        <v>970.1984822296356</v>
       </c>
       <c r="D27">
-        <v>994.8425533841997</v>
+        <v>998.3204822296357</v>
       </c>
       <c r="E27">
-        <v>79.125</v>
+        <v>90.92200000000003</v>
       </c>
       <c r="F27">
-        <v>294.925</v>
+        <v>306.722</v>
       </c>
       <c r="G27">
         <v>278.6</v>
@@ -3501,28 +3501,28 @@
         <v>376.9</v>
       </c>
       <c r="M27">
-        <v>14.8347275</v>
+        <v>15.4281166</v>
       </c>
       <c r="N27">
-        <v>362.0652725</v>
+        <v>361.4718834</v>
       </c>
       <c r="O27">
-        <v>90.516318125</v>
+        <v>90.36797084999999</v>
       </c>
       <c r="P27">
-        <v>271.548954375</v>
+        <v>271.10391255</v>
       </c>
       <c r="Q27">
-        <v>384.548954375</v>
+        <v>384.10391255</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1890406598185946</v>
+        <v>0.1905892074923091</v>
       </c>
       <c r="T27">
-        <v>1.22696851289517</v>
+        <v>1.240233037358901</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>25.40660082903444</v>
+        <v>24.42942387407157</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1508445135443088</v>
+        <v>0.1504772822246715</v>
       </c>
       <c r="C28">
-        <v>970.1984822296356</v>
+        <v>961.9038137796958</v>
       </c>
       <c r="D28">
-        <v>998.3204822296357</v>
+        <v>1001.822813779696</v>
       </c>
       <c r="E28">
-        <v>90.92200000000003</v>
+        <v>102.719</v>
       </c>
       <c r="F28">
-        <v>306.722</v>
+        <v>318.519</v>
       </c>
       <c r="G28">
         <v>278.6</v>
@@ -3583,28 +3583,28 @@
         <v>376.9</v>
       </c>
       <c r="M28">
-        <v>15.4281166</v>
+        <v>16.0215057</v>
       </c>
       <c r="N28">
-        <v>361.4718834</v>
+        <v>360.8784943</v>
       </c>
       <c r="O28">
-        <v>90.36797084999999</v>
+        <v>90.219623575</v>
       </c>
       <c r="P28">
-        <v>271.10391255</v>
+        <v>270.658870725</v>
       </c>
       <c r="Q28">
-        <v>384.10391255</v>
+        <v>383.658870725</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1905892074923091</v>
+        <v>0.1921801811296871</v>
       </c>
       <c r="T28">
-        <v>1.240233037358901</v>
+        <v>1.253860973451776</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>24.42942387407157</v>
+        <v>23.52463039725411</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1504772822246715</v>
+        <v>0.1501100509050343</v>
       </c>
       <c r="C29">
-        <v>961.9038137796958</v>
+        <v>953.6338057690098</v>
       </c>
       <c r="D29">
-        <v>1001.822813779696</v>
+        <v>1005.34980576901</v>
       </c>
       <c r="E29">
-        <v>102.719</v>
+        <v>114.516</v>
       </c>
       <c r="F29">
-        <v>318.519</v>
+        <v>330.316</v>
       </c>
       <c r="G29">
         <v>278.6</v>
@@ -3665,28 +3665,28 @@
         <v>376.9</v>
       </c>
       <c r="M29">
-        <v>16.0215057</v>
+        <v>16.6148948</v>
       </c>
       <c r="N29">
-        <v>360.8784943</v>
+        <v>360.2851052</v>
       </c>
       <c r="O29">
-        <v>90.219623575</v>
+        <v>90.07127629999999</v>
       </c>
       <c r="P29">
-        <v>270.658870725</v>
+        <v>270.2138289</v>
       </c>
       <c r="Q29">
-        <v>383.658870725</v>
+        <v>383.2138289</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1921801811296871</v>
+        <v>0.1938153484792144</v>
       </c>
       <c r="T29">
-        <v>1.253860973451776</v>
+        <v>1.267867463325009</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>23.52463039725411</v>
+        <v>22.6844650259236</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1501100509050343</v>
+        <v>0.1497428195853972</v>
       </c>
       <c r="C30">
-        <v>953.6338057690098</v>
+        <v>945.3887195745247</v>
       </c>
       <c r="D30">
-        <v>1005.34980576901</v>
+        <v>1008.901719574525</v>
       </c>
       <c r="E30">
-        <v>114.516</v>
+        <v>126.313</v>
       </c>
       <c r="F30">
-        <v>330.316</v>
+        <v>342.1130000000001</v>
       </c>
       <c r="G30">
         <v>278.6</v>
@@ -3747,28 +3747,28 @@
         <v>376.9</v>
       </c>
       <c r="M30">
-        <v>16.6148948</v>
+        <v>17.2082839</v>
       </c>
       <c r="N30">
-        <v>360.2851052</v>
+        <v>359.6917161</v>
       </c>
       <c r="O30">
-        <v>90.07127629999999</v>
+        <v>89.92292902499999</v>
       </c>
       <c r="P30">
-        <v>270.2138289</v>
+        <v>269.768787075</v>
       </c>
       <c r="Q30">
-        <v>383.2138289</v>
+        <v>382.768787075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1938153484792144</v>
+        <v>0.1954965768808411</v>
       </c>
       <c r="T30">
-        <v>1.267867463325009</v>
+        <v>1.282268502208755</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>22.6844650259236</v>
+        <v>21.9022420939952</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1497428195853971</v>
+        <v>0.14937558826576</v>
       </c>
       <c r="C31">
-        <v>945.3887195745249</v>
+        <v>937.1688202800785</v>
       </c>
       <c r="D31">
-        <v>1008.901719574525</v>
+        <v>1012.478820280078</v>
       </c>
       <c r="E31">
-        <v>126.313</v>
+        <v>138.11</v>
       </c>
       <c r="F31">
-        <v>342.113</v>
+        <v>353.91</v>
       </c>
       <c r="G31">
         <v>278.6</v>
@@ -3829,28 +3829,28 @@
         <v>376.9</v>
       </c>
       <c r="M31">
-        <v>17.2082839</v>
+        <v>17.801673</v>
       </c>
       <c r="N31">
-        <v>359.6917161</v>
+        <v>359.098327</v>
       </c>
       <c r="O31">
-        <v>89.922929025</v>
+        <v>89.77458175</v>
       </c>
       <c r="P31">
-        <v>269.768787075</v>
+        <v>269.32374525</v>
       </c>
       <c r="Q31">
-        <v>382.768787075</v>
+        <v>382.32374525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1954965768808411</v>
+        <v>0.1972258403796571</v>
       </c>
       <c r="T31">
-        <v>1.282268502208755</v>
+        <v>1.297080999346322</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>21.90224209399521</v>
+        <v>21.1721673575287</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.14937558826576</v>
+        <v>0.1490083569461228</v>
       </c>
       <c r="C32">
-        <v>937.1688202800785</v>
+        <v>928.974376742345</v>
       </c>
       <c r="D32">
-        <v>1012.478820280078</v>
+        <v>1016.081376742345</v>
       </c>
       <c r="E32">
-        <v>138.11</v>
+        <v>149.907</v>
       </c>
       <c r="F32">
-        <v>353.91</v>
+        <v>365.707</v>
       </c>
       <c r="G32">
         <v>278.6</v>
@@ -3911,28 +3911,28 @@
         <v>376.9</v>
       </c>
       <c r="M32">
-        <v>17.801673</v>
+        <v>18.3950621</v>
       </c>
       <c r="N32">
-        <v>359.098327</v>
+        <v>358.5049379</v>
       </c>
       <c r="O32">
-        <v>89.77458175</v>
+        <v>89.62623447499999</v>
       </c>
       <c r="P32">
-        <v>269.32374525</v>
+        <v>268.878703425</v>
       </c>
       <c r="Q32">
-        <v>382.32374525</v>
+        <v>381.878703425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1972258403796571</v>
+        <v>0.199005227458149</v>
       </c>
       <c r="T32">
-        <v>1.297080999346322</v>
+        <v>1.312322844227007</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.1721673575287</v>
+        <v>20.48919421696326</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1490083569461228</v>
+        <v>0.1486411256264856</v>
       </c>
       <c r="C33">
-        <v>928.974376742345</v>
+        <v>920.8056616581974</v>
       </c>
       <c r="D33">
-        <v>1016.081376742345</v>
+        <v>1019.709661658197</v>
       </c>
       <c r="E33">
-        <v>149.907</v>
+        <v>161.704</v>
       </c>
       <c r="F33">
-        <v>365.707</v>
+        <v>377.504</v>
       </c>
       <c r="G33">
         <v>278.6</v>
@@ -3993,28 +3993,28 @@
         <v>376.9</v>
       </c>
       <c r="M33">
-        <v>18.3950621</v>
+        <v>18.9884512</v>
       </c>
       <c r="N33">
-        <v>358.5049379</v>
+        <v>357.9115488</v>
       </c>
       <c r="O33">
-        <v>89.62623447499999</v>
+        <v>89.4778872</v>
       </c>
       <c r="P33">
-        <v>268.878703425</v>
+        <v>268.4336616</v>
       </c>
       <c r="Q33">
-        <v>381.878703425</v>
+        <v>381.4336616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.199005227458149</v>
+        <v>0.2008369494507141</v>
       </c>
       <c r="T33">
-        <v>1.312322844227007</v>
+        <v>1.328012978663007</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>20.48919421696326</v>
+        <v>19.84890689768315</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1486411256264856</v>
+        <v>0.1482738943068484</v>
       </c>
       <c r="C34">
-        <v>920.8056616581974</v>
+        <v>912.6629516335178</v>
       </c>
       <c r="D34">
-        <v>1019.709661658197</v>
+        <v>1023.363951633518</v>
       </c>
       <c r="E34">
-        <v>161.704</v>
+        <v>173.501</v>
       </c>
       <c r="F34">
-        <v>377.504</v>
+        <v>389.301</v>
       </c>
       <c r="G34">
         <v>278.6</v>
@@ -4075,28 +4075,28 @@
         <v>376.9</v>
       </c>
       <c r="M34">
-        <v>18.9884512</v>
+        <v>19.5818403</v>
       </c>
       <c r="N34">
-        <v>357.9115488</v>
+        <v>357.3181597</v>
       </c>
       <c r="O34">
-        <v>89.4778872</v>
+        <v>89.32953992499999</v>
       </c>
       <c r="P34">
-        <v>268.4336616</v>
+        <v>267.988619775</v>
       </c>
       <c r="Q34">
-        <v>381.4336616</v>
+        <v>380.988619775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2008369494507141</v>
+        <v>0.2027233497117141</v>
       </c>
       <c r="T34">
-        <v>1.328012978663007</v>
+        <v>1.344171475320977</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>19.84890689768315</v>
+        <v>19.24742487048064</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1482738943068484</v>
+        <v>0.1479066629872112</v>
       </c>
       <c r="C35">
-        <v>912.6629516335178</v>
+        <v>904.5465272534906</v>
       </c>
       <c r="D35">
-        <v>1023.363951633518</v>
+        <v>1027.044527253491</v>
       </c>
       <c r="E35">
-        <v>173.501</v>
+        <v>185.2980000000001</v>
       </c>
       <c r="F35">
-        <v>389.301</v>
+        <v>401.0980000000001</v>
       </c>
       <c r="G35">
         <v>278.6</v>
@@ -4157,28 +4157,28 @@
         <v>376.9</v>
       </c>
       <c r="M35">
-        <v>19.5818403</v>
+        <v>20.1752294</v>
       </c>
       <c r="N35">
-        <v>357.3181597</v>
+        <v>356.7247706</v>
       </c>
       <c r="O35">
-        <v>89.32953992499999</v>
+        <v>89.18119265</v>
       </c>
       <c r="P35">
-        <v>267.988619775</v>
+        <v>267.54357795</v>
       </c>
       <c r="Q35">
-        <v>380.988619775</v>
+        <v>380.54357795</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2027233497117141</v>
+        <v>0.2046669136169867</v>
       </c>
       <c r="T35">
-        <v>1.344171475320977</v>
+        <v>1.360819623392824</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.24742487048064</v>
+        <v>18.68132413899591</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1479066629872112</v>
+        <v>0.1475394316675741</v>
       </c>
       <c r="C36">
-        <v>904.5465272534906</v>
+        <v>896.4566731544205</v>
       </c>
       <c r="D36">
-        <v>1027.044527253491</v>
+        <v>1030.751673154421</v>
       </c>
       <c r="E36">
-        <v>185.2980000000001</v>
+        <v>197.095</v>
       </c>
       <c r="F36">
-        <v>401.0980000000001</v>
+        <v>412.895</v>
       </c>
       <c r="G36">
         <v>278.6</v>
@@ -4239,28 +4239,28 @@
         <v>376.9</v>
       </c>
       <c r="M36">
-        <v>20.1752294</v>
+        <v>20.7686185</v>
       </c>
       <c r="N36">
-        <v>356.7247706</v>
+        <v>356.1313815</v>
       </c>
       <c r="O36">
-        <v>89.18119265</v>
+        <v>89.03284537499999</v>
       </c>
       <c r="P36">
-        <v>267.54357795</v>
+        <v>267.098536125</v>
       </c>
       <c r="Q36">
-        <v>380.54357795</v>
+        <v>380.098536125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2046669136169867</v>
+        <v>0.2066702794885755</v>
       </c>
       <c r="T36">
-        <v>1.360819623392824</v>
+        <v>1.377980022174575</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>18.68132413899591</v>
+        <v>18.14757202073888</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1475394316675741</v>
+        <v>0.1471722003479368</v>
       </c>
       <c r="C37">
-        <v>896.4566731544205</v>
+        <v>888.3936780971126</v>
       </c>
       <c r="D37">
-        <v>1030.751673154421</v>
+        <v>1034.485678097112</v>
       </c>
       <c r="E37">
-        <v>197.095</v>
+        <v>208.8920000000001</v>
       </c>
       <c r="F37">
-        <v>412.895</v>
+        <v>424.6920000000001</v>
       </c>
       <c r="G37">
         <v>278.6</v>
@@ -4321,28 +4321,28 @@
         <v>376.9</v>
       </c>
       <c r="M37">
-        <v>20.7686185</v>
+        <v>21.3620076</v>
       </c>
       <c r="N37">
-        <v>356.1313815</v>
+        <v>355.5379924</v>
       </c>
       <c r="O37">
-        <v>89.03284537499999</v>
+        <v>88.88449809999999</v>
       </c>
       <c r="P37">
-        <v>267.098536125</v>
+        <v>266.6534943</v>
       </c>
       <c r="Q37">
-        <v>380.098536125</v>
+        <v>379.6534943</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2066702794885755</v>
+        <v>0.2087362505436513</v>
       </c>
       <c r="T37">
-        <v>1.377980022174575</v>
+        <v>1.395676683418255</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.14757202073888</v>
+        <v>17.64347279794058</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1471722003479369</v>
+        <v>0.1468049690282996</v>
       </c>
       <c r="C38">
-        <v>888.3936780971121</v>
+        <v>880.3578350418461</v>
       </c>
       <c r="D38">
-        <v>1034.485678097112</v>
+        <v>1038.246835041846</v>
       </c>
       <c r="E38">
-        <v>208.892</v>
+        <v>220.689</v>
       </c>
       <c r="F38">
-        <v>424.692</v>
+        <v>436.489</v>
       </c>
       <c r="G38">
         <v>278.6</v>
@@ -4403,28 +4403,28 @@
         <v>376.9</v>
       </c>
       <c r="M38">
-        <v>21.3620076</v>
+        <v>21.9553967</v>
       </c>
       <c r="N38">
-        <v>355.5379924</v>
+        <v>354.9446033</v>
       </c>
       <c r="O38">
-        <v>88.8844981</v>
+        <v>88.736150825</v>
       </c>
       <c r="P38">
-        <v>266.6534943</v>
+        <v>266.208452475</v>
       </c>
       <c r="Q38">
-        <v>379.6534943</v>
+        <v>379.208452475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2087362505436513</v>
+        <v>0.210867807981428</v>
       </c>
       <c r="T38">
-        <v>1.395676683418255</v>
+        <v>1.413935143431576</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>17.64347279794059</v>
+        <v>17.16662218178002</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1468049690282996</v>
+        <v>0.1464377377086625</v>
       </c>
       <c r="C39">
-        <v>880.3578350418461</v>
+        <v>872.3494412249988</v>
       </c>
       <c r="D39">
-        <v>1038.246835041846</v>
+        <v>1042.035441224999</v>
       </c>
       <c r="E39">
-        <v>220.689</v>
+        <v>232.486</v>
       </c>
       <c r="F39">
-        <v>436.489</v>
+        <v>448.286</v>
       </c>
       <c r="G39">
         <v>278.6</v>
@@ -4485,28 +4485,28 @@
         <v>376.9</v>
       </c>
       <c r="M39">
-        <v>21.9553967</v>
+        <v>22.5487858</v>
       </c>
       <c r="N39">
-        <v>354.9446033</v>
+        <v>354.3512142</v>
       </c>
       <c r="O39">
-        <v>88.736150825</v>
+        <v>88.58780354999999</v>
       </c>
       <c r="P39">
-        <v>266.208452475</v>
+        <v>265.76341065</v>
       </c>
       <c r="Q39">
-        <v>379.208452475</v>
+        <v>378.76341065</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.210867807981428</v>
+        <v>0.2130681253365524</v>
       </c>
       <c r="T39">
-        <v>1.413935143431576</v>
+        <v>1.432782586025972</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.16662218178002</v>
+        <v>16.71486896647003</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1464377377086625</v>
+        <v>0.1460705063890253</v>
       </c>
       <c r="C40">
-        <v>872.3494412249988</v>
+        <v>864.3687982373503</v>
       </c>
       <c r="D40">
-        <v>1042.035441224999</v>
+        <v>1045.85179823735</v>
       </c>
       <c r="E40">
-        <v>232.486</v>
+        <v>244.283</v>
       </c>
       <c r="F40">
-        <v>448.286</v>
+        <v>460.083</v>
       </c>
       <c r="G40">
         <v>278.6</v>
@@ -4567,28 +4567,28 @@
         <v>376.9</v>
       </c>
       <c r="M40">
-        <v>22.5487858</v>
+        <v>23.1421749</v>
       </c>
       <c r="N40">
-        <v>354.3512142</v>
+        <v>353.7578251</v>
       </c>
       <c r="O40">
-        <v>88.58780354999999</v>
+        <v>88.439456275</v>
       </c>
       <c r="P40">
-        <v>265.76341065</v>
+        <v>265.318368825</v>
       </c>
       <c r="Q40">
-        <v>378.76341065</v>
+        <v>378.318368825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2130681253365524</v>
+        <v>0.2153405842443037</v>
       </c>
       <c r="T40">
-        <v>1.432782586025972</v>
+        <v>1.452247977557889</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>16.71486896647003</v>
+        <v>16.28628258271439</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1460705063890253</v>
+        <v>0.1457032750693881</v>
       </c>
       <c r="C41">
-        <v>864.3687982373503</v>
+        <v>856.4162121041118</v>
       </c>
       <c r="D41">
-        <v>1045.85179823735</v>
+        <v>1049.696212104112</v>
       </c>
       <c r="E41">
-        <v>244.283</v>
+        <v>256.08</v>
       </c>
       <c r="F41">
-        <v>460.083</v>
+        <v>471.8800000000001</v>
       </c>
       <c r="G41">
         <v>278.6</v>
@@ -4649,28 +4649,28 @@
         <v>376.9</v>
       </c>
       <c r="M41">
-        <v>23.1421749</v>
+        <v>23.735564</v>
       </c>
       <c r="N41">
-        <v>353.7578251</v>
+        <v>353.164436</v>
       </c>
       <c r="O41">
-        <v>88.439456275</v>
+        <v>88.29110899999999</v>
       </c>
       <c r="P41">
-        <v>265.318368825</v>
+        <v>264.873327</v>
       </c>
       <c r="Q41">
-        <v>378.318368825</v>
+        <v>377.873327</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2153405842443037</v>
+        <v>0.2176887917823135</v>
       </c>
       <c r="T41">
-        <v>1.452247977557889</v>
+        <v>1.472362215474204</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.28628258271439</v>
+        <v>15.87912551814652</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1457032750693881</v>
+        <v>0.1453360437497509</v>
       </c>
       <c r="C42">
-        <v>856.4162121041118</v>
+        <v>848.4919933667293</v>
       </c>
       <c r="D42">
-        <v>1049.696212104112</v>
+        <v>1053.56899336673</v>
       </c>
       <c r="E42">
-        <v>256.08</v>
+        <v>267.8770000000001</v>
       </c>
       <c r="F42">
-        <v>471.8800000000001</v>
+        <v>483.6770000000001</v>
       </c>
       <c r="G42">
         <v>278.6</v>
@@ -4731,28 +4731,28 @@
         <v>376.9</v>
       </c>
       <c r="M42">
-        <v>23.735564</v>
+        <v>24.3289531</v>
       </c>
       <c r="N42">
-        <v>353.164436</v>
+        <v>352.5710469</v>
       </c>
       <c r="O42">
-        <v>88.29110899999999</v>
+        <v>88.142761725</v>
       </c>
       <c r="P42">
-        <v>264.873327</v>
+        <v>264.428285175</v>
       </c>
       <c r="Q42">
-        <v>377.873327</v>
+        <v>377.428285175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2176887917823135</v>
+        <v>0.220116599575849</v>
       </c>
       <c r="T42">
-        <v>1.472362215474204</v>
+        <v>1.493158291963952</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.87912551814652</v>
+        <v>15.49182977380149</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1453360437497509</v>
+        <v>0.1449688124301137</v>
       </c>
       <c r="C43">
-        <v>848.4919933667293</v>
+        <v>840.5964571665055</v>
       </c>
       <c r="D43">
-        <v>1053.56899336673</v>
+        <v>1057.470457166506</v>
       </c>
       <c r="E43">
-        <v>267.8770000000001</v>
+        <v>279.674</v>
       </c>
       <c r="F43">
-        <v>483.6770000000001</v>
+        <v>495.474</v>
       </c>
       <c r="G43">
         <v>278.6</v>
@@ -4813,28 +4813,28 @@
         <v>376.9</v>
       </c>
       <c r="M43">
-        <v>24.3289531</v>
+        <v>24.9223422</v>
       </c>
       <c r="N43">
-        <v>352.5710469</v>
+        <v>351.9776578</v>
       </c>
       <c r="O43">
-        <v>88.142761725</v>
+        <v>87.99441444999999</v>
       </c>
       <c r="P43">
-        <v>264.428285175</v>
+        <v>263.98324335</v>
       </c>
       <c r="Q43">
-        <v>377.428285175</v>
+        <v>376.98324335</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.220116599575849</v>
+        <v>0.2226281248795064</v>
       </c>
       <c r="T43">
-        <v>1.493158291963952</v>
+        <v>1.514671474539554</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.49182977380149</v>
+        <v>15.12297668394907</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1449688124301137</v>
+        <v>0.1446015811104765</v>
       </c>
       <c r="C44">
-        <v>840.5964571665056</v>
+        <v>832.7299233300826</v>
       </c>
       <c r="D44">
-        <v>1057.470457166506</v>
+        <v>1061.400923330082</v>
       </c>
       <c r="E44">
-        <v>279.674</v>
+        <v>291.471</v>
       </c>
       <c r="F44">
-        <v>495.474</v>
+        <v>507.271</v>
       </c>
       <c r="G44">
         <v>278.6</v>
@@ -4895,28 +4895,28 @@
         <v>376.9</v>
       </c>
       <c r="M44">
-        <v>24.9223422</v>
+        <v>25.5157313</v>
       </c>
       <c r="N44">
-        <v>351.9776578</v>
+        <v>351.3842687</v>
       </c>
       <c r="O44">
-        <v>87.99441444999999</v>
+        <v>87.846067175</v>
       </c>
       <c r="P44">
-        <v>263.98324335</v>
+        <v>263.538201525</v>
       </c>
       <c r="Q44">
-        <v>376.98324335</v>
+        <v>376.538201525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2226281248795064</v>
+        <v>0.2252277738780289</v>
       </c>
       <c r="T44">
-        <v>1.514671474539554</v>
+        <v>1.536939505626581</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.12297668394907</v>
+        <v>14.77127955176421</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1446015811104765</v>
+        <v>0.1442343497908394</v>
       </c>
       <c r="C45">
-        <v>832.7299233300826</v>
+        <v>824.8927164568402</v>
       </c>
       <c r="D45">
-        <v>1061.400923330082</v>
+        <v>1065.36071645684</v>
       </c>
       <c r="E45">
-        <v>291.471</v>
+        <v>303.268</v>
       </c>
       <c r="F45">
-        <v>507.271</v>
+        <v>519.068</v>
       </c>
       <c r="G45">
         <v>278.6</v>
@@ -4977,28 +4977,28 @@
         <v>376.9</v>
       </c>
       <c r="M45">
-        <v>25.5157313</v>
+        <v>26.1091204</v>
       </c>
       <c r="N45">
-        <v>351.3842687</v>
+        <v>350.7908796</v>
       </c>
       <c r="O45">
-        <v>87.846067175</v>
+        <v>87.6977199</v>
       </c>
       <c r="P45">
-        <v>263.538201525</v>
+        <v>263.0931597</v>
       </c>
       <c r="Q45">
-        <v>376.538201525</v>
+        <v>376.0931597</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2252277738780289</v>
+        <v>0.2279202674836417</v>
       </c>
       <c r="T45">
-        <v>1.536939505626581</v>
+        <v>1.560002823538144</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>14.77127955176421</v>
+        <v>14.43556865286048</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1442343497908394</v>
+        <v>0.1438671184712021</v>
       </c>
       <c r="C46">
-        <v>824.8927164568402</v>
+        <v>817.0851660082606</v>
       </c>
       <c r="D46">
-        <v>1065.36071645684</v>
+        <v>1069.350166008261</v>
       </c>
       <c r="E46">
-        <v>303.268</v>
+        <v>315.065</v>
       </c>
       <c r="F46">
-        <v>519.068</v>
+        <v>530.865</v>
       </c>
       <c r="G46">
         <v>278.6</v>
@@ -5059,28 +5059,28 @@
         <v>376.9</v>
       </c>
       <c r="M46">
-        <v>26.1091204</v>
+        <v>26.7025095</v>
       </c>
       <c r="N46">
-        <v>350.7908796</v>
+        <v>350.1974905</v>
       </c>
       <c r="O46">
-        <v>87.6977199</v>
+        <v>87.54937262499999</v>
       </c>
       <c r="P46">
-        <v>263.0931597</v>
+        <v>262.648117875</v>
       </c>
       <c r="Q46">
-        <v>376.0931597</v>
+        <v>375.648117875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2279202674836417</v>
+        <v>0.2307106699476403</v>
       </c>
       <c r="T46">
-        <v>1.560002823538144</v>
+        <v>1.583904807555583</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.43556865286048</v>
+        <v>14.11477823835247</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1438671184712021</v>
+        <v>0.1434998871515649</v>
       </c>
       <c r="C47">
-        <v>817.0851660082606</v>
+        <v>809.3076063993051</v>
       </c>
       <c r="D47">
-        <v>1069.350166008261</v>
+        <v>1073.369606399305</v>
       </c>
       <c r="E47">
-        <v>315.065</v>
+        <v>326.862</v>
       </c>
       <c r="F47">
-        <v>530.865</v>
+        <v>542.662</v>
       </c>
       <c r="G47">
         <v>278.6</v>
@@ -5141,28 +5141,28 @@
         <v>376.9</v>
       </c>
       <c r="M47">
-        <v>26.7025095</v>
+        <v>27.2958986</v>
       </c>
       <c r="N47">
-        <v>350.1974905</v>
+        <v>349.6041014</v>
       </c>
       <c r="O47">
-        <v>87.54937262499999</v>
+        <v>87.40102535</v>
       </c>
       <c r="P47">
-        <v>262.648117875</v>
+        <v>262.20307605</v>
       </c>
       <c r="Q47">
-        <v>375.648117875</v>
+        <v>375.20307605</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2307106699476403</v>
+        <v>0.2336044206510462</v>
       </c>
       <c r="T47">
-        <v>1.583904807555583</v>
+        <v>1.608692050240333</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.11477823835247</v>
+        <v>13.80793523317089</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1434998871515649</v>
+        <v>0.1431326558319277</v>
       </c>
       <c r="C48">
-        <v>809.3076063993051</v>
+        <v>801.5603770918581</v>
       </c>
       <c r="D48">
-        <v>1073.369606399305</v>
+        <v>1077.419377091858</v>
       </c>
       <c r="E48">
-        <v>326.862</v>
+        <v>338.659</v>
       </c>
       <c r="F48">
-        <v>542.662</v>
+        <v>554.4590000000001</v>
       </c>
       <c r="G48">
         <v>278.6</v>
@@ -5223,28 +5223,28 @@
         <v>376.9</v>
       </c>
       <c r="M48">
-        <v>27.2958986</v>
+        <v>27.8892877</v>
       </c>
       <c r="N48">
-        <v>349.6041014</v>
+        <v>349.0107123</v>
       </c>
       <c r="O48">
-        <v>87.40102535</v>
+        <v>87.25267807499999</v>
       </c>
       <c r="P48">
-        <v>262.20307605</v>
+        <v>261.758034225</v>
       </c>
       <c r="Q48">
-        <v>375.20307605</v>
+        <v>374.758034225</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2336044206510462</v>
+        <v>0.2366073694942033</v>
       </c>
       <c r="T48">
-        <v>1.608692050240333</v>
+        <v>1.634414660573565</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.80793523317089</v>
+        <v>13.51414937714598</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1431326558319277</v>
+        <v>0.1427654245122906</v>
       </c>
       <c r="C49">
-        <v>801.5603770918581</v>
+        <v>793.8438226902988</v>
       </c>
       <c r="D49">
-        <v>1077.419377091858</v>
+        <v>1081.499822690299</v>
       </c>
       <c r="E49">
-        <v>338.659</v>
+        <v>350.4560000000001</v>
       </c>
       <c r="F49">
-        <v>554.4590000000001</v>
+        <v>566.2560000000001</v>
       </c>
       <c r="G49">
         <v>278.6</v>
@@ -5305,28 +5305,28 @@
         <v>376.9</v>
       </c>
       <c r="M49">
-        <v>27.8892877</v>
+        <v>28.4826768</v>
       </c>
       <c r="N49">
-        <v>349.0107123</v>
+        <v>348.4173232</v>
       </c>
       <c r="O49">
-        <v>87.25267807499999</v>
+        <v>87.1043308</v>
       </c>
       <c r="P49">
-        <v>261.758034225</v>
+        <v>261.3129924</v>
       </c>
       <c r="Q49">
-        <v>374.758034225</v>
+        <v>374.3129924</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2366073694942033</v>
+        <v>0.2397258163697896</v>
       </c>
       <c r="T49">
-        <v>1.634414660573565</v>
+        <v>1.66112660207346</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.51414937714598</v>
+        <v>13.23260459845543</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1427654245122906</v>
+        <v>0.1423981931926534</v>
       </c>
       <c r="C50">
-        <v>793.8438226902989</v>
+        <v>786.1582930392509</v>
       </c>
       <c r="D50">
-        <v>1081.499822690299</v>
+        <v>1085.611293039251</v>
       </c>
       <c r="E50">
-        <v>350.456</v>
+        <v>362.253</v>
       </c>
       <c r="F50">
-        <v>566.256</v>
+        <v>578.053</v>
       </c>
       <c r="G50">
         <v>278.6</v>
@@ -5387,28 +5387,28 @@
         <v>376.9</v>
       </c>
       <c r="M50">
-        <v>28.4826768</v>
+        <v>29.0760659</v>
       </c>
       <c r="N50">
-        <v>348.4173232</v>
+        <v>347.8239341</v>
       </c>
       <c r="O50">
-        <v>87.1043308</v>
+        <v>86.95598352499999</v>
       </c>
       <c r="P50">
-        <v>261.3129924</v>
+        <v>260.867950575</v>
       </c>
       <c r="Q50">
-        <v>374.3129924</v>
+        <v>373.867950575</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2397258163697896</v>
+        <v>0.2429665552797125</v>
       </c>
       <c r="T50">
-        <v>1.66112660207346</v>
+        <v>1.688886070690998</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.23260459845544</v>
+        <v>12.96255144338492</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1423981931926534</v>
+        <v>0.1425934618730162</v>
       </c>
       <c r="C51">
-        <v>786.1582930392509</v>
+        <v>772.1712082909975</v>
       </c>
       <c r="D51">
-        <v>1085.611293039251</v>
+        <v>1083.421208290998</v>
       </c>
       <c r="E51">
-        <v>362.253</v>
+        <v>374.05</v>
       </c>
       <c r="F51">
-        <v>578.053</v>
+        <v>589.85</v>
       </c>
       <c r="G51">
         <v>278.6</v>
@@ -5469,45 +5469,45 @@
         <v>376.9</v>
       </c>
       <c r="M51">
-        <v>29.0760659</v>
+        <v>30.55423</v>
       </c>
       <c r="N51">
-        <v>347.8239341</v>
+        <v>346.34577</v>
       </c>
       <c r="O51">
-        <v>86.95598352499999</v>
+        <v>86.58644249999999</v>
       </c>
       <c r="P51">
-        <v>260.867950575</v>
+        <v>259.7593275</v>
       </c>
       <c r="Q51">
-        <v>373.867950575</v>
+        <v>372.7593275</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2429665552797125</v>
+        <v>0.2463369237460324</v>
       </c>
       <c r="T51">
-        <v>1.688886070690998</v>
+        <v>1.717755918053237</v>
       </c>
       <c r="U51">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y51">
-        <v>12.96255144338492</v>
+        <v>12.33544422490765</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1425934618730162</v>
+        <v>0.142237480553379</v>
       </c>
       <c r="C52">
-        <v>772.1712082909975</v>
+        <v>764.3734595078193</v>
       </c>
       <c r="D52">
-        <v>1083.421208290998</v>
+        <v>1087.420459507819</v>
       </c>
       <c r="E52">
-        <v>374.05</v>
+        <v>385.847</v>
       </c>
       <c r="F52">
-        <v>589.85</v>
+        <v>601.647</v>
       </c>
       <c r="G52">
         <v>278.6</v>
@@ -5551,28 +5551,28 @@
         <v>376.9</v>
       </c>
       <c r="M52">
-        <v>30.55423</v>
+        <v>31.1653146</v>
       </c>
       <c r="N52">
-        <v>346.34577</v>
+        <v>345.7346854</v>
       </c>
       <c r="O52">
-        <v>86.58644249999999</v>
+        <v>86.43367135</v>
       </c>
       <c r="P52">
-        <v>259.7593275</v>
+        <v>259.30101405</v>
       </c>
       <c r="Q52">
-        <v>372.7593275</v>
+        <v>372.30101405</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2463369237460324</v>
+        <v>0.2498448582722021</v>
       </c>
       <c r="T52">
-        <v>1.717755918053237</v>
+        <v>1.747804126532303</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>12.33544422490765</v>
+        <v>12.0935727695173</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.142237480553379</v>
+        <v>0.1418814992337418</v>
       </c>
       <c r="C53">
-        <v>764.3734595078193</v>
+        <v>756.6053451232946</v>
       </c>
       <c r="D53">
-        <v>1087.420459507819</v>
+        <v>1091.449345123295</v>
       </c>
       <c r="E53">
-        <v>385.847</v>
+        <v>397.6440000000001</v>
       </c>
       <c r="F53">
-        <v>601.647</v>
+        <v>613.4440000000001</v>
       </c>
       <c r="G53">
         <v>278.6</v>
@@ -5633,28 +5633,28 @@
         <v>376.9</v>
       </c>
       <c r="M53">
-        <v>31.1653146</v>
+        <v>31.7763992</v>
       </c>
       <c r="N53">
-        <v>345.7346854</v>
+        <v>345.1236008</v>
       </c>
       <c r="O53">
-        <v>86.43367135</v>
+        <v>86.28090019999999</v>
       </c>
       <c r="P53">
-        <v>259.30101405</v>
+        <v>258.8427005999999</v>
       </c>
       <c r="Q53">
-        <v>372.30101405</v>
+        <v>371.8427005999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2498448582722021</v>
+        <v>0.2534989567369621</v>
       </c>
       <c r="T53">
-        <v>1.747804126532303</v>
+        <v>1.779104343697996</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.0935727695173</v>
+        <v>11.8610040624112</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1418814992337418</v>
+        <v>0.1415255179141046</v>
       </c>
       <c r="C54">
-        <v>756.6053451232946</v>
+        <v>748.8671957480855</v>
       </c>
       <c r="D54">
-        <v>1091.449345123295</v>
+        <v>1095.508195748086</v>
       </c>
       <c r="E54">
-        <v>397.6440000000001</v>
+        <v>409.4410000000001</v>
       </c>
       <c r="F54">
-        <v>613.4440000000001</v>
+        <v>625.2410000000001</v>
       </c>
       <c r="G54">
         <v>278.6</v>
@@ -5715,28 +5715,28 @@
         <v>376.9</v>
       </c>
       <c r="M54">
-        <v>31.7763992</v>
+        <v>32.38748380000001</v>
       </c>
       <c r="N54">
-        <v>345.1236008</v>
+        <v>344.5125162</v>
       </c>
       <c r="O54">
-        <v>86.28090019999999</v>
+        <v>86.12812905</v>
       </c>
       <c r="P54">
-        <v>258.8427005999999</v>
+        <v>258.38438715</v>
       </c>
       <c r="Q54">
-        <v>371.8427005999999</v>
+        <v>371.38438715</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2534989567369621</v>
+        <v>0.2573085487534141</v>
       </c>
       <c r="T54">
-        <v>1.779104343697996</v>
+        <v>1.8117364849984</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.8610040624112</v>
+        <v>11.63721153293174</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1415255179141046</v>
+        <v>0.1411695365944674</v>
       </c>
       <c r="C55">
-        <v>748.8671957480855</v>
+        <v>741.159346929076</v>
       </c>
       <c r="D55">
-        <v>1095.508195748086</v>
+        <v>1099.597346929076</v>
       </c>
       <c r="E55">
-        <v>409.4410000000001</v>
+        <v>421.238</v>
       </c>
       <c r="F55">
-        <v>625.2410000000001</v>
+        <v>637.038</v>
       </c>
       <c r="G55">
         <v>278.6</v>
@@ -5797,28 +5797,28 @@
         <v>376.9</v>
       </c>
       <c r="M55">
-        <v>32.38748380000001</v>
+        <v>32.9985684</v>
       </c>
       <c r="N55">
-        <v>344.5125162</v>
+        <v>343.9014316</v>
       </c>
       <c r="O55">
-        <v>86.12812905</v>
+        <v>85.97535789999999</v>
       </c>
       <c r="P55">
-        <v>258.38438715</v>
+        <v>257.9260737</v>
       </c>
       <c r="Q55">
-        <v>371.38438715</v>
+        <v>370.9260737</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2573085487534141</v>
+        <v>0.261283775205364</v>
       </c>
       <c r="T55">
-        <v>1.8117364849984</v>
+        <v>1.845787415050995</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.63721153293174</v>
+        <v>11.42170761565523</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1411695365944674</v>
+        <v>0.1408135552748302</v>
       </c>
       <c r="C56">
-        <v>741.159346929076</v>
+        <v>733.4821392418371</v>
       </c>
       <c r="D56">
-        <v>1099.597346929076</v>
+        <v>1103.717139241837</v>
       </c>
       <c r="E56">
-        <v>421.238</v>
+        <v>433.035</v>
       </c>
       <c r="F56">
-        <v>637.038</v>
+        <v>648.835</v>
       </c>
       <c r="G56">
         <v>278.6</v>
@@ -5879,28 +5879,28 @@
         <v>376.9</v>
       </c>
       <c r="M56">
-        <v>32.9985684</v>
+        <v>33.609653</v>
       </c>
       <c r="N56">
-        <v>343.9014316</v>
+        <v>343.290347</v>
       </c>
       <c r="O56">
-        <v>85.97535789999999</v>
+        <v>85.82258675</v>
       </c>
       <c r="P56">
-        <v>257.9260737</v>
+        <v>257.46776025</v>
       </c>
       <c r="Q56">
-        <v>370.9260737</v>
+        <v>370.46776025</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.261283775205364</v>
+        <v>0.2654356783885117</v>
       </c>
       <c r="T56">
-        <v>1.845787415050995</v>
+        <v>1.881351719772594</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.42170761565523</v>
+        <v>11.2140402044615</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1408135552748302</v>
+        <v>0.1404575739551931</v>
       </c>
       <c r="C57">
-        <v>733.4821392418371</v>
+        <v>725.835918385189</v>
       </c>
       <c r="D57">
-        <v>1103.717139241837</v>
+        <v>1107.867918385189</v>
       </c>
       <c r="E57">
-        <v>433.035</v>
+        <v>444.8320000000001</v>
       </c>
       <c r="F57">
-        <v>648.835</v>
+        <v>660.6320000000001</v>
       </c>
       <c r="G57">
         <v>278.6</v>
@@ -5961,28 +5961,28 @@
         <v>376.9</v>
       </c>
       <c r="M57">
-        <v>33.609653</v>
+        <v>34.2207376</v>
       </c>
       <c r="N57">
-        <v>343.290347</v>
+        <v>342.6792624</v>
       </c>
       <c r="O57">
-        <v>85.82258675</v>
+        <v>85.66981559999999</v>
       </c>
       <c r="P57">
-        <v>257.46776025</v>
+        <v>257.0094468</v>
       </c>
       <c r="Q57">
-        <v>370.46776025</v>
+        <v>370.0094468</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2654356783885117</v>
+        <v>0.2697763044436206</v>
       </c>
       <c r="T57">
-        <v>1.881351719772594</v>
+        <v>1.91853258379972</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.2140402044615</v>
+        <v>11.01378948652468</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1404575739551931</v>
+        <v>0.1401015926355559</v>
       </c>
       <c r="C58">
-        <v>725.835918385189</v>
+        <v>718.221035277897</v>
       </c>
       <c r="D58">
-        <v>1107.867918385189</v>
+        <v>1112.050035277897</v>
       </c>
       <c r="E58">
-        <v>444.8320000000001</v>
+        <v>456.6290000000001</v>
       </c>
       <c r="F58">
-        <v>660.6320000000001</v>
+        <v>672.4290000000001</v>
       </c>
       <c r="G58">
         <v>278.6</v>
@@ -6043,28 +6043,28 @@
         <v>376.9</v>
       </c>
       <c r="M58">
-        <v>34.2207376</v>
+        <v>34.8318222</v>
       </c>
       <c r="N58">
-        <v>342.6792624</v>
+        <v>342.0681777999999</v>
       </c>
       <c r="O58">
-        <v>85.66981559999999</v>
+        <v>85.51704444999999</v>
       </c>
       <c r="P58">
-        <v>257.0094468</v>
+        <v>256.55113335</v>
       </c>
       <c r="Q58">
-        <v>370.0094468</v>
+        <v>369.55113335</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2697763044436206</v>
+        <v>0.2743188200826881</v>
       </c>
       <c r="T58">
-        <v>1.91853258379972</v>
+        <v>1.957442790339736</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.01378948652468</v>
+        <v>10.82056510956811</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1401015926355559</v>
+        <v>0.1397456113159187</v>
       </c>
       <c r="C59">
-        <v>718.221035277897</v>
+        <v>710.6378461575732</v>
       </c>
       <c r="D59">
-        <v>1112.050035277897</v>
+        <v>1116.263846157573</v>
       </c>
       <c r="E59">
-        <v>456.6290000000001</v>
+        <v>468.4260000000001</v>
       </c>
       <c r="F59">
-        <v>672.4290000000001</v>
+        <v>684.2260000000001</v>
       </c>
       <c r="G59">
         <v>278.6</v>
@@ -6125,28 +6125,28 @@
         <v>376.9</v>
       </c>
       <c r="M59">
-        <v>34.8318222</v>
+        <v>35.4429068</v>
       </c>
       <c r="N59">
-        <v>342.0681777999999</v>
+        <v>341.4570932</v>
       </c>
       <c r="O59">
-        <v>85.51704444999999</v>
+        <v>85.36427329999999</v>
       </c>
       <c r="P59">
-        <v>256.55113335</v>
+        <v>256.0928199</v>
       </c>
       <c r="Q59">
-        <v>369.55113335</v>
+        <v>369.0928199</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2743188200826881</v>
+        <v>0.2790776459902826</v>
       </c>
       <c r="T59">
-        <v>1.957442790339736</v>
+        <v>1.998205863857848</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.82056510956811</v>
+        <v>10.63400364216176</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1397456113159187</v>
+        <v>0.1393896299962815</v>
       </c>
       <c r="C60">
-        <v>710.6378461575733</v>
+        <v>703.0867126818263</v>
       </c>
       <c r="D60">
-        <v>1116.263846157573</v>
+        <v>1120.509712681826</v>
       </c>
       <c r="E60">
-        <v>468.426</v>
+        <v>480.223</v>
       </c>
       <c r="F60">
-        <v>684.226</v>
+        <v>696.023</v>
       </c>
       <c r="G60">
         <v>278.6</v>
@@ -6207,28 +6207,28 @@
         <v>376.9</v>
       </c>
       <c r="M60">
-        <v>35.4429068</v>
+        <v>36.0539914</v>
       </c>
       <c r="N60">
-        <v>341.4570932</v>
+        <v>340.8460086</v>
       </c>
       <c r="O60">
-        <v>85.36427329999999</v>
+        <v>85.21150215</v>
       </c>
       <c r="P60">
-        <v>256.0928199</v>
+        <v>255.63450645</v>
       </c>
       <c r="Q60">
-        <v>369.0928199</v>
+        <v>368.63450645</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2790776459902826</v>
+        <v>0.284068609747028</v>
       </c>
       <c r="T60">
-        <v>1.998205863857847</v>
+        <v>2.040957379986599</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.63400364216177</v>
+        <v>10.45376629229462</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1393896299962815</v>
+        <v>0.1390336486766443</v>
       </c>
       <c r="C61">
-        <v>703.0867126818263</v>
+        <v>695.5680020317387</v>
       </c>
       <c r="D61">
-        <v>1120.509712681826</v>
+        <v>1124.788002031739</v>
       </c>
       <c r="E61">
-        <v>480.223</v>
+        <v>492.02</v>
       </c>
       <c r="F61">
-        <v>696.023</v>
+        <v>707.8200000000001</v>
       </c>
       <c r="G61">
         <v>278.6</v>
@@ -6289,28 +6289,28 @@
         <v>376.9</v>
       </c>
       <c r="M61">
-        <v>36.0539914</v>
+        <v>36.665076</v>
       </c>
       <c r="N61">
-        <v>340.8460086</v>
+        <v>340.234924</v>
       </c>
       <c r="O61">
-        <v>85.21150215</v>
+        <v>85.05873099999999</v>
       </c>
       <c r="P61">
-        <v>255.63450645</v>
+        <v>255.176193</v>
       </c>
       <c r="Q61">
-        <v>368.63450645</v>
+        <v>368.176193</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.284068609747028</v>
+        <v>0.2893091216916108</v>
       </c>
       <c r="T61">
-        <v>2.040957379986599</v>
+        <v>2.085846471921788</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.45376629229462</v>
+        <v>10.27953685408971</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1390336486766443</v>
+        <v>0.1386776673570071</v>
       </c>
       <c r="C62">
-        <v>695.5680020317387</v>
+        <v>688.0820870177156</v>
       </c>
       <c r="D62">
-        <v>1124.788002031739</v>
+        <v>1129.099087017715</v>
       </c>
       <c r="E62">
-        <v>492.02</v>
+        <v>503.817</v>
       </c>
       <c r="F62">
-        <v>707.8200000000001</v>
+        <v>719.617</v>
       </c>
       <c r="G62">
         <v>278.6</v>
@@ -6371,28 +6371,28 @@
         <v>376.9</v>
       </c>
       <c r="M62">
-        <v>36.665076</v>
+        <v>37.2761606</v>
       </c>
       <c r="N62">
-        <v>340.234924</v>
+        <v>339.6238394</v>
       </c>
       <c r="O62">
-        <v>85.05873099999999</v>
+        <v>84.90595984999999</v>
       </c>
       <c r="P62">
-        <v>255.176193</v>
+        <v>254.71787955</v>
       </c>
       <c r="Q62">
-        <v>368.176193</v>
+        <v>367.71787955</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2893091216916108</v>
+        <v>0.2948183778384798</v>
       </c>
       <c r="T62">
-        <v>2.085846471921788</v>
+        <v>2.133037568571603</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.27953685408971</v>
+        <v>10.11101985648168</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1386776673570071</v>
+        <v>0.1383216860373699</v>
       </c>
       <c r="C63">
-        <v>688.0820870177156</v>
+        <v>680.6293461877801</v>
       </c>
       <c r="D63">
-        <v>1129.099087017715</v>
+        <v>1133.44334618778</v>
       </c>
       <c r="E63">
-        <v>503.817</v>
+        <v>515.614</v>
       </c>
       <c r="F63">
-        <v>719.617</v>
+        <v>731.414</v>
       </c>
       <c r="G63">
         <v>278.6</v>
@@ -6453,28 +6453,28 @@
         <v>376.9</v>
       </c>
       <c r="M63">
-        <v>37.2761606</v>
+        <v>37.8872452</v>
       </c>
       <c r="N63">
-        <v>339.6238394</v>
+        <v>339.0127548</v>
       </c>
       <c r="O63">
-        <v>84.90595984999999</v>
+        <v>84.7531887</v>
       </c>
       <c r="P63">
-        <v>254.71787955</v>
+        <v>254.2595661</v>
       </c>
       <c r="Q63">
-        <v>367.71787955</v>
+        <v>367.2595661</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2948183778384798</v>
+        <v>0.300617594835184</v>
       </c>
       <c r="T63">
-        <v>2.133037568571603</v>
+        <v>2.182712407150354</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.11101985648168</v>
+        <v>9.947938891054555</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1383216860373699</v>
+        <v>0.1387689547177327</v>
       </c>
       <c r="C64">
-        <v>680.6293461877801</v>
+        <v>663.3794107293295</v>
       </c>
       <c r="D64">
-        <v>1133.44334618778</v>
+        <v>1127.99041072933</v>
       </c>
       <c r="E64">
-        <v>515.614</v>
+        <v>527.4110000000001</v>
       </c>
       <c r="F64">
-        <v>731.414</v>
+        <v>743.211</v>
       </c>
       <c r="G64">
         <v>278.6</v>
@@ -6535,45 +6535,45 @@
         <v>376.9</v>
       </c>
       <c r="M64">
-        <v>37.8872452</v>
+        <v>39.7617885</v>
       </c>
       <c r="N64">
-        <v>339.0127548</v>
+        <v>337.1382115</v>
       </c>
       <c r="O64">
-        <v>84.7531887</v>
+        <v>84.28455287499999</v>
       </c>
       <c r="P64">
-        <v>254.2595661</v>
+        <v>252.853658625</v>
       </c>
       <c r="Q64">
-        <v>367.2595661</v>
+        <v>365.853658625</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.300617594835184</v>
+        <v>0.3067302830208993</v>
       </c>
       <c r="T64">
-        <v>2.182712407150354</v>
+        <v>2.235072372138768</v>
       </c>
       <c r="U64">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>9.947938891054555</v>
+        <v>9.478949871683964</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1387689547177327</v>
+        <v>0.1384257233980956</v>
       </c>
       <c r="C65">
-        <v>663.3794107293295</v>
+        <v>655.762260807787</v>
       </c>
       <c r="D65">
-        <v>1127.99041072933</v>
+        <v>1132.170260807787</v>
       </c>
       <c r="E65">
-        <v>527.4110000000001</v>
+        <v>539.2080000000001</v>
       </c>
       <c r="F65">
-        <v>743.211</v>
+        <v>755.008</v>
       </c>
       <c r="G65">
         <v>278.6</v>
@@ -6617,28 +6617,28 @@
         <v>376.9</v>
       </c>
       <c r="M65">
-        <v>39.7617885</v>
+        <v>40.392928</v>
       </c>
       <c r="N65">
-        <v>337.1382115</v>
+        <v>336.507072</v>
       </c>
       <c r="O65">
-        <v>84.28455287499999</v>
+        <v>84.126768</v>
       </c>
       <c r="P65">
-        <v>252.853658625</v>
+        <v>252.380304</v>
       </c>
       <c r="Q65">
-        <v>365.853658625</v>
+        <v>365.380304</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3067302830208993</v>
+        <v>0.3131825649947099</v>
       </c>
       <c r="T65">
-        <v>2.235072372138768</v>
+        <v>2.290341224070983</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.478949871683964</v>
+        <v>9.330841279938905</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1384257233980956</v>
+        <v>0.1380824920784584</v>
       </c>
       <c r="C66">
-        <v>655.762260807787</v>
+        <v>648.1762035762233</v>
       </c>
       <c r="D66">
-        <v>1132.170260807787</v>
+        <v>1136.381203576223</v>
       </c>
       <c r="E66">
-        <v>539.2080000000001</v>
+        <v>551.0050000000001</v>
       </c>
       <c r="F66">
-        <v>755.008</v>
+        <v>766.8050000000001</v>
       </c>
       <c r="G66">
         <v>278.6</v>
@@ -6699,28 +6699,28 @@
         <v>376.9</v>
       </c>
       <c r="M66">
-        <v>40.392928</v>
+        <v>41.0240675</v>
       </c>
       <c r="N66">
-        <v>336.507072</v>
+        <v>335.8759325</v>
       </c>
       <c r="O66">
-        <v>84.126768</v>
+        <v>83.96898312499999</v>
       </c>
       <c r="P66">
-        <v>252.380304</v>
+        <v>251.906949375</v>
       </c>
       <c r="Q66">
-        <v>365.380304</v>
+        <v>364.906949375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3131825649947099</v>
+        <v>0.3200035487955953</v>
       </c>
       <c r="T66">
-        <v>2.290341224070983</v>
+        <v>2.348768296113611</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>9.330841279938905</v>
+        <v>9.187289875632151</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1380824920784584</v>
+        <v>0.1377392607588211</v>
       </c>
       <c r="C67">
-        <v>648.1762035762233</v>
+        <v>640.6215872640535</v>
       </c>
       <c r="D67">
-        <v>1136.381203576223</v>
+        <v>1140.623587264053</v>
       </c>
       <c r="E67">
-        <v>551.0050000000001</v>
+        <v>562.8020000000001</v>
       </c>
       <c r="F67">
-        <v>766.8050000000001</v>
+        <v>778.6020000000001</v>
       </c>
       <c r="G67">
         <v>278.6</v>
@@ -6781,28 +6781,28 @@
         <v>376.9</v>
       </c>
       <c r="M67">
-        <v>41.0240675</v>
+        <v>41.655207</v>
       </c>
       <c r="N67">
-        <v>335.8759325</v>
+        <v>335.244793</v>
       </c>
       <c r="O67">
-        <v>83.96898312499999</v>
+        <v>83.81119824999999</v>
       </c>
       <c r="P67">
-        <v>251.906949375</v>
+        <v>251.43359475</v>
       </c>
       <c r="Q67">
-        <v>364.906949375</v>
+        <v>364.43359475</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3200035487955953</v>
+        <v>0.3272257669377093</v>
       </c>
       <c r="T67">
-        <v>2.348768296113611</v>
+        <v>2.410632254746981</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.187289875632151</v>
+        <v>9.048088513880147</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1377392607588211</v>
+        <v>0.137396029439184</v>
       </c>
       <c r="C68">
-        <v>640.6215872640535</v>
+        <v>633.098765320274</v>
       </c>
       <c r="D68">
-        <v>1140.623587264053</v>
+        <v>1144.897765320274</v>
       </c>
       <c r="E68">
-        <v>562.8020000000001</v>
+        <v>574.5990000000002</v>
       </c>
       <c r="F68">
-        <v>778.6020000000001</v>
+        <v>790.3990000000001</v>
       </c>
       <c r="G68">
         <v>278.6</v>
@@ -6863,28 +6863,28 @@
         <v>376.9</v>
       </c>
       <c r="M68">
-        <v>41.655207</v>
+        <v>42.28634650000001</v>
       </c>
       <c r="N68">
-        <v>335.244793</v>
+        <v>334.6136534999999</v>
       </c>
       <c r="O68">
-        <v>83.81119824999999</v>
+        <v>83.65341337499999</v>
       </c>
       <c r="P68">
-        <v>251.43359475</v>
+        <v>250.960240125</v>
       </c>
       <c r="Q68">
-        <v>364.43359475</v>
+        <v>363.9602401249999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3272257669377093</v>
+        <v>0.3348856952702545</v>
       </c>
       <c r="T68">
-        <v>2.410632254746981</v>
+        <v>2.476245544206615</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.048088513880147</v>
+        <v>8.913042416658055</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.137396029439184</v>
+        <v>0.1370527981195468</v>
       </c>
       <c r="C69">
-        <v>633.098765320274</v>
+        <v>625.6080965116282</v>
       </c>
       <c r="D69">
-        <v>1144.897765320274</v>
+        <v>1149.204096511628</v>
       </c>
       <c r="E69">
-        <v>574.5990000000002</v>
+        <v>586.3960000000002</v>
       </c>
       <c r="F69">
-        <v>790.3990000000001</v>
+        <v>802.1960000000001</v>
       </c>
       <c r="G69">
         <v>278.6</v>
@@ -6945,28 +6945,28 @@
         <v>376.9</v>
       </c>
       <c r="M69">
-        <v>42.28634650000001</v>
+        <v>42.917486</v>
       </c>
       <c r="N69">
-        <v>334.6136534999999</v>
+        <v>333.982514</v>
       </c>
       <c r="O69">
-        <v>83.65341337499999</v>
+        <v>83.4956285</v>
       </c>
       <c r="P69">
-        <v>250.960240125</v>
+        <v>250.4868855</v>
       </c>
       <c r="Q69">
-        <v>363.9602401249999</v>
+        <v>363.4868855</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3348856952702545</v>
+        <v>0.3430243691235837</v>
       </c>
       <c r="T69">
-        <v>2.476245544206615</v>
+        <v>2.545959664257477</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.913042416658055</v>
+        <v>8.781968263471908</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1370527981195468</v>
+        <v>0.1367095667999096</v>
       </c>
       <c r="C70">
-        <v>625.6080965116282</v>
+        <v>618.1499450229879</v>
       </c>
       <c r="D70">
-        <v>1149.204096511628</v>
+        <v>1153.542945022988</v>
       </c>
       <c r="E70">
-        <v>586.3960000000002</v>
+        <v>598.193</v>
       </c>
       <c r="F70">
-        <v>802.1960000000001</v>
+        <v>813.9930000000001</v>
       </c>
       <c r="G70">
         <v>278.6</v>
@@ -7027,28 +7027,28 @@
         <v>376.9</v>
       </c>
       <c r="M70">
-        <v>42.917486</v>
+        <v>43.5486255</v>
       </c>
       <c r="N70">
-        <v>333.982514</v>
+        <v>333.3513745</v>
       </c>
       <c r="O70">
-        <v>83.4956285</v>
+        <v>83.33784362499999</v>
       </c>
       <c r="P70">
-        <v>250.4868855</v>
+        <v>250.013530875</v>
       </c>
       <c r="Q70">
-        <v>363.4868855</v>
+        <v>363.013530875</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3430243691235837</v>
+        <v>0.3516881187093859</v>
       </c>
       <c r="T70">
-        <v>2.545959664257477</v>
+        <v>2.620171469472911</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.781968263471908</v>
+        <v>8.654693361102751</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1367095667999096</v>
+        <v>0.1363663354802724</v>
       </c>
       <c r="C71">
-        <v>618.1499450229879</v>
+        <v>610.7246805600265</v>
       </c>
       <c r="D71">
-        <v>1153.542945022988</v>
+        <v>1157.914680560026</v>
       </c>
       <c r="E71">
-        <v>598.193</v>
+        <v>609.99</v>
       </c>
       <c r="F71">
-        <v>813.9930000000001</v>
+        <v>825.7900000000001</v>
       </c>
       <c r="G71">
         <v>278.6</v>
@@ -7109,28 +7109,28 @@
         <v>376.9</v>
       </c>
       <c r="M71">
-        <v>43.5486255</v>
+        <v>44.179765</v>
       </c>
       <c r="N71">
-        <v>333.3513745</v>
+        <v>332.720235</v>
       </c>
       <c r="O71">
-        <v>83.33784362499999</v>
+        <v>83.18005875</v>
       </c>
       <c r="P71">
-        <v>250.013530875</v>
+        <v>249.54017625</v>
       </c>
       <c r="Q71">
-        <v>363.013530875</v>
+        <v>362.54017625</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3516881187093859</v>
+        <v>0.3609294516009081</v>
       </c>
       <c r="T71">
-        <v>2.620171469472911</v>
+        <v>2.699330728369373</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.654693361102751</v>
+        <v>8.531054884515569</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1363663354802724</v>
+        <v>0.1360231041606352</v>
       </c>
       <c r="C72">
-        <v>610.7246805600265</v>
+        <v>603.3326784542272</v>
       </c>
       <c r="D72">
-        <v>1157.914680560026</v>
+        <v>1162.319678454227</v>
       </c>
       <c r="E72">
-        <v>609.99</v>
+        <v>621.787</v>
       </c>
       <c r="F72">
-        <v>825.7900000000001</v>
+        <v>837.5870000000001</v>
       </c>
       <c r="G72">
         <v>278.6</v>
@@ -7191,28 +7191,28 @@
         <v>376.9</v>
       </c>
       <c r="M72">
-        <v>44.179765</v>
+        <v>44.81090450000001</v>
       </c>
       <c r="N72">
-        <v>332.720235</v>
+        <v>332.0890955</v>
       </c>
       <c r="O72">
-        <v>83.18005875</v>
+        <v>83.022273875</v>
       </c>
       <c r="P72">
-        <v>249.54017625</v>
+        <v>249.066821625</v>
       </c>
       <c r="Q72">
-        <v>362.54017625</v>
+        <v>362.066821625</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3609294516009081</v>
+        <v>0.370808117795294</v>
       </c>
       <c r="T72">
-        <v>2.699330728369373</v>
+        <v>2.783949246500075</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.531054884515569</v>
+        <v>8.410899181916758</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1360231041606352</v>
+        <v>0.135679872840998</v>
       </c>
       <c r="C73">
-        <v>603.3326784542273</v>
+        <v>595.9743197703078</v>
       </c>
       <c r="D73">
-        <v>1162.319678454227</v>
+        <v>1166.758319770308</v>
       </c>
       <c r="E73">
-        <v>621.787</v>
+        <v>633.5840000000001</v>
       </c>
       <c r="F73">
-        <v>837.587</v>
+        <v>849.384</v>
       </c>
       <c r="G73">
         <v>278.6</v>
@@ -7273,28 +7273,28 @@
         <v>376.9</v>
       </c>
       <c r="M73">
-        <v>44.8109045</v>
+        <v>45.442044</v>
       </c>
       <c r="N73">
-        <v>332.0890955</v>
+        <v>331.457956</v>
       </c>
       <c r="O73">
-        <v>83.022273875</v>
+        <v>82.86448899999999</v>
       </c>
       <c r="P73">
-        <v>249.066821625</v>
+        <v>248.593467</v>
       </c>
       <c r="Q73">
-        <v>362.066821625</v>
+        <v>361.593467</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3708081177952939</v>
+        <v>0.3813924030035644</v>
       </c>
       <c r="T73">
-        <v>2.783949246500074</v>
+        <v>2.874611944497254</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.410899181916758</v>
+        <v>8.29408113772347</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.135679872840998</v>
+        <v>0.1353366415213609</v>
       </c>
       <c r="C74">
-        <v>595.9743197703078</v>
+        <v>588.6499914161045</v>
       </c>
       <c r="D74">
-        <v>1166.758319770308</v>
+        <v>1171.230991416104</v>
       </c>
       <c r="E74">
-        <v>633.5840000000001</v>
+        <v>645.3810000000001</v>
       </c>
       <c r="F74">
-        <v>849.384</v>
+        <v>861.181</v>
       </c>
       <c r="G74">
         <v>278.6</v>
@@ -7355,28 +7355,28 @@
         <v>376.9</v>
       </c>
       <c r="M74">
-        <v>45.442044</v>
+        <v>46.0731835</v>
       </c>
       <c r="N74">
-        <v>331.457956</v>
+        <v>330.8268164999999</v>
       </c>
       <c r="O74">
-        <v>82.86448899999999</v>
+        <v>82.70670412499999</v>
       </c>
       <c r="P74">
-        <v>248.593467</v>
+        <v>248.120112375</v>
       </c>
       <c r="Q74">
-        <v>361.593467</v>
+        <v>361.120112375</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3813924030035644</v>
+        <v>0.3927607093383735</v>
       </c>
       <c r="T74">
-        <v>2.874611944497254</v>
+        <v>2.971990397901633</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.29408113772347</v>
+        <v>8.180463587891641</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1353366415213609</v>
+        <v>0.1349934102017236</v>
       </c>
       <c r="C75">
-        <v>588.6499914161045</v>
+        <v>581.3600862550006</v>
       </c>
       <c r="D75">
-        <v>1171.230991416104</v>
+        <v>1175.738086255001</v>
       </c>
       <c r="E75">
-        <v>645.3810000000001</v>
+        <v>657.1780000000001</v>
       </c>
       <c r="F75">
-        <v>861.181</v>
+        <v>872.9780000000001</v>
       </c>
       <c r="G75">
         <v>278.6</v>
@@ -7437,28 +7437,28 @@
         <v>376.9</v>
       </c>
       <c r="M75">
-        <v>46.0731835</v>
+        <v>46.704323</v>
       </c>
       <c r="N75">
-        <v>330.8268164999999</v>
+        <v>330.195677</v>
       </c>
       <c r="O75">
-        <v>82.70670412499999</v>
+        <v>82.54891925</v>
       </c>
       <c r="P75">
-        <v>248.120112375</v>
+        <v>247.64675775</v>
       </c>
       <c r="Q75">
-        <v>361.120112375</v>
+        <v>360.64675775</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3927607093383735</v>
+        <v>0.4050035007758602</v>
       </c>
       <c r="T75">
-        <v>2.971990397901633</v>
+        <v>3.076859501567887</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.180463587891641</v>
+        <v>8.069916782649862</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1349934102017236</v>
+        <v>0.1346501788820865</v>
       </c>
       <c r="C76">
-        <v>581.3600862550006</v>
+        <v>574.1050032209591</v>
       </c>
       <c r="D76">
-        <v>1175.738086255001</v>
+        <v>1180.280003220959</v>
       </c>
       <c r="E76">
-        <v>657.1780000000001</v>
+        <v>668.9750000000001</v>
       </c>
       <c r="F76">
-        <v>872.9780000000001</v>
+        <v>884.7750000000001</v>
       </c>
       <c r="G76">
         <v>278.6</v>
@@ -7519,28 +7519,28 @@
         <v>376.9</v>
       </c>
       <c r="M76">
-        <v>46.704323</v>
+        <v>47.33546250000001</v>
       </c>
       <c r="N76">
-        <v>330.195677</v>
+        <v>329.5645375</v>
       </c>
       <c r="O76">
-        <v>82.54891925</v>
+        <v>82.39113437499999</v>
       </c>
       <c r="P76">
-        <v>247.64675775</v>
+        <v>247.173403125</v>
       </c>
       <c r="Q76">
-        <v>360.64675775</v>
+        <v>360.173403125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4050035007758602</v>
+        <v>0.4182257155283459</v>
       </c>
       <c r="T76">
-        <v>3.076859501567887</v>
+        <v>3.190118133527441</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.069916782649862</v>
+        <v>7.96231789221453</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1346501788820865</v>
+        <v>0.1343069475624493</v>
       </c>
       <c r="C77">
-        <v>574.1050032209591</v>
+        <v>566.8851474362315</v>
       </c>
       <c r="D77">
-        <v>1180.280003220959</v>
+        <v>1184.857147436232</v>
       </c>
       <c r="E77">
-        <v>668.9750000000001</v>
+        <v>680.7719999999999</v>
       </c>
       <c r="F77">
-        <v>884.7750000000001</v>
+        <v>896.572</v>
       </c>
       <c r="G77">
         <v>278.6</v>
@@ -7601,28 +7601,28 @@
         <v>376.9</v>
       </c>
       <c r="M77">
-        <v>47.33546250000001</v>
+        <v>47.966602</v>
       </c>
       <c r="N77">
-        <v>329.5645375</v>
+        <v>328.933398</v>
       </c>
       <c r="O77">
-        <v>82.39113437499999</v>
+        <v>82.23334949999999</v>
       </c>
       <c r="P77">
-        <v>247.173403125</v>
+        <v>246.7000485</v>
       </c>
       <c r="Q77">
-        <v>360.173403125</v>
+        <v>359.7000485</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4182257155283459</v>
+        <v>0.4325497815102053</v>
       </c>
       <c r="T77">
-        <v>3.190118133527441</v>
+        <v>3.312814984816958</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.96231789221453</v>
+        <v>7.857550551527497</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1343069475624493</v>
+        <v>0.1339637162428121</v>
       </c>
       <c r="C78">
-        <v>566.8851474362315</v>
+        <v>559.7009303318169</v>
       </c>
       <c r="D78">
-        <v>1184.857147436232</v>
+        <v>1189.469930331817</v>
       </c>
       <c r="E78">
-        <v>680.7719999999999</v>
+        <v>692.569</v>
       </c>
       <c r="F78">
-        <v>896.572</v>
+        <v>908.369</v>
       </c>
       <c r="G78">
         <v>278.6</v>
@@ -7683,28 +7683,28 @@
         <v>376.9</v>
       </c>
       <c r="M78">
-        <v>47.966602</v>
+        <v>48.5977415</v>
       </c>
       <c r="N78">
-        <v>328.933398</v>
+        <v>328.3022585</v>
       </c>
       <c r="O78">
-        <v>82.23334949999999</v>
+        <v>82.075564625</v>
       </c>
       <c r="P78">
-        <v>246.7000485</v>
+        <v>246.226693875</v>
       </c>
       <c r="Q78">
-        <v>359.7000485</v>
+        <v>359.226693875</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4325497815102053</v>
+        <v>0.4481194184470091</v>
       </c>
       <c r="T78">
-        <v>3.312814984816958</v>
+        <v>3.446181127522955</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.857550551527497</v>
+        <v>7.7555044404687</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1339637162428121</v>
+        <v>0.1336204849231749</v>
       </c>
       <c r="C79">
-        <v>559.7009303318169</v>
+        <v>552.5527697707445</v>
       </c>
       <c r="D79">
-        <v>1189.469930331817</v>
+        <v>1194.118769770744</v>
       </c>
       <c r="E79">
-        <v>692.569</v>
+        <v>704.366</v>
       </c>
       <c r="F79">
-        <v>908.369</v>
+        <v>920.1660000000001</v>
       </c>
       <c r="G79">
         <v>278.6</v>
@@ -7765,28 +7765,28 @@
         <v>376.9</v>
       </c>
       <c r="M79">
-        <v>48.5977415</v>
+        <v>49.228881</v>
       </c>
       <c r="N79">
-        <v>328.3022585</v>
+        <v>327.671119</v>
       </c>
       <c r="O79">
-        <v>82.075564625</v>
+        <v>81.91777974999999</v>
       </c>
       <c r="P79">
-        <v>246.226693875</v>
+        <v>245.75333925</v>
       </c>
       <c r="Q79">
-        <v>359.226693875</v>
+        <v>358.75333925</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4481194184470091</v>
+        <v>0.4651044769235222</v>
       </c>
       <c r="T79">
-        <v>3.446181127522955</v>
+        <v>3.591671465020406</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.7555044404687</v>
+        <v>7.656074896360126</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1336204849231749</v>
+        <v>0.1337512536035377</v>
       </c>
       <c r="C80">
-        <v>552.5527697707445</v>
+        <v>538.9803165586355</v>
       </c>
       <c r="D80">
-        <v>1194.118769770744</v>
+        <v>1192.343316558636</v>
       </c>
       <c r="E80">
-        <v>704.366</v>
+        <v>716.163</v>
       </c>
       <c r="F80">
-        <v>920.1660000000001</v>
+        <v>931.9630000000001</v>
       </c>
       <c r="G80">
         <v>278.6</v>
@@ -7847,45 +7847,45 @@
         <v>376.9</v>
       </c>
       <c r="M80">
-        <v>49.228881</v>
+        <v>50.6055909</v>
       </c>
       <c r="N80">
-        <v>327.671119</v>
+        <v>326.2944091</v>
       </c>
       <c r="O80">
-        <v>81.91777974999999</v>
+        <v>81.573602275</v>
       </c>
       <c r="P80">
-        <v>245.75333925</v>
+        <v>244.720806825</v>
       </c>
       <c r="Q80">
-        <v>358.75333925</v>
+        <v>357.720806825</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4651044769235222</v>
+        <v>0.4837071600168463</v>
       </c>
       <c r="T80">
-        <v>3.591671465020406</v>
+        <v>3.751018025136662</v>
       </c>
       <c r="U80">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y80">
-        <v>7.656074896360126</v>
+        <v>7.447793678464882</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1337512536035377</v>
+        <v>0.1334140222839005</v>
       </c>
       <c r="C81">
-        <v>538.9803165586355</v>
+        <v>531.7727133198151</v>
       </c>
       <c r="D81">
-        <v>1192.343316558636</v>
+        <v>1196.932713319815</v>
       </c>
       <c r="E81">
-        <v>716.163</v>
+        <v>727.96</v>
       </c>
       <c r="F81">
-        <v>931.9630000000001</v>
+        <v>943.7600000000001</v>
       </c>
       <c r="G81">
         <v>278.6</v>
@@ -7929,28 +7929,28 @@
         <v>376.9</v>
       </c>
       <c r="M81">
-        <v>50.6055909</v>
+        <v>51.246168</v>
       </c>
       <c r="N81">
-        <v>326.2944091</v>
+        <v>325.653832</v>
       </c>
       <c r="O81">
-        <v>81.573602275</v>
+        <v>81.41345799999999</v>
       </c>
       <c r="P81">
-        <v>244.720806825</v>
+        <v>244.240374</v>
       </c>
       <c r="Q81">
-        <v>357.720806825</v>
+        <v>357.240374</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4837071600168463</v>
+        <v>0.5041701114195026</v>
       </c>
       <c r="T81">
-        <v>3.751018025136662</v>
+        <v>3.926299241264544</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.447793678464882</v>
+        <v>7.35469625748407</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1334140222839005</v>
+        <v>0.1330767909642633</v>
       </c>
       <c r="C82">
-        <v>531.7727133198151</v>
+        <v>524.6005762870506</v>
       </c>
       <c r="D82">
-        <v>1196.932713319815</v>
+        <v>1201.557576287051</v>
       </c>
       <c r="E82">
-        <v>727.96</v>
+        <v>739.7570000000001</v>
       </c>
       <c r="F82">
-        <v>943.7600000000001</v>
+        <v>955.5570000000001</v>
       </c>
       <c r="G82">
         <v>278.6</v>
@@ -8011,28 +8011,28 @@
         <v>376.9</v>
       </c>
       <c r="M82">
-        <v>51.246168</v>
+        <v>51.88674510000001</v>
       </c>
       <c r="N82">
-        <v>325.653832</v>
+        <v>325.0132549</v>
       </c>
       <c r="O82">
-        <v>81.41345799999999</v>
+        <v>81.253313725</v>
       </c>
       <c r="P82">
-        <v>244.240374</v>
+        <v>243.759941175</v>
       </c>
       <c r="Q82">
-        <v>357.240374</v>
+        <v>356.759941175</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5041701114195026</v>
+        <v>0.5267870577066492</v>
       </c>
       <c r="T82">
-        <v>3.926299241264544</v>
+        <v>4.120031111721676</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.35469625748407</v>
+        <v>7.263897538255873</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1330767909642633</v>
+        <v>0.1327395596446261</v>
       </c>
       <c r="C83">
-        <v>524.6005762870506</v>
+        <v>517.4643181717307</v>
       </c>
       <c r="D83">
-        <v>1201.557576287051</v>
+        <v>1206.218318171731</v>
       </c>
       <c r="E83">
-        <v>739.7570000000001</v>
+        <v>751.5540000000001</v>
       </c>
       <c r="F83">
-        <v>955.5570000000001</v>
+        <v>967.3540000000002</v>
       </c>
       <c r="G83">
         <v>278.6</v>
@@ -8093,28 +8093,28 @@
         <v>376.9</v>
       </c>
       <c r="M83">
-        <v>51.88674510000001</v>
+        <v>52.52732220000001</v>
       </c>
       <c r="N83">
-        <v>325.0132549</v>
+        <v>324.3726778</v>
       </c>
       <c r="O83">
-        <v>81.253313725</v>
+        <v>81.09316944999999</v>
       </c>
       <c r="P83">
-        <v>243.759941175</v>
+        <v>243.27950835</v>
       </c>
       <c r="Q83">
-        <v>356.759941175</v>
+        <v>356.27950835</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5267870577066492</v>
+        <v>0.5519169980257008</v>
       </c>
       <c r="T83">
-        <v>4.120031111721676</v>
+        <v>4.335288745562933</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.263897538255873</v>
+        <v>7.175313421935678</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1327395596446261</v>
+        <v>0.1324023283249889</v>
       </c>
       <c r="C84">
-        <v>517.4643181717307</v>
+        <v>510.3643581136723</v>
       </c>
       <c r="D84">
-        <v>1206.218318171731</v>
+        <v>1210.915358113672</v>
       </c>
       <c r="E84">
-        <v>751.5540000000001</v>
+        <v>763.3510000000001</v>
       </c>
       <c r="F84">
-        <v>967.3540000000002</v>
+        <v>979.1510000000001</v>
       </c>
       <c r="G84">
         <v>278.6</v>
@@ -8175,28 +8175,28 @@
         <v>376.9</v>
       </c>
       <c r="M84">
-        <v>52.52732220000001</v>
+        <v>53.1678993</v>
       </c>
       <c r="N84">
-        <v>324.3726778</v>
+        <v>323.7321007</v>
       </c>
       <c r="O84">
-        <v>81.09316944999999</v>
+        <v>80.933025175</v>
       </c>
       <c r="P84">
-        <v>243.27950835</v>
+        <v>242.799075525</v>
       </c>
       <c r="Q84">
-        <v>356.27950835</v>
+        <v>355.799075525</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5519169980257008</v>
+        <v>0.5800034019117</v>
       </c>
       <c r="T84">
-        <v>4.335288745562933</v>
+        <v>4.575870806914929</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.175313421935678</v>
+        <v>7.088863862635249</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1324023283249889</v>
+        <v>0.1320650970053518</v>
       </c>
       <c r="C85">
-        <v>510.3643581136723</v>
+        <v>503.3011218067711</v>
       </c>
       <c r="D85">
-        <v>1210.915358113672</v>
+        <v>1215.649121806771</v>
       </c>
       <c r="E85">
-        <v>763.3510000000001</v>
+        <v>775.1480000000001</v>
       </c>
       <c r="F85">
-        <v>979.1510000000001</v>
+        <v>990.9480000000001</v>
       </c>
       <c r="G85">
         <v>278.6</v>
@@ -8257,28 +8257,28 @@
         <v>376.9</v>
       </c>
       <c r="M85">
-        <v>53.1678993</v>
+        <v>53.8084764</v>
       </c>
       <c r="N85">
-        <v>323.7321007</v>
+        <v>323.0915236</v>
       </c>
       <c r="O85">
-        <v>80.933025175</v>
+        <v>80.77288089999999</v>
       </c>
       <c r="P85">
-        <v>242.799075525</v>
+        <v>242.3186427</v>
       </c>
       <c r="Q85">
-        <v>355.799075525</v>
+        <v>355.3186426999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5800034019117</v>
+        <v>0.6116006062834488</v>
       </c>
       <c r="T85">
-        <v>4.575870806914929</v>
+        <v>4.846525625935922</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.088863862635249</v>
+        <v>7.004472626175305</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1320650970053518</v>
+        <v>0.1317278656857146</v>
       </c>
       <c r="C86">
-        <v>503.3011218067712</v>
+        <v>496.2750416276139</v>
       </c>
       <c r="D86">
-        <v>1215.649121806771</v>
+        <v>1220.420041627614</v>
       </c>
       <c r="E86">
-        <v>775.1479999999999</v>
+        <v>786.9449999999999</v>
       </c>
       <c r="F86">
-        <v>990.948</v>
+        <v>1002.745</v>
       </c>
       <c r="G86">
         <v>278.6</v>
@@ -8339,28 +8339,28 @@
         <v>376.9</v>
       </c>
       <c r="M86">
-        <v>53.8084764</v>
+        <v>54.4490535</v>
       </c>
       <c r="N86">
-        <v>323.0915236</v>
+        <v>322.4509465</v>
       </c>
       <c r="O86">
-        <v>80.77288089999999</v>
+        <v>80.612736625</v>
       </c>
       <c r="P86">
-        <v>242.3186427</v>
+        <v>241.838209875</v>
       </c>
       <c r="Q86">
-        <v>355.3186426999999</v>
+        <v>354.838209875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6116006062834484</v>
+        <v>0.6474107712380971</v>
       </c>
       <c r="T86">
-        <v>4.846525625935919</v>
+        <v>5.153267754159712</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.004472626175306</v>
+        <v>6.922067065867362</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1317278656857146</v>
+        <v>0.1313906343660774</v>
       </c>
       <c r="C87">
-        <v>496.2750416276139</v>
+        <v>489.2865567671264</v>
       </c>
       <c r="D87">
-        <v>1220.420041627614</v>
+        <v>1225.228556767126</v>
       </c>
       <c r="E87">
-        <v>786.9449999999999</v>
+        <v>798.742</v>
       </c>
       <c r="F87">
-        <v>1002.745</v>
+        <v>1014.542</v>
       </c>
       <c r="G87">
         <v>278.6</v>
@@ -8421,28 +8421,28 @@
         <v>376.9</v>
       </c>
       <c r="M87">
-        <v>54.4490535</v>
+        <v>55.0896306</v>
       </c>
       <c r="N87">
-        <v>322.4509465</v>
+        <v>321.8103694</v>
       </c>
       <c r="O87">
-        <v>80.612736625</v>
+        <v>80.45259234999999</v>
       </c>
       <c r="P87">
-        <v>241.838209875</v>
+        <v>241.35777705</v>
       </c>
       <c r="Q87">
-        <v>354.838209875</v>
+        <v>354.35777705</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6474107712380971</v>
+        <v>0.6883366740434098</v>
       </c>
       <c r="T87">
-        <v>5.153267754159712</v>
+        <v>5.503830186415475</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.922067065867362</v>
+        <v>6.841577913938671</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1313906343660774</v>
+        <v>0.1310534030464402</v>
       </c>
       <c r="C88">
-        <v>489.2865567671264</v>
+        <v>482.3361133653502</v>
       </c>
       <c r="D88">
-        <v>1225.228556767126</v>
+        <v>1230.07511336535</v>
       </c>
       <c r="E88">
-        <v>798.742</v>
+        <v>810.539</v>
       </c>
       <c r="F88">
-        <v>1014.542</v>
+        <v>1026.339</v>
       </c>
       <c r="G88">
         <v>278.6</v>
@@ -8503,28 +8503,28 @@
         <v>376.9</v>
       </c>
       <c r="M88">
-        <v>55.0896306</v>
+        <v>55.7302077</v>
       </c>
       <c r="N88">
-        <v>321.8103694</v>
+        <v>321.1697923</v>
       </c>
       <c r="O88">
-        <v>80.45259234999999</v>
+        <v>80.292448075</v>
       </c>
       <c r="P88">
-        <v>241.35777705</v>
+        <v>240.877344225</v>
       </c>
       <c r="Q88">
-        <v>354.35777705</v>
+        <v>353.877344225</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6883366740434098</v>
+        <v>0.7355588695880014</v>
       </c>
       <c r="T88">
-        <v>5.503830186415475</v>
+        <v>5.908325300556739</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.841577913938671</v>
+        <v>6.762939087341675</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1310534030464402</v>
+        <v>0.130716171726803</v>
       </c>
       <c r="C89">
-        <v>482.3361133653502</v>
+        <v>475.4241646494288</v>
       </c>
       <c r="D89">
-        <v>1230.07511336535</v>
+        <v>1234.960164649429</v>
       </c>
       <c r="E89">
-        <v>810.539</v>
+        <v>822.336</v>
       </c>
       <c r="F89">
-        <v>1026.339</v>
+        <v>1038.136</v>
       </c>
       <c r="G89">
         <v>278.6</v>
@@ -8585,28 +8585,28 @@
         <v>376.9</v>
       </c>
       <c r="M89">
-        <v>55.7302077</v>
+        <v>56.3707848</v>
       </c>
       <c r="N89">
-        <v>321.1697923</v>
+        <v>320.5292152</v>
       </c>
       <c r="O89">
-        <v>80.292448075</v>
+        <v>80.13230379999999</v>
       </c>
       <c r="P89">
-        <v>240.877344225</v>
+        <v>240.3969114</v>
       </c>
       <c r="Q89">
-        <v>353.877344225</v>
+        <v>353.3969114</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7355588695880014</v>
+        <v>0.7906514310566917</v>
       </c>
       <c r="T89">
-        <v>5.908325300556739</v>
+        <v>6.380236267054882</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.762939087341675</v>
+        <v>6.686087506803701</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.130716171726803</v>
+        <v>0.1303789404071658</v>
       </c>
       <c r="C90">
-        <v>475.4241646494288</v>
+        <v>468.551171074896</v>
       </c>
       <c r="D90">
-        <v>1234.960164649429</v>
+        <v>1239.884171074896</v>
       </c>
       <c r="E90">
-        <v>822.336</v>
+        <v>834.133</v>
       </c>
       <c r="F90">
-        <v>1038.136</v>
+        <v>1049.933</v>
       </c>
       <c r="G90">
         <v>278.6</v>
@@ -8667,28 +8667,28 @@
         <v>376.9</v>
       </c>
       <c r="M90">
-        <v>56.3707848</v>
+        <v>57.0113619</v>
       </c>
       <c r="N90">
-        <v>320.5292152</v>
+        <v>319.8886381</v>
       </c>
       <c r="O90">
-        <v>80.13230379999999</v>
+        <v>79.972159525</v>
       </c>
       <c r="P90">
-        <v>240.3969114</v>
+        <v>239.916478575</v>
       </c>
       <c r="Q90">
-        <v>353.3969114</v>
+        <v>352.916478575</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7906514310566917</v>
+        <v>0.8557608218833256</v>
       </c>
       <c r="T90">
-        <v>6.380236267054882</v>
+        <v>6.937949227461777</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.686087506803701</v>
+        <v>6.61096292807557</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1303789404071658</v>
+        <v>0.1300417090875286</v>
       </c>
       <c r="C91">
-        <v>468.551171074896</v>
+        <v>461.717600470356</v>
       </c>
       <c r="D91">
-        <v>1239.884171074896</v>
+        <v>1244.847600470356</v>
       </c>
       <c r="E91">
-        <v>834.133</v>
+        <v>845.9300000000001</v>
       </c>
       <c r="F91">
-        <v>1049.933</v>
+        <v>1061.73</v>
       </c>
       <c r="G91">
         <v>278.6</v>
@@ -8749,28 +8749,28 @@
         <v>376.9</v>
       </c>
       <c r="M91">
-        <v>57.0113619</v>
+        <v>57.651939</v>
       </c>
       <c r="N91">
-        <v>319.8886381</v>
+        <v>319.248061</v>
       </c>
       <c r="O91">
-        <v>79.972159525</v>
+        <v>79.81201525</v>
       </c>
       <c r="P91">
-        <v>239.916478575</v>
+        <v>239.43604575</v>
       </c>
       <c r="Q91">
-        <v>352.916478575</v>
+        <v>352.43604575</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8557608218833256</v>
+        <v>0.9338920908752865</v>
       </c>
       <c r="T91">
-        <v>6.937949227461777</v>
+        <v>7.607204779950053</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.61096292807557</v>
+        <v>6.537507784430287</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1300417090875286</v>
+        <v>0.1297044777678914</v>
       </c>
       <c r="C92">
-        <v>461.717600470356</v>
+        <v>454.9239281856553</v>
       </c>
       <c r="D92">
-        <v>1244.847600470356</v>
+        <v>1249.850928185655</v>
       </c>
       <c r="E92">
-        <v>845.9300000000001</v>
+        <v>857.7270000000001</v>
       </c>
       <c r="F92">
-        <v>1061.73</v>
+        <v>1073.527</v>
       </c>
       <c r="G92">
         <v>278.6</v>
@@ -8831,28 +8831,28 @@
         <v>376.9</v>
       </c>
       <c r="M92">
-        <v>57.651939</v>
+        <v>58.2925161</v>
       </c>
       <c r="N92">
-        <v>319.248061</v>
+        <v>318.6074839</v>
       </c>
       <c r="O92">
-        <v>79.81201525</v>
+        <v>79.65187097499999</v>
       </c>
       <c r="P92">
-        <v>239.43604575</v>
+        <v>238.955612925</v>
       </c>
       <c r="Q92">
-        <v>352.43604575</v>
+        <v>351.955612925</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9338920908752865</v>
+        <v>1.029385864087683</v>
       </c>
       <c r="T92">
-        <v>7.607204779950053</v>
+        <v>8.425183788546834</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.537507784430287</v>
+        <v>6.465667039546436</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1297044777678914</v>
+        <v>0.1293672464482543</v>
       </c>
       <c r="C93">
-        <v>454.9239281856553</v>
+        <v>448.1706372436388</v>
       </c>
       <c r="D93">
-        <v>1249.850928185655</v>
+        <v>1254.894637243639</v>
       </c>
       <c r="E93">
-        <v>857.7270000000001</v>
+        <v>869.5240000000001</v>
       </c>
       <c r="F93">
-        <v>1073.527</v>
+        <v>1085.324</v>
       </c>
       <c r="G93">
         <v>278.6</v>
@@ -8913,28 +8913,28 @@
         <v>376.9</v>
       </c>
       <c r="M93">
-        <v>58.2925161</v>
+        <v>58.9330932</v>
       </c>
       <c r="N93">
-        <v>318.6074839</v>
+        <v>317.9669067999999</v>
       </c>
       <c r="O93">
-        <v>79.65187097499999</v>
+        <v>79.49172669999999</v>
       </c>
       <c r="P93">
-        <v>238.955612925</v>
+        <v>238.4751801</v>
       </c>
       <c r="Q93">
-        <v>351.955612925</v>
+        <v>351.4751801</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.029385864087683</v>
+        <v>1.148753080603179</v>
       </c>
       <c r="T93">
-        <v>8.425183788546834</v>
+        <v>9.447657549292812</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.465667039546436</v>
+        <v>6.395388049986148</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1293672464482543</v>
+        <v>0.1290300151286171</v>
       </c>
       <c r="C94">
-        <v>448.1706372436388</v>
+        <v>441.4582184955989</v>
       </c>
       <c r="D94">
-        <v>1254.894637243639</v>
+        <v>1259.979218495599</v>
       </c>
       <c r="E94">
-        <v>869.5240000000001</v>
+        <v>881.3210000000001</v>
       </c>
       <c r="F94">
-        <v>1085.324</v>
+        <v>1097.121</v>
       </c>
       <c r="G94">
         <v>278.6</v>
@@ -8995,28 +8995,28 @@
         <v>376.9</v>
       </c>
       <c r="M94">
-        <v>58.9330932</v>
+        <v>59.5736703</v>
       </c>
       <c r="N94">
-        <v>317.9669067999999</v>
+        <v>317.3263297</v>
       </c>
       <c r="O94">
-        <v>79.49172669999999</v>
+        <v>79.33158242499999</v>
       </c>
       <c r="P94">
-        <v>238.4751801</v>
+        <v>237.994747275</v>
       </c>
       <c r="Q94">
-        <v>351.4751801</v>
+        <v>350.994747275</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.148753080603179</v>
+        <v>1.302225216123102</v>
       </c>
       <c r="T94">
-        <v>9.447657549292812</v>
+        <v>10.76226667025192</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.395388049986148</v>
+        <v>6.326620436545437</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1290300151286171</v>
+        <v>0.1286927838089799</v>
       </c>
       <c r="C95">
-        <v>441.4582184955989</v>
+        <v>434.7871707805152</v>
       </c>
       <c r="D95">
-        <v>1259.979218495599</v>
+        <v>1265.105170780515</v>
       </c>
       <c r="E95">
-        <v>881.3210000000001</v>
+        <v>893.1180000000002</v>
       </c>
       <c r="F95">
-        <v>1097.121</v>
+        <v>1108.918</v>
       </c>
       <c r="G95">
         <v>278.6</v>
@@ -9077,28 +9077,28 @@
         <v>376.9</v>
       </c>
       <c r="M95">
-        <v>59.5736703</v>
+        <v>60.2142474</v>
       </c>
       <c r="N95">
-        <v>317.3263297</v>
+        <v>316.6857526</v>
       </c>
       <c r="O95">
-        <v>79.33158242499999</v>
+        <v>79.17143815</v>
       </c>
       <c r="P95">
-        <v>237.994747275</v>
+        <v>237.51431445</v>
       </c>
       <c r="Q95">
-        <v>350.994747275</v>
+        <v>350.51431445</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.302225216123102</v>
+        <v>1.506854730149666</v>
       </c>
       <c r="T95">
-        <v>10.76226667025192</v>
+        <v>12.51507883153074</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.326620436545437</v>
+        <v>6.259315963816231</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1286927838089799</v>
+        <v>0.1283555524893427</v>
       </c>
       <c r="C96">
-        <v>434.7871707805152</v>
+        <v>428.1580010882003</v>
       </c>
       <c r="D96">
-        <v>1265.105170780515</v>
+        <v>1270.273001088201</v>
       </c>
       <c r="E96">
-        <v>893.1180000000002</v>
+        <v>904.9150000000002</v>
       </c>
       <c r="F96">
-        <v>1108.918</v>
+        <v>1120.715</v>
       </c>
       <c r="G96">
         <v>278.6</v>
@@ -9159,28 +9159,28 @@
         <v>376.9</v>
       </c>
       <c r="M96">
-        <v>60.2142474</v>
+        <v>60.85482450000001</v>
       </c>
       <c r="N96">
-        <v>316.6857526</v>
+        <v>316.0451755</v>
       </c>
       <c r="O96">
-        <v>79.17143815</v>
+        <v>79.01129387499999</v>
       </c>
       <c r="P96">
-        <v>237.51431445</v>
+        <v>237.033881625</v>
       </c>
       <c r="Q96">
-        <v>350.51431445</v>
+        <v>350.033881625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.506854730149666</v>
+        <v>1.793336049786856</v>
       </c>
       <c r="T96">
-        <v>12.51507883153074</v>
+        <v>14.96901585732109</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.259315963816231</v>
+        <v>6.193428427355006</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1283555524893427</v>
+        <v>0.1280183211697055</v>
       </c>
       <c r="C97">
-        <v>428.1580010882003</v>
+        <v>421.5712247264605</v>
       </c>
       <c r="D97">
-        <v>1270.273001088201</v>
+        <v>1275.483224726461</v>
       </c>
       <c r="E97">
-        <v>904.9150000000002</v>
+        <v>916.7120000000002</v>
       </c>
       <c r="F97">
-        <v>1120.715</v>
+        <v>1132.512</v>
       </c>
       <c r="G97">
         <v>278.6</v>
@@ -9241,28 +9241,28 @@
         <v>376.9</v>
       </c>
       <c r="M97">
-        <v>60.85482450000001</v>
+        <v>61.49540160000001</v>
       </c>
       <c r="N97">
-        <v>316.0451755</v>
+        <v>315.4045983999999</v>
       </c>
       <c r="O97">
-        <v>79.01129387499999</v>
+        <v>78.85114959999999</v>
       </c>
       <c r="P97">
-        <v>237.033881625</v>
+        <v>236.5534488</v>
       </c>
       <c r="Q97">
-        <v>350.033881625</v>
+        <v>349.5534488</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.793336049786856</v>
+        <v>2.223058029242641</v>
       </c>
       <c r="T97">
-        <v>14.96901585732109</v>
+        <v>18.64992139600661</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.193428427355006</v>
+        <v>6.128913547903392</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1280183211697055</v>
+        <v>0.1284085898500683</v>
       </c>
       <c r="C98">
-        <v>421.5712247264603</v>
+        <v>403.7484451332932</v>
       </c>
       <c r="D98">
-        <v>1275.48322472646</v>
+        <v>1269.457445133293</v>
       </c>
       <c r="E98">
-        <v>916.712</v>
+        <v>928.509</v>
       </c>
       <c r="F98">
-        <v>1132.512</v>
+        <v>1144.309</v>
       </c>
       <c r="G98">
         <v>278.6</v>
@@ -9323,45 +9323,45 @@
         <v>376.9</v>
       </c>
       <c r="M98">
-        <v>61.4954016</v>
+        <v>63.2802877</v>
       </c>
       <c r="N98">
-        <v>315.4045984</v>
+        <v>313.6197122999999</v>
       </c>
       <c r="O98">
-        <v>78.8511496</v>
+        <v>78.40492807499999</v>
       </c>
       <c r="P98">
-        <v>236.5534488</v>
+        <v>235.214784225</v>
       </c>
       <c r="Q98">
-        <v>349.5534488</v>
+        <v>348.214784225</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.223058029242636</v>
+        <v>2.939261328335608</v>
       </c>
       <c r="T98">
-        <v>18.64992139600657</v>
+        <v>24.7847639604824</v>
       </c>
       <c r="U98">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>6.128913547903393</v>
+        <v>5.956041189111091</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1284085898500683</v>
+        <v>0.1280788585304311</v>
       </c>
       <c r="C99">
-        <v>403.7484451332932</v>
+        <v>397.0387772388092</v>
       </c>
       <c r="D99">
-        <v>1269.457445133293</v>
+        <v>1274.544777238809</v>
       </c>
       <c r="E99">
-        <v>928.509</v>
+        <v>940.306</v>
       </c>
       <c r="F99">
-        <v>1144.309</v>
+        <v>1156.106</v>
       </c>
       <c r="G99">
         <v>278.6</v>
@@ -9405,28 +9405,28 @@
         <v>376.9</v>
       </c>
       <c r="M99">
-        <v>63.2802877</v>
+        <v>63.93266180000001</v>
       </c>
       <c r="N99">
-        <v>313.6197122999999</v>
+        <v>312.9673382</v>
       </c>
       <c r="O99">
-        <v>78.40492807499999</v>
+        <v>78.24183454999999</v>
       </c>
       <c r="P99">
-        <v>235.214784225</v>
+        <v>234.72550365</v>
       </c>
       <c r="Q99">
-        <v>348.214784225</v>
+        <v>347.72550365</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.939261328335608</v>
+        <v>4.371667926521552</v>
       </c>
       <c r="T99">
-        <v>24.7847639604824</v>
+        <v>37.05444908943409</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.956041189111091</v>
+        <v>5.895265258609958</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1280788585304311</v>
+        <v>0.1277491272107939</v>
       </c>
       <c r="C100">
-        <v>397.0387772388092</v>
+        <v>390.3700482239853</v>
       </c>
       <c r="D100">
-        <v>1274.544777238809</v>
+        <v>1279.673048223985</v>
       </c>
       <c r="E100">
-        <v>940.306</v>
+        <v>952.1030000000001</v>
       </c>
       <c r="F100">
-        <v>1156.106</v>
+        <v>1167.903</v>
       </c>
       <c r="G100">
         <v>278.6</v>
@@ -9487,28 +9487,28 @@
         <v>376.9</v>
       </c>
       <c r="M100">
-        <v>63.93266180000001</v>
+        <v>64.58503590000001</v>
       </c>
       <c r="N100">
-        <v>312.9673382</v>
+        <v>312.3149641</v>
       </c>
       <c r="O100">
-        <v>78.24183454999999</v>
+        <v>78.078741025</v>
       </c>
       <c r="P100">
-        <v>234.72550365</v>
+        <v>234.236223075</v>
       </c>
       <c r="Q100">
-        <v>347.72550365</v>
+        <v>347.236223075</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.371667926521552</v>
+        <v>8.668887721079386</v>
       </c>
       <c r="T100">
-        <v>37.05444908943409</v>
+        <v>73.86350447628915</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.895265258609958</v>
+        <v>5.835717124684605</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1277491272107939</v>
-      </c>
-      <c r="C101">
-        <v>390.3700482239853</v>
-      </c>
-      <c r="D101">
-        <v>1279.673048223985</v>
-      </c>
-      <c r="E101">
-        <v>952.1030000000001</v>
-      </c>
-      <c r="F101">
-        <v>1167.903</v>
-      </c>
-      <c r="G101">
-        <v>278.6</v>
-      </c>
-      <c r="H101">
-        <v>963.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>489.9</v>
-      </c>
-      <c r="K101">
-        <v>113</v>
-      </c>
-      <c r="L101">
-        <v>376.9</v>
-      </c>
-      <c r="M101">
-        <v>64.58503590000001</v>
-      </c>
-      <c r="N101">
-        <v>312.3149641</v>
-      </c>
-      <c r="O101">
-        <v>78.078741025</v>
-      </c>
-      <c r="P101">
-        <v>234.236223075</v>
-      </c>
-      <c r="Q101">
-        <v>347.236223075</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.668887721079386</v>
-      </c>
-      <c r="T101">
-        <v>73.86350447628915</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.041475</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.835717124684605</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
